--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -200,7 +200,7 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The language switcher at the top of the page (read out by screen readers)</t>
+          <t xml:space="preserve">The label over the language switcher at the top of the page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
@@ -210,7 +210,7 @@
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the language switcher, for screen readers.</t>
+          <t xml:space="preserve">The label over the language switcher, also read out by screen readers.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -259,22 +259,22 @@
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lede.intro</t>
+          <t xml:space="preserve">language.machine.title</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: what the tool does</t>
+          <t xml:space="preserve">Under the language switcher, only when the page is in Chinese or Malay: the note that a computer translated it</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool does the following to your video:</t>
+          <t xml:space="preserve">Machine translation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the three lines that follow.</t>
+          <t xml:space="preserve">The heading of the note, so no full stop.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -291,17 +291,17 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lede.promises.0</t>
+          <t xml:space="preserve">language.machine.text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: what the tool does</t>
+          <t xml:space="preserve">Under the language switcher, only when the page is in Chinese or Malay: the note that a computer translated it</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds approved branding.</t>
+          <t xml:space="preserve">A computer translated this page from English, so some words may be wrong.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -323,22 +323,22 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lede.promises.1</t>
+          <t xml:space="preserve">language.machine.link</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: what the tool does</t>
+          <t xml:space="preserve">Under the language switcher, only when the page is in Chinese or Malay: the note that a computer translated it</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ensures consistent audio levels.</t>
+          <t xml:space="preserve">Email better wording to {address}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The words of a link that opens an email to the maintainer, with your language in its subject. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -355,7 +355,7 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lede.promises.2</t>
+          <t xml:space="preserve">lede.intro</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -365,12 +365,12 @@
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Outputs an optimised file type and size.</t>
+          <t xml:space="preserve">This tool does the following to your video:</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the three lines that follow.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -387,7 +387,7 @@
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lede.privacy</t>
+          <t xml:space="preserve">lede.promises.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -397,7 +397,7 @@
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is processed on your device, it is never uploaded, and the original file does not change.</t>
+          <t xml:space="preserve">Adds approved branding.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -419,17 +419,17 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">browserNote.pending</t>
+          <t xml:space="preserve">lede.promises.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: the note about the browser</t>
+          <t xml:space="preserve">Under the page heading: what the tool does</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This app is designed and built for Chrome, other browsers may not work.</t>
+          <t xml:space="preserve">Ensures consistent audio levels.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -451,17 +451,17 @@
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">browserNote.notPassed</t>
+          <t xml:space="preserve">lede.promises.2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: the note about the browser</t>
+          <t xml:space="preserve">Under the page heading: what the tool does</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This app is designed and built for Chrome, and this browser has not passed all of its checks. The system check at the foot of the page says what is missing.</t>
+          <t xml:space="preserve">Outputs an optimised file type and size.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -483,17 +483,17 @@
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">browserNote.passed</t>
+          <t xml:space="preserve">lede.privacy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Under the page heading: the note about the browser</t>
+          <t xml:space="preserve">Under the page heading: what the tool does</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This app is designed and built for Chrome, and this browser has passed the checks for it.</t>
+          <t xml:space="preserve">Your video is processed on your device, it is never uploaded, and the original file does not change.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -515,17 +515,17 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.choose</t>
+          <t xml:space="preserve">browserNote.pending</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Under the page heading: the note about the browser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a video</t>
+          <t xml:space="preserve">This app is designed and built for Chrome, other browsers may not work.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -547,17 +547,17 @@
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.trim</t>
+          <t xml:space="preserve">browserNote.notPassed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Under the page heading: the note about the browser</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Trim</t>
+          <t xml:space="preserve">This app is designed and built for Chrome, and this browser has not passed all of its checks. The system check at the foot of the page says what is missing.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -579,17 +579,17 @@
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.closing</t>
+          <t xml:space="preserve">browserNote.passed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Under the page heading: the note about the browser</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">This app is designed and built for Chrome, and this browser has passed the checks for it.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -611,7 +611,7 @@
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.preset</t>
+          <t xml:space="preserve">steps.choose</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -621,7 +621,7 @@
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">Choose a video</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -643,7 +643,7 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.create</t>
+          <t xml:space="preserve">steps.trim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -653,7 +653,7 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create</t>
+          <t xml:space="preserve">Trim</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -675,17 +675,17 @@
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHint</t>
+          <t xml:space="preserve">steps.closing</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Or drop it here.</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -707,17 +707,17 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHeld</t>
+          <t xml:space="preserve">steps.preset</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Let go to read this video.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -739,17 +739,17 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.reading</t>
+          <t xml:space="preserve">steps.create</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">Create</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -771,17 +771,17 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.making</t>
+          <t xml:space="preserve">choose.dropHint</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">Or drop it here.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -803,17 +803,17 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.saving</t>
+          <t xml:space="preserve">choose.dropHeld</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">Let go to read this video.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -835,17 +835,17 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.starting</t>
+          <t xml:space="preserve">choose.reading</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -867,7 +867,7 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.unavailable</t>
+          <t xml:space="preserve">choose.drop.making</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -877,7 +877,7 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
+          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -899,7 +899,7 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.nothing</t>
+          <t xml:space="preserve">choose.drop.saving</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -909,7 +909,7 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
+          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -931,7 +931,7 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.several</t>
+          <t xml:space="preserve">choose.drop.starting</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -941,12 +941,12 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
+          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -963,7 +963,7 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.notVideo</t>
+          <t xml:space="preserve">choose.drop.unavailable</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -973,7 +973,7 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
+          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -995,22 +995,22 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.readSummary</t>
+          <t xml:space="preserve">choose.drop.nothing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video read. {facts}.</t>
+          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1027,22 +1027,22 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variableFrameRate</t>
+          <t xml:space="preserve">choose.drop.several</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">variable frame rate</t>
+          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1059,17 +1059,17 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSound</t>
+          <t xml:space="preserve">choose.drop.notVideo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no sound</t>
+          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -1091,7 +1091,7 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.properties</t>
+          <t xml:space="preserve">source.readSummary</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video properties</t>
+          <t xml:space="preserve">Video read. {facts}.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1123,7 +1123,7 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.lossesTitle</t>
+          <t xml:space="preserve">source.variableFrameRate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not carried into the new file</t>
+          <t xml:space="preserve">variable frame rate</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
@@ -1155,17 +1155,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.duration</t>
+          <t xml:space="preserve">source.noSound</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t xml:space="preserve">no sound</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -1187,17 +1187,17 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.videoFormat</t>
+          <t xml:space="preserve">source.properties</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format</t>
+          <t xml:space="preserve">Video properties</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
@@ -1219,17 +1219,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileSize</t>
+          <t xml:space="preserve">source.lossesTitle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size</t>
+          <t xml:space="preserve">Not carried into the new file</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
@@ -1251,7 +1251,7 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.resolution</t>
+          <t xml:space="preserve">source.rows.duration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Resolution</t>
+          <t xml:space="preserve">Duration</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
@@ -1283,7 +1283,7 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.frameRate</t>
+          <t xml:space="preserve">source.rows.videoFormat</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Frame rate</t>
+          <t xml:space="preserve">Video format</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -1315,7 +1315,7 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundFormat</t>
+          <t xml:space="preserve">source.rows.fileSize</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format</t>
+          <t xml:space="preserve">File size</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
@@ -1347,7 +1347,7 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundChannels</t>
+          <t xml:space="preserve">source.rows.resolution</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound channels</t>
+          <t xml:space="preserve">Resolution</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
@@ -1379,7 +1379,7 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sampleRate</t>
+          <t xml:space="preserve">source.rows.frameRate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound sample rate</t>
+          <t xml:space="preserve">Frame rate</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -1411,7 +1411,7 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sound</t>
+          <t xml:space="preserve">source.rows.soundFormat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound</t>
+          <t xml:space="preserve">Sound format</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -1443,7 +1443,7 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.captions</t>
+          <t xml:space="preserve">source.rows.soundChannels</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Captions</t>
+          <t xml:space="preserve">Sound channels</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -1475,7 +1475,7 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileType</t>
+          <t xml:space="preserve">source.rows.sampleRate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File type</t>
+          <t xml:space="preserve">Sound sample rate</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -1507,17 +1507,17 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeVideo</t>
+          <t xml:space="preserve">source.rows.sound</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this video format.</t>
+          <t xml:space="preserve">Sound</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -1539,17 +1539,17 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeAudio</t>
+          <t xml:space="preserve">source.rows.captions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this audio format.</t>
+          <t xml:space="preserve">Captions</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -1571,22 +1571,22 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rotated</t>
+          <t xml:space="preserve">source.rows.fileType</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
+          <t xml:space="preserve">File type</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1603,7 +1603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesOnAverage</t>
+          <t xml:space="preserve">source.cannotDecodeVideo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} on average, but it varies</t>
+          <t xml:space="preserve">This browser cannot read this video format.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1635,7 +1635,7 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesNote</t>
+          <t xml:space="preserve">source.cannotDecodeAudio</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
+          <t xml:space="preserve">This browser cannot read this audio format.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -1667,7 +1667,7 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.outputRate</t>
+          <t xml:space="preserve">source.rotated</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
+          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1699,7 +1699,7 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.sampleRate</t>
+          <t xml:space="preserve">source.variesOnAverage</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
+          <t xml:space="preserve">{rate} on average, but it varies</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1731,7 +1731,7 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundTrack</t>
+          <t xml:space="preserve">source.variesNote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No sound track found</t>
+          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="2">
@@ -1763,7 +1763,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundNote</t>
+          <t xml:space="preserve">source.outputRate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
+          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -1795,7 +1795,7 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsUnchecked</t>
+          <t xml:space="preserve">source.sampleRate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not be checked in this kind of file</t>
+          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -1827,7 +1827,7 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsFound</t>
+          <t xml:space="preserve">source.noSoundTrack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Found {found}</t>
+          <t xml:space="preserve">No sound track found</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -1859,7 +1859,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsNone</t>
+          <t xml:space="preserve">source.noSoundNote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None found in this file</t>
+          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
@@ -1891,7 +1891,7 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.one</t>
+          <t xml:space="preserve">source.captionsUnchecked</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption track</t>
+          <t xml:space="preserve">Could not be checked in this kind of file</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -1923,7 +1923,7 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.other</t>
+          <t xml:space="preserve">source.captionsFound</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption tracks</t>
+          <t xml:space="preserve">Found {found}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -1955,7 +1955,7 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.one</t>
+          <t xml:space="preserve">source.captionsNone</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter track</t>
+          <t xml:space="preserve">None found in this file</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -1987,7 +1987,7 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.other</t>
+          <t xml:space="preserve">source.captionTracks.one</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter tracks</t>
+          <t xml:space="preserve">{count} caption track</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2019,7 +2019,7 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.one</t>
+          <t xml:space="preserve">source.captionTracks.other</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video track</t>
+          <t xml:space="preserve">{count} caption tracks</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2051,7 +2051,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.other</t>
+          <t xml:space="preserve">source.chapterTracks.one</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video tracks</t>
+          <t xml:space="preserve">{count} chapter track</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2083,7 +2083,7 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.one</t>
+          <t xml:space="preserve">source.chapterTracks.other</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound track</t>
+          <t xml:space="preserve">{count} chapter tracks</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2115,7 +2115,7 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.other</t>
+          <t xml:space="preserve">source.moreVideoTracks.one</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound tracks</t>
+          <t xml:space="preserve">{count} more video track</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2147,22 +2147,22 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksTitle</t>
+          <t xml:space="preserve">source.moreVideoTracks.other</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has {found}</t>
+          <t xml:space="preserve">{count} more video tracks</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2179,22 +2179,22 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksDetail</t>
+          <t xml:space="preserve">source.moreSoundTracks.one</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
+          <t xml:space="preserve">{count} more sound track</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2211,22 +2211,22 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedTitle</t>
+          <t xml:space="preserve">source.moreSoundTracks.other</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
+          <t xml:space="preserve">{count} more sound tracks</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2243,7 +2243,7 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedDetail</t>
+          <t xml:space="preserve">source.losses.extraTracksTitle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
+          <t xml:space="preserve">This file has {found}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2275,7 +2275,7 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.captionsConsequence</t>
+          <t xml:space="preserve">source.losses.extraTracksDetail</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
+          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="2">
@@ -2307,7 +2307,7 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.chaptersConsequence</t>
+          <t xml:space="preserve">source.losses.uncheckedTitle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The chapters will not be in the new file.</t>
+          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="2">
@@ -2339,7 +2339,7 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.keepOriginals</t>
+          <t xml:space="preserve">source.losses.uncheckedDetail</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
+          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="2">
@@ -2371,17 +2371,17 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.intro</t>
+          <t xml:space="preserve">source.losses.captionsConsequence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
+          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="2">
@@ -2403,17 +2403,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.noPreview</t>
+          <t xml:space="preserve">source.losses.chaptersConsequence</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
+          <t xml:space="preserve">The chapters will not be in the new file.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="2">
@@ -2435,17 +2435,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.start</t>
+          <t xml:space="preserve">source.losses.keepOriginals</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start</t>
+          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="2">
@@ -2467,7 +2467,7 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.end</t>
+          <t xml:space="preserve">trim.intro</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End</t>
+          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="2">
@@ -2499,7 +2499,7 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.startTime</t>
+          <t xml:space="preserve">trim.noPreview</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start time</t>
+          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="2">
@@ -2531,7 +2531,7 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.endTime</t>
+          <t xml:space="preserve">trim.start</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End time</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="2">
@@ -2563,7 +2563,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setStart</t>
+          <t xml:space="preserve">trim.end</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set start here</t>
+          <t xml:space="preserve">End</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="2">
@@ -2595,7 +2595,7 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setEnd</t>
+          <t xml:space="preserve">trim.startTime</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set end here</t>
+          <t xml:space="preserve">Start time</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="2">
@@ -2627,7 +2627,7 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.format</t>
+          <t xml:space="preserve">trim.endTime</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
+          <t xml:space="preserve">End time</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2659,7 +2659,7 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.useWhole</t>
+          <t xml:space="preserve">trim.setStart</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the whole video</t>
+          <t xml:space="preserve">Set start here</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="2">
@@ -2691,7 +2691,7 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.reading</t>
+          <t xml:space="preserve">trim.setEnd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">Set end here</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="2">
@@ -2723,7 +2723,7 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.unreadable</t>
+          <t xml:space="preserve">trim.format</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
+          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2755,7 +2755,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.tooShort</t>
+          <t xml:space="preserve">trim.useWhole</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
+          <t xml:space="preserve">Use the whole video</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -2787,7 +2787,7 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keepingWhole</t>
+          <t xml:space="preserve">trim.reading</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -2819,7 +2819,7 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keeping</t>
+          <t xml:space="preserve">trim.unreadable</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
+          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -2851,7 +2851,7 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleBeginning</t>
+          <t xml:space="preserve">trim.tooShort</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the beginning</t>
+          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -2883,7 +2883,7 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleEnd</t>
+          <t xml:space="preserve">trim.keepingWhole</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the end</t>
+          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -2915,22 +2915,22 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.start</t>
+          <t xml:space="preserve">trim.keeping</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
+          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -2947,22 +2947,22 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.end</t>
+          <t xml:space="preserve">trim.handleBeginning</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">the beginning</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
+          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -2979,22 +2979,22 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.start</t>
+          <t xml:space="preserve">trim.handleEnd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">the end</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3011,7 +3011,7 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.end</t>
+          <t xml:space="preserve">trim.problem.notATime.start</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3043,7 +3043,7 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notTimes</t>
+          <t xml:space="preserve">trim.problem.notATime.end</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start or end of the video is not a time.</t>
+          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3075,7 +3075,7 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.startAfterEnd</t>
+          <t xml:space="preserve">trim.problem.afterEnd.start</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start is after the end of the video.</t>
+          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3107,7 +3107,7 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.endBeforeStart</t>
+          <t xml:space="preserve">trim.problem.afterEnd.end</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end must come after the start.</t>
+          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3139,7 +3139,7 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.keepAtLeast</t>
+          <t xml:space="preserve">trim.problem.notTimes</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
+          <t xml:space="preserve">The start or end of the video is not a time.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3171,17 +3171,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.correctToContinue</t>
+          <t xml:space="preserve">trim.problem.startAfterEnd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
+          <t xml:space="preserve">The start is after the end of the video.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="2">
@@ -3203,17 +3203,17 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.legend</t>
+          <t xml:space="preserve">trim.problem.endBeforeStart</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">The end must come after the start.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="2">
@@ -3235,22 +3235,22 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.typeLabel</t>
+          <t xml:space="preserve">trim.problem.keepAtLeast</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation type</t>
+          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3267,17 +3267,17 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.cut</t>
+          <t xml:space="preserve">trim.correctToContinue</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cut</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="2">
@@ -3299,7 +3299,7 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.fade</t>
+          <t xml:space="preserve">closing.legend</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Fade</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="2">
@@ -3331,7 +3331,7 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.slide</t>
+          <t xml:space="preserve">closing.typeLabel</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Slide</t>
+          <t xml:space="preserve">Animation type</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="2">
@@ -3363,7 +3363,7 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.none</t>
+          <t xml:space="preserve">closing.types.cut</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Cut</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="2">
@@ -3395,7 +3395,7 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsetLabel</t>
+          <t xml:space="preserve">closing.types.fade</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation onset</t>
+          <t xml:space="preserve">Fade</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="2">
@@ -3427,7 +3427,7 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.existing</t>
+          <t xml:space="preserve">closing.types.slide</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">Slide</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="2">
@@ -3459,7 +3459,7 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.freeze</t>
+          <t xml:space="preserve">closing.types.none</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="2">
@@ -3491,7 +3491,7 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpLabel</t>
+          <t xml:space="preserve">closing.onsetLabel</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About animation onset</t>
+          <t xml:space="preserve">Animation onset</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="2">
@@ -3523,7 +3523,7 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingTerm</t>
+          <t xml:space="preserve">closing.onsets.existing</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3555,7 +3555,7 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingText</t>
+          <t xml:space="preserve">closing.onsets.freeze</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3587,7 +3587,7 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeTerm</t>
+          <t xml:space="preserve">closing.helpLabel</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">About animation onset</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="2">
@@ -3619,7 +3619,7 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeText</t>
+          <t xml:space="preserve">closing.helpExistingTerm</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3651,7 +3651,7 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colourLabel</t>
+          <t xml:space="preserve">closing.helpExistingText</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Colour</t>
+          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3683,7 +3683,7 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.blue</t>
+          <t xml:space="preserve">closing.helpFreezeTerm</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Blue</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3715,7 +3715,7 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.white</t>
+          <t xml:space="preserve">closing.helpFreezeText</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">White</t>
+          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3747,7 +3747,7 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.cut</t>
+          <t xml:space="preserve">closing.colourLabel</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with Cut.</t>
+          <t xml:space="preserve">Colour</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3779,7 +3779,7 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.none</t>
+          <t xml:space="preserve">closing.colours.blue</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with None.</t>
+          <t xml:space="preserve">Blue</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -3811,22 +3811,22 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.none</t>
+          <t xml:space="preserve">closing.colours.white</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No University closing will be added.</t>
+          <t xml:space="preserve">White</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -3843,22 +3843,22 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.one</t>
+          <t xml:space="preserve">closing.notUsedWith.cut</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} second.</t>
+          <t xml:space="preserve">Not used with Cut.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -3875,22 +3875,22 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.other</t>
+          <t xml:space="preserve">closing.notUsedWith.none</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} seconds.</t>
+          <t xml:space="preserve">Not used with None.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -3907,7 +3907,7 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.blue</t>
+          <t xml:space="preserve">closing.result.none</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
+          <t xml:space="preserve">No University closing will be added.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -3939,7 +3939,7 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.white</t>
+          <t xml:space="preserve">closing.result.adds.one</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
+          <t xml:space="preserve">Adds {count} second.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -3971,7 +3971,7 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
+          <t xml:space="preserve">closing.result.adds.other</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Adds {count} seconds.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4003,7 +4003,7 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
+          <t xml:space="preserve">closing.result.cut.blue</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4035,7 +4035,7 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
+          <t xml:space="preserve">closing.result.cut.white</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4067,7 +4067,7 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4099,7 +4099,7 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4131,7 +4131,7 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4163,7 +4163,7 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4195,7 +4195,7 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4227,22 +4227,22 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.legend</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4259,22 +4259,22 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.best</t>
+          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larger / better</t>
+          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4291,22 +4291,22 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.smaller</t>
+          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Smaller / reduced</t>
+          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4323,7 +4323,7 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.best</t>
+          <t xml:space="preserve">preset.legend</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="2">
@@ -4355,7 +4355,7 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.smaller</t>
+          <t xml:space="preserve">preset.labels.best</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For messaging or email etc.</t>
+          <t xml:space="preserve">Larger / better</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4387,22 +4387,22 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.note</t>
+          <t xml:space="preserve">preset.labels.smaller</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
+          <t xml:space="preserve">Smaller / reduced</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4419,17 +4419,17 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceProgress</t>
+          <t xml:space="preserve">preset.details.best</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Announce progress</t>
+          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="2">
@@ -4451,17 +4451,17 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceHelp</t>
+          <t xml:space="preserve">preset.details.smaller</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
+          <t xml:space="preserve">For messaging or email etc.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="2">
@@ -4483,7 +4483,7 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.progressLabel</t>
+          <t xml:space="preserve">create.note</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video</t>
+          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="2">
@@ -4515,7 +4515,7 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.create</t>
+          <t xml:space="preserve">create.announceProgress</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create the video</t>
+          <t xml:space="preserve">Announce progress</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="2">
@@ -4547,7 +4547,7 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.cancel</t>
+          <t xml:space="preserve">create.announceHelp</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="2">
@@ -4579,7 +4579,7 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.continueAnyway</t>
+          <t xml:space="preserve">create.progressLabel</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Continue anyway</t>
+          <t xml:space="preserve">Creating your video</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="2">
@@ -4611,7 +4611,7 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopCheck</t>
+          <t xml:space="preserve">create.create</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop the check</t>
+          <t xml:space="preserve">Create the video</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="2">
@@ -4643,7 +4643,7 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.checkAgain</t>
+          <t xml:space="preserve">create.cancel</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check again</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="2">
@@ -4675,7 +4675,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopSaving</t>
+          <t xml:space="preserve">create.continueAnyway</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop saving</t>
+          <t xml:space="preserve">Continue anyway</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="2">
@@ -4707,7 +4707,7 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.save</t>
+          <t xml:space="preserve">create.stopCheck</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save the video</t>
+          <t xml:space="preserve">Stop the check</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="2">
@@ -4739,7 +4739,7 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.saved</t>
+          <t xml:space="preserve">create.checkAgain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved</t>
+          <t xml:space="preserve">Check again</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="2">
@@ -4771,7 +4771,7 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.discard</t>
+          <t xml:space="preserve">create.stopSaving</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Discard it and start again</t>
+          <t xml:space="preserve">Stop saving</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="2">
@@ -4803,7 +4803,7 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.keep</t>
+          <t xml:space="preserve">create.save</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep it</t>
+          <t xml:space="preserve">Save the video</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="2">
@@ -4835,7 +4835,7 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedMaking</t>
+          <t xml:space="preserve">create.saved</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being made.</t>
+          <t xml:space="preserve">Saved</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="2">
@@ -4867,7 +4867,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedSaving</t>
+          <t xml:space="preserve">create.discard</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being saved.</t>
+          <t xml:space="preserve">Discard it and start again</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="2">
@@ -4899,17 +4899,17 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checking</t>
+          <t xml:space="preserve">create.keep</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking this video against your device…</t>
+          <t xml:space="preserve">Keep it</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="2">
@@ -4931,17 +4931,17 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checkStopped</t>
+          <t xml:space="preserve">create.lockedMaking</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check stopped.</t>
+          <t xml:space="preserve">Locked while your video is being made.</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="2">
@@ -4963,17 +4963,17 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.stoppingSave</t>
+          <t xml:space="preserve">create.lockedSaving</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stopping the save…</t>
+          <t xml:space="preserve">Locked while your video is being saved.</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="2">
@@ -4995,7 +4995,7 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelling</t>
+          <t xml:space="preserve">status.checking</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelling…</t>
+          <t xml:space="preserve">Checking this video against your device…</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="2">
@@ -5027,7 +5027,7 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelled</t>
+          <t xml:space="preserve">status.checkStopped</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
+          <t xml:space="preserve">Check stopped.</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="2">
@@ -5059,7 +5059,7 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saving</t>
+          <t xml:space="preserve">status.stoppingSave</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving…</t>
+          <t xml:space="preserve">Stopping the save…</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="2">
@@ -5091,7 +5091,7 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveStopped</t>
+          <t xml:space="preserve">status.cancelling</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
+          <t xml:space="preserve">Cancelling…</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="2">
@@ -5123,7 +5123,7 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.notSaved</t>
+          <t xml:space="preserve">status.cancelled</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
+          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="2">
@@ -5155,7 +5155,7 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.refusedSource</t>
+          <t xml:space="preserve">status.saving</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
+          <t xml:space="preserve">Saving…</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="2">
@@ -5187,7 +5187,7 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saved</t>
+          <t xml:space="preserve">status.saveStopped</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
+          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="2">
@@ -5219,7 +5219,7 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveFailed</t>
+          <t xml:space="preserve">status.notSaved</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
+          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="2">
@@ -5251,7 +5251,7 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.storageWayOut</t>
+          <t xml:space="preserve">status.refusedSource</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
+          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5283,7 +5283,7 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.creating</t>
+          <t xml:space="preserve">status.saved</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video. {notice}</t>
+          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5315,7 +5315,7 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.ready</t>
+          <t xml:space="preserve">status.saveFailed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is ready.</t>
+          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.couldNotCreate</t>
+          <t xml:space="preserve">status.storageWayOut</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be created. {sentence}</t>
+          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5379,22 +5379,22 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.verdictSpoken</t>
+          <t xml:space="preserve">status.creating</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Device check complete. {heading}.</t>
+          <t xml:space="preserve">Creating your video. {notice}</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
+          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5411,17 +5411,17 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.title</t>
+          <t xml:space="preserve">status.ready</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet</t>
+          <t xml:space="preserve">Your video is ready.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="2">
@@ -5443,22 +5443,22 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.delivered</t>
+          <t xml:space="preserve">status.couldNotCreate</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
+          <t xml:space="preserve">The video could not be created. {sentence}</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5475,22 +5475,22 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.unsaved</t>
+          <t xml:space="preserve">status.verdictSpoken</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
+          <t xml:space="preserve">Device check complete. {heading}.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5507,22 +5507,22 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.spoken</t>
+          <t xml:space="preserve">discard.title</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet. {question}</t>
+          <t xml:space="preserve">This video is not saved yet</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5539,22 +5539,22 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.finished</t>
+          <t xml:space="preserve">discard.delivered</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finished video — {size}</t>
+          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5571,22 +5571,22 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.previous</t>
+          <t xml:space="preserve">discard.unsaved</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Previous video — {size}</t>
+          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5603,22 +5603,22 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetime</t>
+          <t xml:space="preserve">discard.spoken</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
+          <t xml:space="preserve">This video is not saved yet. {question}</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5635,7 +5635,7 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetimeDelivered</t>
+          <t xml:space="preserve">result.finished</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
+          <t xml:space="preserve">Finished video — {size}</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5667,7 +5667,7 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptWhole</t>
+          <t xml:space="preserve">result.previous</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the whole video ({duration})</t>
+          <t xml:space="preserve">Previous video — {size}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5699,7 +5699,7 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptPart</t>
+          <t xml:space="preserve">result.lifetime</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
+          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5731,7 +5731,7 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingNone</t>
+          <t xml:space="preserve">result.lifetimeDelivered</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no University closing</t>
+          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="2">
@@ -5763,7 +5763,7 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.blue</t>
+          <t xml:space="preserve">result.keptWhole</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the blue closing card</t>
+          <t xml:space="preserve">the whole video ({duration})</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -5795,7 +5795,7 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.white</t>
+          <t xml:space="preserve">result.keptPart</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the white closing card</t>
+          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -5827,7 +5827,7 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
+          <t xml:space="preserve">result.closingNone</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
+          <t xml:space="preserve">no University closing</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -5859,7 +5859,7 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
+          <t xml:space="preserve">result.closingCut.blue</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
+          <t xml:space="preserve">a cut to the blue closing card</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -5891,7 +5891,7 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
+          <t xml:space="preserve">result.closingCut.white</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over a held last frame</t>
+          <t xml:space="preserve">a cut to the white closing card</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -5923,7 +5923,7 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
+          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -5955,7 +5955,7 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over the picture</t>
+          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -5987,7 +5987,7 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over the picture</t>
+          <t xml:space="preserve">the white closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6019,7 +6019,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over the picture</t>
+          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over the picture</t>
+          <t xml:space="preserve">the blue closing fading in over the picture</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6083,7 +6083,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summary</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">the blue closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6115,7 +6115,7 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">the white closing fading in over the picture</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6147,7 +6147,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">the white closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6179,7 +6179,7 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.summary</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6243,7 +6243,7 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6275,7 +6275,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6307,7 +6307,7 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6339,7 +6339,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6371,7 +6371,7 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6403,7 +6403,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6435,7 +6435,7 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6467,7 +6467,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6499,7 +6499,7 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6531,22 +6531,22 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6563,22 +6563,22 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6595,22 +6595,22 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6627,7 +6627,7 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="2">
@@ -6659,7 +6659,7 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
@@ -6691,7 +6691,7 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6723,7 +6723,7 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6755,7 +6755,7 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -6787,7 +6787,7 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -6819,7 +6819,7 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -6851,7 +6851,7 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -6883,22 +6883,22 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -6915,22 +6915,22 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -6947,22 +6947,22 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -6979,7 +6979,7 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7011,22 +7011,22 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: said when the video starts being made</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7043,22 +7043,22 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7075,22 +7075,22 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7107,22 +7107,22 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">Step 5: said when the video starts being made</t>
         </is>
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,7 +7203,7 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7299,7 +7299,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,7 +7331,7 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,17 +7395,17 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
@@ -7427,17 +7427,17 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
@@ -7459,22 +7459,22 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,22 +7491,22 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7523,22 +7523,22 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7555,7 +7555,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
@@ -7587,7 +7587,7 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7619,7 +7619,7 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
@@ -7651,7 +7651,7 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,7 +7683,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,7 +7715,7 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7747,7 +7747,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -7811,7 +7811,7 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
@@ -7843,7 +7843,7 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -7971,7 +7971,7 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
@@ -8003,7 +8003,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8035,22 +8035,22 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8067,17 +8067,17 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
@@ -8099,22 +8099,22 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8195,22 +8195,22 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,17 +8227,17 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
@@ -8259,22 +8259,22 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8291,22 +8291,22 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8323,7 +8323,7 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
@@ -8355,7 +8355,7 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
@@ -8387,22 +8387,22 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8419,7 +8419,7 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
@@ -8451,7 +8451,7 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
@@ -8483,7 +8483,7 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
@@ -8515,7 +8515,7 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
@@ -8643,7 +8643,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8707,7 +8707,7 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
@@ -8771,7 +8771,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -8803,7 +8803,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
@@ -8835,22 +8835,22 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -8867,22 +8867,22 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -8899,22 +8899,22 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -8931,7 +8931,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -8963,7 +8963,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -8995,7 +8995,7 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9027,22 +9027,22 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9059,22 +9059,22 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9091,22 +9091,22 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,7 +9123,7 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
@@ -9155,7 +9155,7 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
@@ -9187,7 +9187,7 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
@@ -9219,7 +9219,7 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
@@ -9251,7 +9251,7 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
@@ -9283,7 +9283,7 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
@@ -9315,7 +9315,7 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
@@ -9347,7 +9347,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
@@ -9379,7 +9379,7 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
@@ -9411,7 +9411,7 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
@@ -9795,17 +9795,17 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
@@ -9827,22 +9827,22 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -9859,22 +9859,22 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -9955,22 +9955,22 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,22 +9987,22 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10019,22 +10019,22 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10051,22 +10051,22 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10083,7 +10083,7 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10115,7 +10115,7 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10147,7 +10147,7 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10179,7 +10179,7 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10211,7 +10211,7 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10243,7 +10243,7 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10275,7 +10275,7 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10307,7 +10307,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10339,7 +10339,7 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10371,7 +10371,7 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10403,7 +10403,7 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10435,7 +10435,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
@@ -10467,7 +10467,7 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
@@ -10499,7 +10499,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
@@ -10563,7 +10563,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
@@ -10595,7 +10595,7 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
@@ -10627,7 +10627,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
@@ -10819,17 +10819,17 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,22 +10851,22 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -10883,17 +10883,17 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,17 +10915,17 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,17 +10947,17 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
@@ -10979,22 +10979,22 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11011,7 +11011,7 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,7 +11043,7 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
@@ -11075,7 +11075,7 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11107,7 +11107,7 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
@@ -11139,7 +11139,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
@@ -11171,7 +11171,7 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
@@ -11203,7 +11203,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
@@ -11235,7 +11235,7 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11267,7 +11267,7 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11299,7 +11299,7 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
@@ -11331,7 +11331,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
@@ -11363,7 +11363,7 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
@@ -11427,22 +11427,22 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11459,22 +11459,22 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11491,22 +11491,22 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11523,22 +11523,22 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">save.pickerDescription</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
         </is>
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11555,7 +11555,7 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">save.stem</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">video</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,7 +11587,7 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">save.marks.branded</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11597,12 +11597,12 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">branded</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11619,22 +11619,22 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">save.marks.levelled</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">levelled</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11651,22 +11651,22 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">save.marks.converted</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">converted</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11683,22 +11683,22 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">save.fileName</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,22 +11715,22 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">save.downloadIos</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,17 +11747,17 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">save.downloadOther</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">Saving to your downloads folder</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
@@ -11779,22 +11779,22 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">save.download</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,7 +11811,7 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">format.unknown</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,7 +11843,7 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">format.lessThanASecond</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">less than a second</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -11875,7 +11875,7 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">format.fewSeconds</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">a few seconds</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
@@ -11907,7 +11907,7 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">format.frameRate</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">{rate} frames a second</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,7 +11939,7 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">format.resolution</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">{width} × {height}</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,7 +11971,7 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">format.channels.mono</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">Mono (one channel)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
@@ -12003,30 +12003,126 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">format.channels.stereo</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Stereo (two channels)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr" s="2">
+      <c r="B377" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr" s="2">
+      <c r="C377" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr" s="2">
+      <c r="D377" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr" s="2">
+      <c r="E377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -11523,22 +11523,22 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11555,22 +11555,22 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,22 +11587,22 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11619,22 +11619,22 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11651,22 +11651,22 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11683,22 +11683,22 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,22 +11715,22 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,22 +11747,22 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11779,22 +11779,22 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,22 +11811,22 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,22 +11843,22 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -11875,22 +11875,22 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -11907,22 +11907,22 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,22 +11939,22 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,17 +11971,17 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
@@ -12003,22 +12003,22 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,17 +12035,17 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
@@ -12067,22 +12067,22 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12099,30 +12099,1310 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">statement.enforcement.heading</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Enforcement procedure</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.enforcement.text</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.enforcement.service</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.compliance.heading</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Compliance status</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.compliance.text</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.testing.heading</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">How we tested this tool</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.testing.wave</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.testing.automated</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.testing.manual</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.heading</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">What we plan to test next</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.intro</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.0</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.1</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.2</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.3</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Windows contrast themes</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.4</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.plans.items.5</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.about.heading</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">About this statement</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">statement.about.dates</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">footer.contact.intro</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">For help with this tool:</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">footer.contact.creators</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Email the creators team</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">footer.contact.learningContent</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Email the learning content team</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.pickerDescription</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.stem</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">video</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.branded</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">branded</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.levelled</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">levelled</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.converted</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">converted</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.fileName</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.downloadIos</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.downloadOther</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Saving to your downloads folder</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.download</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.unknown</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.lessThanASecond</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">less than a second</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.fewSeconds</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">a few seconds</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.frameRate</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{rate} frames a second</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.resolution</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{width} × {height}</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.mono</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Mono (one channel)</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.stereo</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Stereo (two channels)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr" s="2">
+      <c r="B417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr" s="2">
+      <c r="C417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr" s="2">
+      <c r="D417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr" s="2">
+      <c r="E417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -3843,7 +3843,7 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.cut</t>
+          <t xml:space="preserve">closing.internalLabel</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with Cut.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
+          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -3875,22 +3875,22 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.none</t>
+          <t xml:space="preserve">closing.internalWords</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with None.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
+          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -3907,22 +3907,22 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.none</t>
+          <t xml:space="preserve">closing.notUsedWith.cut</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No University closing will be added.</t>
+          <t xml:space="preserve">Not used with Cut.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -3939,22 +3939,22 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.one</t>
+          <t xml:space="preserve">closing.notUsedWith.none</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} second.</t>
+          <t xml:space="preserve">Not used with None.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -3971,7 +3971,7 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.other</t>
+          <t xml:space="preserve">closing.result.none</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} seconds.</t>
+          <t xml:space="preserve">No University closing will be added.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4003,7 +4003,7 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.blue</t>
+          <t xml:space="preserve">closing.result.adds.one</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
+          <t xml:space="preserve">Adds {count} second.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4035,7 +4035,7 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.white</t>
+          <t xml:space="preserve">closing.result.adds.other</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
+          <t xml:space="preserve">Adds {count} seconds.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4067,7 +4067,7 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
+          <t xml:space="preserve">closing.result.internal</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">The card says “{words}” under the logo.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4099,7 +4099,7 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
+          <t xml:space="preserve">closing.result.cut.blue</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4131,7 +4131,7 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
+          <t xml:space="preserve">closing.result.cut.white</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4163,7 +4163,7 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4195,7 +4195,7 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4227,7 +4227,7 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4259,7 +4259,7 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4291,7 +4291,7 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4323,22 +4323,22 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.legend</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4355,22 +4355,22 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.best</t>
+          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larger / better</t>
+          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4387,22 +4387,22 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.smaller</t>
+          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Smaller / reduced</t>
+          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4419,7 +4419,7 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.best</t>
+          <t xml:space="preserve">preset.legend</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="2">
@@ -4451,7 +4451,7 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.smaller</t>
+          <t xml:space="preserve">preset.labels.best</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For messaging or email etc.</t>
+          <t xml:space="preserve">Larger / better</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4483,22 +4483,22 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.note</t>
+          <t xml:space="preserve">preset.labels.smaller</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
+          <t xml:space="preserve">Smaller / reduced</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4515,17 +4515,17 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceProgress</t>
+          <t xml:space="preserve">preset.details.best</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Announce progress</t>
+          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="2">
@@ -4547,17 +4547,17 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceHelp</t>
+          <t xml:space="preserve">preset.details.smaller</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
+          <t xml:space="preserve">For messaging or email etc.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="2">
@@ -4579,7 +4579,7 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.progressLabel</t>
+          <t xml:space="preserve">create.note</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video</t>
+          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="2">
@@ -4611,7 +4611,7 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.create</t>
+          <t xml:space="preserve">create.announceProgress</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create the video</t>
+          <t xml:space="preserve">Announce progress</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="2">
@@ -4643,7 +4643,7 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.cancel</t>
+          <t xml:space="preserve">create.announceHelp</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="2">
@@ -4675,7 +4675,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.continueAnyway</t>
+          <t xml:space="preserve">create.progressLabel</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Continue anyway</t>
+          <t xml:space="preserve">Creating your video</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="2">
@@ -4707,7 +4707,7 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopCheck</t>
+          <t xml:space="preserve">create.create</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop the check</t>
+          <t xml:space="preserve">Create the video</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="2">
@@ -4739,7 +4739,7 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.checkAgain</t>
+          <t xml:space="preserve">create.cancel</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check again</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="2">
@@ -4771,7 +4771,7 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopSaving</t>
+          <t xml:space="preserve">create.continueAnyway</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop saving</t>
+          <t xml:space="preserve">Continue anyway</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="2">
@@ -4803,7 +4803,7 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.save</t>
+          <t xml:space="preserve">create.stopCheck</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save the video</t>
+          <t xml:space="preserve">Stop the check</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="2">
@@ -4835,7 +4835,7 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.saved</t>
+          <t xml:space="preserve">create.checkAgain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved</t>
+          <t xml:space="preserve">Check again</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="2">
@@ -4867,7 +4867,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.discard</t>
+          <t xml:space="preserve">create.stopSaving</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Discard it and start again</t>
+          <t xml:space="preserve">Stop saving</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="2">
@@ -4899,7 +4899,7 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.keep</t>
+          <t xml:space="preserve">create.save</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep it</t>
+          <t xml:space="preserve">Save the video</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="2">
@@ -4931,7 +4931,7 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedMaking</t>
+          <t xml:space="preserve">create.saved</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being made.</t>
+          <t xml:space="preserve">Saved</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="2">
@@ -4963,7 +4963,7 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedSaving</t>
+          <t xml:space="preserve">create.discard</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being saved.</t>
+          <t xml:space="preserve">Discard it and start again</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="2">
@@ -4995,17 +4995,17 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checking</t>
+          <t xml:space="preserve">create.keep</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking this video against your device…</t>
+          <t xml:space="preserve">Keep it</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="2">
@@ -5027,17 +5027,17 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checkStopped</t>
+          <t xml:space="preserve">create.lockedMaking</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check stopped.</t>
+          <t xml:space="preserve">Locked while your video is being made.</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="2">
@@ -5059,17 +5059,17 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.stoppingSave</t>
+          <t xml:space="preserve">create.lockedSaving</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stopping the save…</t>
+          <t xml:space="preserve">Locked while your video is being saved.</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="2">
@@ -5091,7 +5091,7 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelling</t>
+          <t xml:space="preserve">status.checking</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelling…</t>
+          <t xml:space="preserve">Checking this video against your device…</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="2">
@@ -5123,7 +5123,7 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelled</t>
+          <t xml:space="preserve">status.checkStopped</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
+          <t xml:space="preserve">Check stopped.</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="2">
@@ -5155,7 +5155,7 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saving</t>
+          <t xml:space="preserve">status.stoppingSave</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving…</t>
+          <t xml:space="preserve">Stopping the save…</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="2">
@@ -5187,7 +5187,7 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveStopped</t>
+          <t xml:space="preserve">status.cancelling</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
+          <t xml:space="preserve">Cancelling…</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="2">
@@ -5219,7 +5219,7 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.notSaved</t>
+          <t xml:space="preserve">status.cancelled</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
+          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="2">
@@ -5251,7 +5251,7 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.refusedSource</t>
+          <t xml:space="preserve">status.saving</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
+          <t xml:space="preserve">Saving…</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="2">
@@ -5283,7 +5283,7 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saved</t>
+          <t xml:space="preserve">status.saveStopped</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
+          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="2">
@@ -5315,7 +5315,7 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveFailed</t>
+          <t xml:space="preserve">status.notSaved</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
+          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.storageWayOut</t>
+          <t xml:space="preserve">status.refusedSource</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
+          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5379,7 +5379,7 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.creating</t>
+          <t xml:space="preserve">status.saved</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video. {notice}</t>
+          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5411,7 +5411,7 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.ready</t>
+          <t xml:space="preserve">status.saveFailed</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is ready.</t>
+          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="2">
@@ -5443,7 +5443,7 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.couldNotCreate</t>
+          <t xml:space="preserve">status.storageWayOut</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be created. {sentence}</t>
+          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5475,22 +5475,22 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.verdictSpoken</t>
+          <t xml:space="preserve">status.creating</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Device check complete. {heading}.</t>
+          <t xml:space="preserve">Creating your video. {notice}</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
+          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5507,17 +5507,17 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.title</t>
+          <t xml:space="preserve">status.ready</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet</t>
+          <t xml:space="preserve">Your video is ready.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="2">
@@ -5539,22 +5539,22 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.delivered</t>
+          <t xml:space="preserve">status.couldNotCreate</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
+          <t xml:space="preserve">The video could not be created. {sentence}</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5571,22 +5571,22 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.unsaved</t>
+          <t xml:space="preserve">status.verdictSpoken</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
+          <t xml:space="preserve">Device check complete. {heading}.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5603,22 +5603,22 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.spoken</t>
+          <t xml:space="preserve">discard.title</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet. {question}</t>
+          <t xml:space="preserve">This video is not saved yet</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5635,22 +5635,22 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.finished</t>
+          <t xml:space="preserve">discard.delivered</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finished video — {size}</t>
+          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5667,22 +5667,22 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.previous</t>
+          <t xml:space="preserve">discard.unsaved</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Previous video — {size}</t>
+          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5699,22 +5699,22 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetime</t>
+          <t xml:space="preserve">discard.spoken</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
+          <t xml:space="preserve">This video is not saved yet. {question}</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5731,7 +5731,7 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetimeDelivered</t>
+          <t xml:space="preserve">result.finished</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
+          <t xml:space="preserve">Finished video — {size}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5763,7 +5763,7 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptWhole</t>
+          <t xml:space="preserve">result.previous</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the whole video ({duration})</t>
+          <t xml:space="preserve">Previous video — {size}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -5795,7 +5795,7 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptPart</t>
+          <t xml:space="preserve">result.lifetime</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
+          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -5827,7 +5827,7 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingNone</t>
+          <t xml:space="preserve">result.lifetimeDelivered</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no University closing</t>
+          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="2">
@@ -5859,7 +5859,7 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.blue</t>
+          <t xml:space="preserve">result.keptWhole</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the blue closing card</t>
+          <t xml:space="preserve">the whole video ({duration})</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -5891,7 +5891,7 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.white</t>
+          <t xml:space="preserve">result.keptPart</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the white closing card</t>
+          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -5923,7 +5923,7 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
+          <t xml:space="preserve">result.closingNone</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
+          <t xml:space="preserve">no University closing</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -5955,7 +5955,7 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
+          <t xml:space="preserve">result.closingInternal</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
+          <t xml:space="preserve">{closing}, marked “{words}”</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -5987,7 +5987,7 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
+          <t xml:space="preserve">result.closingCut.blue</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over a held last frame</t>
+          <t xml:space="preserve">a cut to the blue closing card</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6019,7 +6019,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
+          <t xml:space="preserve">result.closingCut.white</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
+          <t xml:space="preserve">a cut to the white closing card</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over the picture</t>
+          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
@@ -6083,7 +6083,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over the picture</t>
+          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
@@ -6115,7 +6115,7 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over the picture</t>
+          <t xml:space="preserve">the white closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
@@ -6147,7 +6147,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over the picture</t>
+          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
@@ -6179,7 +6179,7 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summary</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">the blue closing fading in over the picture</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">the blue closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6243,7 +6243,7 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">the white closing fading in over the picture</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6275,7 +6275,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">the white closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6307,7 +6307,7 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.summary</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6339,7 +6339,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6371,7 +6371,7 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
@@ -6403,7 +6403,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
@@ -6435,7 +6435,7 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
@@ -6467,7 +6467,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
@@ -6499,7 +6499,7 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="2">
@@ -6531,7 +6531,7 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="2">
@@ -6563,7 +6563,7 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="2">
@@ -6595,7 +6595,7 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="2">
@@ -6627,22 +6627,22 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6659,22 +6659,22 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6691,22 +6691,22 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6723,22 +6723,22 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6755,7 +6755,7 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="2">
@@ -6787,7 +6787,7 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -6819,7 +6819,7 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -6851,7 +6851,7 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -6883,7 +6883,7 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -6915,7 +6915,7 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -6947,7 +6947,7 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -6979,22 +6979,22 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7011,22 +7011,22 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7043,22 +7043,22 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7075,22 +7075,22 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7107,22 +7107,22 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: said when the video starts being made</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,22 +7139,22 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,22 +7171,22 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,22 +7235,22 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">Step 5: said when the video starts being made</t>
         </is>
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7299,7 +7299,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,7 +7331,7 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,7 +7395,7 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7459,7 +7459,7 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,22 +7491,22 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7523,17 +7523,17 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
@@ -7555,22 +7555,22 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7587,22 +7587,22 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7619,22 +7619,22 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7651,22 +7651,22 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,7 +7683,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,7 +7715,7 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
@@ -7747,7 +7747,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
@@ -7811,7 +7811,7 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
@@ -7843,7 +7843,7 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -7971,7 +7971,7 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8003,7 +8003,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
@@ -8131,17 +8131,17 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
@@ -8163,17 +8163,17 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
@@ -8195,22 +8195,22 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,17 +8227,17 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
@@ -8259,7 +8259,7 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8291,17 +8291,17 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
@@ -8323,22 +8323,22 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8355,17 +8355,17 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
@@ -8387,22 +8387,22 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8419,7 +8419,7 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
@@ -8451,7 +8451,7 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
@@ -8483,7 +8483,7 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
@@ -8515,22 +8515,22 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
@@ -8643,7 +8643,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
@@ -8707,7 +8707,7 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
@@ -8771,7 +8771,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -8803,7 +8803,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
@@ -8835,7 +8835,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
@@ -8867,7 +8867,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
@@ -8899,7 +8899,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -8931,22 +8931,22 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -8963,22 +8963,22 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -8995,22 +8995,22 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9027,22 +9027,22 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9059,7 +9059,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9091,7 +9091,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,22 +9123,22 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9155,22 +9155,22 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9187,22 +9187,22 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9219,22 +9219,22 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9251,7 +9251,7 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
@@ -9283,7 +9283,7 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
@@ -9315,7 +9315,7 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
@@ -9347,7 +9347,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
@@ -9379,7 +9379,7 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
@@ -9411,7 +9411,7 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
@@ -9891,17 +9891,17 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
@@ -9923,22 +9923,22 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -9955,22 +9955,22 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,22 +9987,22 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10019,7 +10019,7 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
@@ -10051,22 +10051,22 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10083,22 +10083,22 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10115,22 +10115,22 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10147,22 +10147,22 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10179,22 +10179,22 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10211,7 +10211,7 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10243,7 +10243,7 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10275,7 +10275,7 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10307,7 +10307,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10339,7 +10339,7 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10371,7 +10371,7 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10403,7 +10403,7 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10435,7 +10435,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10467,7 +10467,7 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10499,7 +10499,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10563,7 +10563,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
@@ -10595,7 +10595,7 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
@@ -10627,7 +10627,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
@@ -10819,7 +10819,7 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,7 +10851,7 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -10883,7 +10883,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,17 +10915,17 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,17 +10947,17 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
@@ -10979,22 +10979,22 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11011,17 +11011,17 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,17 +11043,17 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
@@ -11075,22 +11075,22 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11107,17 +11107,17 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
@@ -11139,7 +11139,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
@@ -11171,7 +11171,7 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
@@ -11203,7 +11203,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11235,7 +11235,7 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
@@ -11267,7 +11267,7 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
@@ -11299,7 +11299,7 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
@@ -11331,7 +11331,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11363,7 +11363,7 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
@@ -11427,7 +11427,7 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11459,7 +11459,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11491,7 +11491,7 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11523,22 +11523,22 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11555,22 +11555,22 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,22 +11587,22 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11619,22 +11619,22 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11651,22 +11651,22 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11683,22 +11683,22 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,22 +11715,22 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,7 +11747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
@@ -11779,22 +11779,22 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,22 +11811,22 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,22 +11843,22 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -11875,22 +11875,22 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -11907,22 +11907,22 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,17 +11939,17 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
@@ -11971,22 +11971,22 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12003,7 +12003,7 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,22 +12035,22 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12067,22 +12067,22 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12099,17 +12099,17 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
@@ -12131,22 +12131,22 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12163,22 +12163,22 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Equality Advisory and Support Service</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12195,22 +12195,22 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.heading</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance status</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12227,22 +12227,22 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.text</t>
+          <t xml:space="preserve">statement.enforcement.heading</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+          <t xml:space="preserve">Enforcement procedure</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12259,22 +12259,22 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.heading</t>
+          <t xml:space="preserve">statement.enforcement.text</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How we tested this tool</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12291,7 +12291,7 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.wave</t>
+          <t xml:space="preserve">statement.enforcement.service</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12323,17 +12323,17 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.automated</t>
+          <t xml:space="preserve">statement.compliance.heading</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+          <t xml:space="preserve">Compliance status</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
@@ -12355,7 +12355,7 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.manual</t>
+          <t xml:space="preserve">statement.compliance.text</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12387,7 +12387,7 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.heading</t>
+          <t xml:space="preserve">statement.testing.heading</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What we plan to test next</t>
+          <t xml:space="preserve">How we tested this tool</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
@@ -12419,7 +12419,7 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.intro</t>
+          <t xml:space="preserve">statement.testing.wave</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12451,22 +12451,22 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.0</t>
+          <t xml:space="preserve">statement.testing.automated</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using the tool with a keyboard alone</t>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,22 +12483,22 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.1</t>
+          <t xml:space="preserve">statement.testing.manual</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12515,22 +12515,22 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.2</t>
+          <t xml:space="preserve">statement.plans.heading</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+          <t xml:space="preserve">What we plan to test next</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12547,22 +12547,22 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.3</t>
+          <t xml:space="preserve">statement.plans.intro</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Windows contrast themes</t>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12579,7 +12579,7 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.4</t>
+          <t xml:space="preserve">statement.plans.items.0</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12589,12 +12589,12 @@
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12611,7 +12611,7 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.5</t>
+          <t xml:space="preserve">statement.plans.items.1</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12621,12 +12621,12 @@
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12643,22 +12643,22 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.heading</t>
+          <t xml:space="preserve">statement.plans.items.2</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About this statement</t>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12675,22 +12675,22 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.dates</t>
+          <t xml:space="preserve">statement.plans.items.3</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+          <t xml:space="preserve">Windows contrast themes</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12707,22 +12707,22 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.intro</t>
+          <t xml:space="preserve">statement.plans.items.4</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For help with this tool:</t>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12739,22 +12739,22 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.creators</t>
+          <t xml:space="preserve">statement.plans.items.5</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the creators team</t>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -12771,22 +12771,22 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.learningContent</t>
+          <t xml:space="preserve">statement.about.heading</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the learning content team</t>
+          <t xml:space="preserve">About this statement</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -12803,22 +12803,22 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">statement.about.dates</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -12835,22 +12835,22 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">footer.contact.intro</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
         </is>
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">For help with this tool:</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -12867,22 +12867,22 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">footer.contact.creators</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
         </is>
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">Email the creators team</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,22 +12899,22 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">footer.contact.learningContent</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
         </is>
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">Email the learning content team</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -12931,22 +12931,22 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">save.pickerDescription</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
         </is>
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,7 +12963,7 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">save.stem</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">video</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,22 +12995,22 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">save.marks.branded</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">branded</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13027,22 +13027,22 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">save.marks.levelled</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">levelled</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,22 +13059,22 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">save.marks.converted</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">converted</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13091,22 +13091,22 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">save.fileName</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13123,17 +13123,17 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">save.downloadIos</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
@@ -13155,17 +13155,17 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">save.downloadOther</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">Saving to your downloads folder</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
@@ -13187,22 +13187,22 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">save.download</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,7 +13219,7 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">format.unknown</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,7 +13251,7 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">format.lessThanASecond</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">less than a second</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
@@ -13283,7 +13283,7 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">format.fewSeconds</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">a few seconds</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
@@ -13315,7 +13315,7 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">format.frameRate</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13325,12 +13325,12 @@
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">{rate} frames a second</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,7 +13347,7 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">format.resolution</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">{width} × {height}</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,30 +13379,158 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">format.channels.mono</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Mono (one channel)</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.stereo</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Stereo (two channels)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr" s="2">
+      <c r="B421" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr" s="2">
+      <c r="C421" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr" s="2">
+      <c r="D421" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr" s="2">
+      <c r="E421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -611,22 +611,22 @@
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.choose</t>
+          <t xml:space="preserve">videoKind.label</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the switch between a staff video and a student submission</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a video</t>
+          <t xml:space="preserve">Video type</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The label over the switch, also read out by screen readers.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -643,17 +643,17 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.trim</t>
+          <t xml:space="preserve">videoKind.options.staff</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the switch between a staff video and a student submission</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Trim</t>
+          <t xml:space="preserve">Staff video</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -675,17 +675,17 @@
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.closing</t>
+          <t xml:space="preserve">videoKind.options.submission</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the switch between a staff video and a student submission</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">Student submission</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -707,22 +707,22 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.preset</t>
+          <t xml:space="preserve">videoKind.result.staff</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the line under the switch, saying what the choice means for the closing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">You choose the closing, and whether it says “{words}”.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -739,22 +739,22 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.create</t>
+          <t xml:space="preserve">videoKind.result.submission</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the line under the switch, saying what the choice means for the closing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create</t>
+          <t xml:space="preserve">If the video has a closing, it says “{words}”.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -771,17 +771,17 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHint</t>
+          <t xml:space="preserve">steps.choose</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Or drop it here.</t>
+          <t xml:space="preserve">Choose a video</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -803,17 +803,17 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHeld</t>
+          <t xml:space="preserve">steps.trim</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Let go to read this video.</t>
+          <t xml:space="preserve">Trim</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -835,17 +835,17 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.reading</t>
+          <t xml:space="preserve">steps.closing</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -867,17 +867,17 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.making</t>
+          <t xml:space="preserve">steps.preset</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -899,17 +899,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.saving</t>
+          <t xml:space="preserve">steps.create</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">Create</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -931,17 +931,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.starting</t>
+          <t xml:space="preserve">choose.dropHint</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
+          <t xml:space="preserve">Or drop it here.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -963,17 +963,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.unavailable</t>
+          <t xml:space="preserve">choose.dropHeld</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
+          <t xml:space="preserve">Let go to read this video.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -995,17 +995,17 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.nothing</t>
+          <t xml:space="preserve">choose.reading</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -1027,7 +1027,7 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.several</t>
+          <t xml:space="preserve">choose.drop.making</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
+          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1059,7 +1059,7 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.notVideo</t>
+          <t xml:space="preserve">choose.drop.saving</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
+          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -1091,22 +1091,22 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.readSummary</t>
+          <t xml:space="preserve">choose.drop.starting</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video read. {facts}.</t>
+          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1123,17 +1123,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variableFrameRate</t>
+          <t xml:space="preserve">choose.drop.unavailable</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">variable frame rate</t>
+          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
@@ -1155,17 +1155,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSound</t>
+          <t xml:space="preserve">choose.drop.nothing</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no sound</t>
+          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -1187,22 +1187,22 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.properties</t>
+          <t xml:space="preserve">choose.drop.several</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video properties</t>
+          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1219,17 +1219,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.lossesTitle</t>
+          <t xml:space="preserve">choose.drop.notVideo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not carried into the new file</t>
+          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
@@ -1251,22 +1251,22 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.duration</t>
+          <t xml:space="preserve">source.readSummary</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t xml:space="preserve">Video read. {facts}.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1283,17 +1283,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.videoFormat</t>
+          <t xml:space="preserve">source.variableFrameRate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format</t>
+          <t xml:space="preserve">variable frame rate</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -1315,17 +1315,17 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileSize</t>
+          <t xml:space="preserve">source.noSound</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size</t>
+          <t xml:space="preserve">no sound</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
@@ -1347,17 +1347,17 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.resolution</t>
+          <t xml:space="preserve">source.properties</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Resolution</t>
+          <t xml:space="preserve">Video properties</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
@@ -1379,17 +1379,17 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.frameRate</t>
+          <t xml:space="preserve">source.lossesTitle</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Frame rate</t>
+          <t xml:space="preserve">Not carried into the new file</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -1411,7 +1411,7 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundFormat</t>
+          <t xml:space="preserve">source.rows.duration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format</t>
+          <t xml:space="preserve">Duration</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -1443,7 +1443,7 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundChannels</t>
+          <t xml:space="preserve">source.rows.videoFormat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound channels</t>
+          <t xml:space="preserve">Video format</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -1475,7 +1475,7 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sampleRate</t>
+          <t xml:space="preserve">source.rows.fileSize</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound sample rate</t>
+          <t xml:space="preserve">File size</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -1507,7 +1507,7 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sound</t>
+          <t xml:space="preserve">source.rows.resolution</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound</t>
+          <t xml:space="preserve">Resolution</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -1539,7 +1539,7 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.captions</t>
+          <t xml:space="preserve">source.rows.frameRate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Captions</t>
+          <t xml:space="preserve">Frame rate</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -1571,7 +1571,7 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileType</t>
+          <t xml:space="preserve">source.rows.soundFormat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File type</t>
+          <t xml:space="preserve">Sound format</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -1603,17 +1603,17 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeVideo</t>
+          <t xml:space="preserve">source.rows.soundChannels</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this video format.</t>
+          <t xml:space="preserve">Sound channels</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
@@ -1635,17 +1635,17 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeAudio</t>
+          <t xml:space="preserve">source.rows.sampleRate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this audio format.</t>
+          <t xml:space="preserve">Sound sample rate</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -1667,22 +1667,22 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rotated</t>
+          <t xml:space="preserve">source.rows.sound</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
+          <t xml:space="preserve">Sound</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1699,22 +1699,22 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesOnAverage</t>
+          <t xml:space="preserve">source.rows.captions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} on average, but it varies</t>
+          <t xml:space="preserve">Captions</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1731,17 +1731,17 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesNote</t>
+          <t xml:space="preserve">source.rows.fileType</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
+          <t xml:space="preserve">File type</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="2">
@@ -1763,7 +1763,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.outputRate</t>
+          <t xml:space="preserve">source.cannotDecodeVideo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
+          <t xml:space="preserve">This browser cannot read this video format.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -1795,7 +1795,7 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.sampleRate</t>
+          <t xml:space="preserve">source.cannotDecodeAudio</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
+          <t xml:space="preserve">This browser cannot read this audio format.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -1827,7 +1827,7 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundTrack</t>
+          <t xml:space="preserve">source.rotated</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No sound track found</t>
+          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -1859,7 +1859,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundNote</t>
+          <t xml:space="preserve">source.variesOnAverage</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
+          <t xml:space="preserve">{rate} on average, but it varies</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -1891,7 +1891,7 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsUnchecked</t>
+          <t xml:space="preserve">source.variesNote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not be checked in this kind of file</t>
+          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -1923,7 +1923,7 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsFound</t>
+          <t xml:space="preserve">source.outputRate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Found {found}</t>
+          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -1955,7 +1955,7 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsNone</t>
+          <t xml:space="preserve">source.sampleRate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None found in this file</t>
+          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -1987,7 +1987,7 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.one</t>
+          <t xml:space="preserve">source.noSoundTrack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption track</t>
+          <t xml:space="preserve">No sound track found</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2019,7 +2019,7 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.other</t>
+          <t xml:space="preserve">source.noSoundNote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption tracks</t>
+          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2051,7 +2051,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.one</t>
+          <t xml:space="preserve">source.captionsUnchecked</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter track</t>
+          <t xml:space="preserve">Could not be checked in this kind of file</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2083,7 +2083,7 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.other</t>
+          <t xml:space="preserve">source.captionsFound</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter tracks</t>
+          <t xml:space="preserve">Found {found}</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2115,7 +2115,7 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.one</t>
+          <t xml:space="preserve">source.captionsNone</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video track</t>
+          <t xml:space="preserve">None found in this file</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2147,7 +2147,7 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.other</t>
+          <t xml:space="preserve">source.captionTracks.one</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video tracks</t>
+          <t xml:space="preserve">{count} caption track</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2179,7 +2179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.one</t>
+          <t xml:space="preserve">source.captionTracks.other</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound track</t>
+          <t xml:space="preserve">{count} caption tracks</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2211,7 +2211,7 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.other</t>
+          <t xml:space="preserve">source.chapterTracks.one</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound tracks</t>
+          <t xml:space="preserve">{count} chapter track</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2243,22 +2243,22 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksTitle</t>
+          <t xml:space="preserve">source.chapterTracks.other</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has {found}</t>
+          <t xml:space="preserve">{count} chapter tracks</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2275,22 +2275,22 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksDetail</t>
+          <t xml:space="preserve">source.moreVideoTracks.one</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
+          <t xml:space="preserve">{count} more video track</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2307,22 +2307,22 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedTitle</t>
+          <t xml:space="preserve">source.moreVideoTracks.other</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
+          <t xml:space="preserve">{count} more video tracks</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2339,22 +2339,22 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedDetail</t>
+          <t xml:space="preserve">source.moreSoundTracks.one</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
+          <t xml:space="preserve">{count} more sound track</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2371,22 +2371,22 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.captionsConsequence</t>
+          <t xml:space="preserve">source.moreSoundTracks.other</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
+          <t xml:space="preserve">{count} more sound tracks</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2403,7 +2403,7 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.chaptersConsequence</t>
+          <t xml:space="preserve">source.losses.extraTracksTitle</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The chapters will not be in the new file.</t>
+          <t xml:space="preserve">This file has {found}</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2435,7 +2435,7 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.keepOriginals</t>
+          <t xml:space="preserve">source.losses.extraTracksDetail</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
+          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="2">
@@ -2467,17 +2467,17 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.intro</t>
+          <t xml:space="preserve">source.losses.uncheckedTitle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
+          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="2">
@@ -2499,17 +2499,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.noPreview</t>
+          <t xml:space="preserve">source.losses.uncheckedDetail</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
+          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="2">
@@ -2531,17 +2531,17 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.start</t>
+          <t xml:space="preserve">source.losses.captionsConsequence</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start</t>
+          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="2">
@@ -2563,17 +2563,17 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.end</t>
+          <t xml:space="preserve">source.losses.chaptersConsequence</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End</t>
+          <t xml:space="preserve">The chapters will not be in the new file.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="2">
@@ -2595,17 +2595,17 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.startTime</t>
+          <t xml:space="preserve">source.losses.keepOriginals</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start time</t>
+          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="2">
@@ -2627,7 +2627,7 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.endTime</t>
+          <t xml:space="preserve">trim.intro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End time</t>
+          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="2">
@@ -2659,7 +2659,7 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setStart</t>
+          <t xml:space="preserve">trim.noPreview</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set start here</t>
+          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="2">
@@ -2691,7 +2691,7 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setEnd</t>
+          <t xml:space="preserve">trim.start</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set end here</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="2">
@@ -2723,7 +2723,7 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.format</t>
+          <t xml:space="preserve">trim.end</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
+          <t xml:space="preserve">End</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2755,7 +2755,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.useWhole</t>
+          <t xml:space="preserve">trim.startTime</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the whole video</t>
+          <t xml:space="preserve">Start time</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="2">
@@ -2787,7 +2787,7 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.reading</t>
+          <t xml:space="preserve">trim.endTime</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">End time</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="2">
@@ -2819,7 +2819,7 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.unreadable</t>
+          <t xml:space="preserve">trim.setStart</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
+          <t xml:space="preserve">Set start here</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="2">
@@ -2851,7 +2851,7 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.tooShort</t>
+          <t xml:space="preserve">trim.setEnd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
+          <t xml:space="preserve">Set end here</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -2883,7 +2883,7 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keepingWhole</t>
+          <t xml:space="preserve">trim.format</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
+          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -2915,7 +2915,7 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keeping</t>
+          <t xml:space="preserve">trim.useWhole</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
+          <t xml:space="preserve">Use the whole video</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -2947,7 +2947,7 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleBeginning</t>
+          <t xml:space="preserve">trim.reading</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the beginning</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -2979,7 +2979,7 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleEnd</t>
+          <t xml:space="preserve">trim.unreadable</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the end</t>
+          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3011,22 +3011,22 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.start</t>
+          <t xml:space="preserve">trim.tooShort</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3043,22 +3043,22 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.end</t>
+          <t xml:space="preserve">trim.keepingWhole</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3075,22 +3075,22 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.start</t>
+          <t xml:space="preserve">trim.keeping</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3107,22 +3107,22 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.end</t>
+          <t xml:space="preserve">trim.handleBeginning</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">the beginning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3139,22 +3139,22 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notTimes</t>
+          <t xml:space="preserve">trim.handleEnd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start or end of the video is not a time.</t>
+          <t xml:space="preserve">the end</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3171,7 +3171,7 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.startAfterEnd</t>
+          <t xml:space="preserve">trim.problem.notATime.start</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start is after the end of the video.</t>
+          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3203,7 +3203,7 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.endBeforeStart</t>
+          <t xml:space="preserve">trim.problem.notATime.end</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end must come after the start.</t>
+          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3235,7 +3235,7 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.keepAtLeast</t>
+          <t xml:space="preserve">trim.problem.afterEnd.start</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
+          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3267,22 +3267,22 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.correctToContinue</t>
+          <t xml:space="preserve">trim.problem.afterEnd.end</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
+          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3299,17 +3299,17 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.legend</t>
+          <t xml:space="preserve">trim.problem.notTimes</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">The start or end of the video is not a time.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="2">
@@ -3331,17 +3331,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.typeLabel</t>
+          <t xml:space="preserve">trim.problem.startAfterEnd</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation type</t>
+          <t xml:space="preserve">The start is after the end of the video.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="2">
@@ -3363,17 +3363,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.cut</t>
+          <t xml:space="preserve">trim.problem.endBeforeStart</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cut</t>
+          <t xml:space="preserve">The end must come after the start.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="2">
@@ -3395,22 +3395,22 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.fade</t>
+          <t xml:space="preserve">trim.problem.keepAtLeast</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Fade</t>
+          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3427,17 +3427,17 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.slide</t>
+          <t xml:space="preserve">trim.correctToContinue</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Slide</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="2">
@@ -3459,7 +3459,7 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.none</t>
+          <t xml:space="preserve">closing.legend</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="2">
@@ -3491,7 +3491,7 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsetLabel</t>
+          <t xml:space="preserve">closing.typeLabel</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation onset</t>
+          <t xml:space="preserve">Animation type</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="2">
@@ -3523,7 +3523,7 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.existing</t>
+          <t xml:space="preserve">closing.types.cut</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">Cut</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="2">
@@ -3555,7 +3555,7 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.freeze</t>
+          <t xml:space="preserve">closing.types.fade</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">Fade</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="2">
@@ -3587,7 +3587,7 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpLabel</t>
+          <t xml:space="preserve">closing.types.slide</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About animation onset</t>
+          <t xml:space="preserve">Slide</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="2">
@@ -3619,7 +3619,7 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingTerm</t>
+          <t xml:space="preserve">closing.types.none</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="2">
@@ -3651,7 +3651,7 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingText</t>
+          <t xml:space="preserve">closing.onsetLabel</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
+          <t xml:space="preserve">Animation onset</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3683,7 +3683,7 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeTerm</t>
+          <t xml:space="preserve">closing.onsets.existing</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="2">
@@ -3715,7 +3715,7 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeText</t>
+          <t xml:space="preserve">closing.onsets.freeze</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3747,7 +3747,7 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colourLabel</t>
+          <t xml:space="preserve">closing.helpLabel</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Colour</t>
+          <t xml:space="preserve">About animation onset</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="2">
@@ -3779,7 +3779,7 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.blue</t>
+          <t xml:space="preserve">closing.helpExistingTerm</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Blue</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -3811,7 +3811,7 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.white</t>
+          <t xml:space="preserve">closing.helpExistingText</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">White</t>
+          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -3843,7 +3843,7 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalLabel</t>
+          <t xml:space="preserve">closing.helpFreezeTerm</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -3875,22 +3875,22 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalWords</t>
+          <t xml:space="preserve">closing.helpFreezeText</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
+          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -3907,7 +3907,7 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.cut</t>
+          <t xml:space="preserve">closing.colourLabel</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with Cut.</t>
+          <t xml:space="preserve">Colour</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -3939,7 +3939,7 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.none</t>
+          <t xml:space="preserve">closing.colours.blue</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with None.</t>
+          <t xml:space="preserve">Blue</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -3971,22 +3971,22 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.none</t>
+          <t xml:space="preserve">closing.colours.white</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No University closing will be added.</t>
+          <t xml:space="preserve">White</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4003,22 +4003,22 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.one</t>
+          <t xml:space="preserve">closing.internalLabel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} second.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4035,22 +4035,22 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.other</t>
+          <t xml:space="preserve">closing.internalWords</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} seconds.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4067,22 +4067,22 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.internal</t>
+          <t xml:space="preserve">closing.notUsedWith.cut</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The card says “{words}” under the logo.</t>
+          <t xml:space="preserve">Not used with Cut.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4099,22 +4099,22 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.blue</t>
+          <t xml:space="preserve">closing.notUsedWith.none</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
+          <t xml:space="preserve">Not used with None.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4131,22 +4131,22 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.white</t>
+          <t xml:space="preserve">closing.internalForSubmission</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
+          <t xml:space="preserve">Always on for a student submission.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Why the "Internal use only" checkbox cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4163,7 +4163,7 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
+          <t xml:space="preserve">closing.result.none</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">No University closing will be added.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4195,7 +4195,7 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
+          <t xml:space="preserve">closing.result.adds.one</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Adds {count} second.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4227,7 +4227,7 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
+          <t xml:space="preserve">closing.result.adds.other</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Adds {count} seconds.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4259,7 +4259,7 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
+          <t xml:space="preserve">closing.result.internal</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">The card says “{words}” under the logo.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4291,7 +4291,7 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
+          <t xml:space="preserve">closing.result.cut.blue</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4323,7 +4323,7 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
+          <t xml:space="preserve">closing.result.cut.white</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4355,7 +4355,7 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4387,7 +4387,7 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4419,22 +4419,22 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.legend</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4451,22 +4451,22 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.best</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larger / better</t>
+          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4483,22 +4483,22 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.smaller</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Smaller / reduced</t>
+          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4515,22 +4515,22 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.best</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
+          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4547,22 +4547,22 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.smaller</t>
+          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For messaging or email etc.</t>
+          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4579,22 +4579,22 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.note</t>
+          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
+          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4611,17 +4611,17 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceProgress</t>
+          <t xml:space="preserve">preset.legend</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Announce progress</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="2">
@@ -4643,22 +4643,22 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceHelp</t>
+          <t xml:space="preserve">preset.labels.best</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
+          <t xml:space="preserve">Larger / better</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4675,22 +4675,22 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.progressLabel</t>
+          <t xml:space="preserve">preset.labels.smaller</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video</t>
+          <t xml:space="preserve">Smaller / reduced</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4707,17 +4707,17 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.create</t>
+          <t xml:space="preserve">preset.details.best</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create the video</t>
+          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="2">
@@ -4739,17 +4739,17 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.cancel</t>
+          <t xml:space="preserve">preset.details.smaller</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">For messaging or email etc.</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="2">
@@ -4771,7 +4771,7 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.continueAnyway</t>
+          <t xml:space="preserve">create.note</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Continue anyway</t>
+          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="2">
@@ -4803,7 +4803,7 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopCheck</t>
+          <t xml:space="preserve">create.announceProgress</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop the check</t>
+          <t xml:space="preserve">Announce progress</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="2">
@@ -4835,7 +4835,7 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.checkAgain</t>
+          <t xml:space="preserve">create.announceHelp</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check again</t>
+          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="2">
@@ -4867,7 +4867,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopSaving</t>
+          <t xml:space="preserve">create.progressLabel</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop saving</t>
+          <t xml:space="preserve">Creating your video</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="2">
@@ -4899,7 +4899,7 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.save</t>
+          <t xml:space="preserve">create.create</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save the video</t>
+          <t xml:space="preserve">Create the video</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="2">
@@ -4931,7 +4931,7 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.saved</t>
+          <t xml:space="preserve">create.cancel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="2">
@@ -4963,7 +4963,7 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.discard</t>
+          <t xml:space="preserve">create.continueAnyway</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Discard it and start again</t>
+          <t xml:space="preserve">Continue anyway</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="2">
@@ -4995,7 +4995,7 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.keep</t>
+          <t xml:space="preserve">create.stopCheck</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep it</t>
+          <t xml:space="preserve">Stop the check</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="2">
@@ -5027,7 +5027,7 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedMaking</t>
+          <t xml:space="preserve">create.checkAgain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being made.</t>
+          <t xml:space="preserve">Check again</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="2">
@@ -5059,7 +5059,7 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedSaving</t>
+          <t xml:space="preserve">create.stopSaving</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being saved.</t>
+          <t xml:space="preserve">Stop saving</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="2">
@@ -5091,17 +5091,17 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checking</t>
+          <t xml:space="preserve">create.save</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking this video against your device…</t>
+          <t xml:space="preserve">Save the video</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="2">
@@ -5123,17 +5123,17 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checkStopped</t>
+          <t xml:space="preserve">create.saved</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check stopped.</t>
+          <t xml:space="preserve">Saved</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="2">
@@ -5155,17 +5155,17 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.stoppingSave</t>
+          <t xml:space="preserve">create.discard</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stopping the save…</t>
+          <t xml:space="preserve">Discard it and start again</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="2">
@@ -5187,17 +5187,17 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelling</t>
+          <t xml:space="preserve">create.keep</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelling…</t>
+          <t xml:space="preserve">Keep it</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="2">
@@ -5219,17 +5219,17 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelled</t>
+          <t xml:space="preserve">create.lockedMaking</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
+          <t xml:space="preserve">Locked while your video is being made.</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="2">
@@ -5251,17 +5251,17 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saving</t>
+          <t xml:space="preserve">create.lockedSaving</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving…</t>
+          <t xml:space="preserve">Locked while your video is being saved.</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="2">
@@ -5283,7 +5283,7 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveStopped</t>
+          <t xml:space="preserve">status.checking</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
+          <t xml:space="preserve">Checking this video against your device…</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="2">
@@ -5315,7 +5315,7 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.notSaved</t>
+          <t xml:space="preserve">status.checkStopped</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
+          <t xml:space="preserve">Check stopped.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.refusedSource</t>
+          <t xml:space="preserve">status.stoppingSave</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
+          <t xml:space="preserve">Stopping the save…</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="2">
@@ -5379,7 +5379,7 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saved</t>
+          <t xml:space="preserve">status.cancelling</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
+          <t xml:space="preserve">Cancelling…</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="2">
@@ -5411,7 +5411,7 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveFailed</t>
+          <t xml:space="preserve">status.cancelled</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
+          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="2">
@@ -5443,7 +5443,7 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.storageWayOut</t>
+          <t xml:space="preserve">status.saving</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
+          <t xml:space="preserve">Saving…</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5475,7 +5475,7 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.creating</t>
+          <t xml:space="preserve">status.saveStopped</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video. {notice}</t>
+          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5507,7 +5507,7 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.ready</t>
+          <t xml:space="preserve">status.notSaved</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is ready.</t>
+          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="2">
@@ -5539,7 +5539,7 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.couldNotCreate</t>
+          <t xml:space="preserve">status.refusedSource</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be created. {sentence}</t>
+          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5571,22 +5571,22 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.verdictSpoken</t>
+          <t xml:space="preserve">status.saved</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Device check complete. {heading}.</t>
+          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5603,17 +5603,17 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.title</t>
+          <t xml:space="preserve">status.saveFailed</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet</t>
+          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="2">
@@ -5635,22 +5635,22 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.delivered</t>
+          <t xml:space="preserve">status.storageWayOut</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
+          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5667,22 +5667,22 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.unsaved</t>
+          <t xml:space="preserve">status.creating</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
+          <t xml:space="preserve">Creating your video. {notice}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5699,22 +5699,22 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.spoken</t>
+          <t xml:space="preserve">status.ready</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet. {question}</t>
+          <t xml:space="preserve">Your video is ready.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5731,22 +5731,22 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.finished</t>
+          <t xml:space="preserve">status.couldNotCreate</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finished video — {size}</t>
+          <t xml:space="preserve">The video could not be created. {sentence}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5763,22 +5763,22 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.previous</t>
+          <t xml:space="preserve">status.verdictSpoken</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Previous video — {size}</t>
+          <t xml:space="preserve">Device check complete. {heading}.</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -5795,17 +5795,17 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetime</t>
+          <t xml:space="preserve">discard.title</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
+          <t xml:space="preserve">This video is not saved yet</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="2">
@@ -5827,17 +5827,17 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetimeDelivered</t>
+          <t xml:space="preserve">discard.delivered</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
+          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="2">
@@ -5859,22 +5859,22 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptWhole</t>
+          <t xml:space="preserve">discard.unsaved</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the whole video ({duration})</t>
+          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -5891,22 +5891,22 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptPart</t>
+          <t xml:space="preserve">discard.spoken</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
+          <t xml:space="preserve">This video is not saved yet. {question}</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
+          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -5923,7 +5923,7 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingNone</t>
+          <t xml:space="preserve">result.finished</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no University closing</t>
+          <t xml:space="preserve">Finished video — {size}</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -5955,7 +5955,7 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingInternal</t>
+          <t xml:space="preserve">result.previous</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{closing}, marked “{words}”</t>
+          <t xml:space="preserve">Previous video — {size}</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -5987,7 +5987,7 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.blue</t>
+          <t xml:space="preserve">result.lifetime</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the blue closing card</t>
+          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6019,7 +6019,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.white</t>
+          <t xml:space="preserve">result.lifetimeDelivered</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the white closing card</t>
+          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
+          <t xml:space="preserve">result.keptWhole</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
+          <t xml:space="preserve">the whole video ({duration})</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6083,7 +6083,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
+          <t xml:space="preserve">result.keptPart</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
+          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6115,7 +6115,7 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
+          <t xml:space="preserve">result.closingNone</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over a held last frame</t>
+          <t xml:space="preserve">no University closing</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6147,7 +6147,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
+          <t xml:space="preserve">result.closingInternal</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
+          <t xml:space="preserve">{closing}, marked “{words}”</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6179,7 +6179,7 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
+          <t xml:space="preserve">result.closingCut.blue</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over the picture</t>
+          <t xml:space="preserve">a cut to the blue closing card</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
+          <t xml:space="preserve">result.closingCut.white</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over the picture</t>
+          <t xml:space="preserve">a cut to the white closing card</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6243,7 +6243,7 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over the picture</t>
+          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6275,7 +6275,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over the picture</t>
+          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6307,7 +6307,7 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summary</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">the white closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6339,7 +6339,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6371,7 +6371,7 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">the blue closing fading in over the picture</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
@@ -6403,7 +6403,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">the blue closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
@@ -6435,7 +6435,7 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">the white closing fading in over the picture</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
@@ -6467,7 +6467,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">the white closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
@@ -6499,7 +6499,7 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.summary</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6531,7 +6531,7 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6563,7 +6563,7 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6595,7 +6595,7 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6627,7 +6627,7 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6659,7 +6659,7 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6691,7 +6691,7 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6723,7 +6723,7 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6755,22 +6755,22 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -6787,22 +6787,22 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -6819,22 +6819,22 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -6851,22 +6851,22 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -6883,22 +6883,22 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -6915,22 +6915,22 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -6947,7 +6947,7 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -6979,7 +6979,7 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7011,7 +7011,7 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7043,7 +7043,7 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7075,7 +7075,7 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
@@ -7107,22 +7107,22 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,22 +7139,22 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,22 +7171,22 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,22 +7235,22 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: said when the video starts being made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,17 +7267,17 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
@@ -7299,22 +7299,22 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,22 +7331,22 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,22 +7363,22 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,22 +7395,22 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7427,22 +7427,22 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">Step 5: said when the video starts being made</t>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7459,7 +7459,7 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,7 +7491,7 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7523,7 +7523,7 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7555,7 +7555,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7587,7 +7587,7 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7619,22 +7619,22 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7651,22 +7651,22 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,22 +7683,22 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,22 +7715,22 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7747,22 +7747,22 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,22 +7779,22 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -7811,17 +7811,17 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
@@ -7843,22 +7843,22 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -7971,7 +7971,7 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8003,7 +8003,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8195,7 +8195,7 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,7 +8227,7 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
@@ -8259,17 +8259,17 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
@@ -8291,17 +8291,17 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
@@ -8323,22 +8323,22 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8355,17 +8355,17 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
@@ -8387,22 +8387,22 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8419,17 +8419,17 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
@@ -8451,22 +8451,22 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8483,17 +8483,17 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
@@ -8515,22 +8515,22 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8547,17 +8547,17 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
@@ -8579,22 +8579,22 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
@@ -8643,7 +8643,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
@@ -8707,22 +8707,22 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
@@ -8771,7 +8771,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
@@ -8803,7 +8803,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
@@ -8835,7 +8835,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
@@ -8867,7 +8867,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
@@ -8899,7 +8899,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -8931,7 +8931,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
@@ -8963,7 +8963,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
@@ -8995,7 +8995,7 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
@@ -9027,7 +9027,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
@@ -9059,22 +9059,22 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9091,22 +9091,22 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,22 +9123,22 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9155,22 +9155,22 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9187,22 +9187,22 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9219,22 +9219,22 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9251,22 +9251,22 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9283,22 +9283,22 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9315,22 +9315,22 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9347,22 +9347,22 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9379,22 +9379,22 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9411,22 +9411,22 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
@@ -9955,7 +9955,7 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,7 +9987,7 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
@@ -10019,17 +10019,17 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
@@ -10051,22 +10051,22 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10083,22 +10083,22 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10115,22 +10115,22 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10147,17 +10147,17 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
@@ -10179,17 +10179,17 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
@@ -10211,22 +10211,22 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10243,22 +10243,22 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10275,22 +10275,22 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10307,22 +10307,22 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10339,22 +10339,22 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10371,17 +10371,17 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
@@ -10403,7 +10403,7 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10435,7 +10435,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10467,7 +10467,7 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10499,7 +10499,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10563,7 +10563,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
@@ -10595,7 +10595,7 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
@@ -10627,7 +10627,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
@@ -10819,7 +10819,7 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,7 +10851,7 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
@@ -10883,7 +10883,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,7 +10915,7 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,7 +10947,7 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
@@ -10979,7 +10979,7 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11011,7 +11011,7 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,17 +11043,17 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
@@ -11075,17 +11075,17 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
@@ -11107,17 +11107,17 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
@@ -11139,17 +11139,17 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
@@ -11171,22 +11171,22 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11203,22 +11203,22 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11235,17 +11235,17 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
@@ -11267,17 +11267,17 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
@@ -11299,17 +11299,17 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
@@ -11331,7 +11331,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
@@ -11363,7 +11363,7 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11427,7 +11427,7 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
@@ -11459,7 +11459,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11491,7 +11491,7 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11523,7 +11523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
@@ -11555,7 +11555,7 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,7 +11587,7 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
@@ -11619,7 +11619,7 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
@@ -11651,22 +11651,22 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11683,22 +11683,22 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,22 +11715,22 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,22 +11747,22 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11779,22 +11779,22 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,22 +11811,22 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,22 +11843,22 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -11875,22 +11875,22 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -11907,7 +11907,7 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,22 +11939,22 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,22 +11971,22 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12003,22 +12003,22 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,22 +12035,22 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12067,22 +12067,22 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12099,17 +12099,17 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
@@ -12131,22 +12131,22 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12163,22 +12163,22 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12195,22 +12195,22 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12227,22 +12227,22 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12259,22 +12259,22 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12291,22 +12291,22 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Equality Advisory and Support Service</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12323,22 +12323,22 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.heading</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance status</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12355,22 +12355,22 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.text</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12387,22 +12387,22 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.heading</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How we tested this tool</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12419,22 +12419,22 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.wave</t>
+          <t xml:space="preserve">statement.enforcement.heading</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+          <t xml:space="preserve">Enforcement procedure</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12451,7 +12451,7 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.automated</t>
+          <t xml:space="preserve">statement.enforcement.text</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,7 +12483,7 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.manual</t>
+          <t xml:space="preserve">statement.enforcement.service</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12515,7 +12515,7 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.heading</t>
+          <t xml:space="preserve">statement.compliance.heading</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What we plan to test next</t>
+          <t xml:space="preserve">Compliance status</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
@@ -12547,7 +12547,7 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.intro</t>
+          <t xml:space="preserve">statement.compliance.text</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12557,12 +12557,12 @@
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12579,22 +12579,22 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.0</t>
+          <t xml:space="preserve">statement.testing.heading</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using the tool with a keyboard alone</t>
+          <t xml:space="preserve">How we tested this tool</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12611,22 +12611,22 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.1</t>
+          <t xml:space="preserve">statement.testing.wave</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12643,22 +12643,22 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.2</t>
+          <t xml:space="preserve">statement.testing.automated</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12675,22 +12675,22 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.3</t>
+          <t xml:space="preserve">statement.testing.manual</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Windows contrast themes</t>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12707,22 +12707,22 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.4</t>
+          <t xml:space="preserve">statement.plans.heading</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+          <t xml:space="preserve">What we plan to test next</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12739,22 +12739,22 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.5</t>
+          <t xml:space="preserve">statement.plans.intro</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -12771,22 +12771,22 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.heading</t>
+          <t xml:space="preserve">statement.plans.items.0</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About this statement</t>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -12803,22 +12803,22 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.dates</t>
+          <t xml:space="preserve">statement.plans.items.1</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -12835,22 +12835,22 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.intro</t>
+          <t xml:space="preserve">statement.plans.items.2</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For help with this tool:</t>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -12867,22 +12867,22 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.creators</t>
+          <t xml:space="preserve">statement.plans.items.3</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the creators team</t>
+          <t xml:space="preserve">Windows contrast themes</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,22 +12899,22 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.learningContent</t>
+          <t xml:space="preserve">statement.plans.items.4</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the learning content team</t>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -12931,22 +12931,22 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">statement.plans.items.5</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,22 +12963,22 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">statement.about.heading</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">About this statement</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,22 +12995,22 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">statement.about.dates</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13027,22 +13027,22 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">footer.contact.intro</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
         </is>
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">For help with this tool:</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,22 +13059,22 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">footer.contact.creators</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
         </is>
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">Email the creators team</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13091,22 +13091,22 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">footer.contact.learningContent</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
         </is>
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">Email the learning content team</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13123,17 +13123,17 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">save.pickerDescription</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
@@ -13155,22 +13155,22 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">save.stem</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">video</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13187,22 +13187,22 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">save.marks.branded</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">branded</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,22 +13219,22 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">save.marks.levelled</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">levelled</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,22 +13251,22 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">save.marks.converted</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">converted</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13283,22 +13283,22 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">save.fileName</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13315,22 +13315,22 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">save.downloadIos</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,22 +13347,22 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">save.downloadOther</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">Saving to your downloads folder</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,22 +13379,22 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">save.download</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13411,7 +13411,7 @@
     <row r="418">
       <c r="A418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">format.unknown</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="C418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13443,7 +13443,7 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">format.lessThanASecond</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">less than a second</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="2">
@@ -13475,7 +13475,7 @@
     <row r="420">
       <c r="A420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">format.fewSeconds</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">a few seconds</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="2">
@@ -13507,30 +13507,222 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">format.frameRate</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{rate} frames a second</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.resolution</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{width} × {height}</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.mono</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Mono (one channel)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.stereo</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Stereo (two channels)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr" s="2">
+      <c r="B427" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr" s="2">
+      <c r="C427" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr" s="2">
+      <c r="D427" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr" s="2">
+      <c r="E427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -771,22 +771,22 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.choose</t>
+          <t xml:space="preserve">videoLanguage.label</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the choice of language for the words drawn into the video</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a video</t>
+          <t xml:space="preserve">Video language</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The label over the choice, also read out by screen readers. Use the same word for "video" as videoKind.label and for "language" as language.label.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -803,22 +803,22 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.trim</t>
+          <t xml:space="preserve">videoLanguage.helper</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of each of the five steps</t>
+          <t xml:space="preserve">Above Step 1: the choice of language for the words drawn into the video</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Trim</t>
+          <t xml:space="preserve">Words the app adds to your video are in this language.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The words the app draws into the video, such as closing.internalWords, follow this choice; the page itself does not.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -835,7 +835,7 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.closing</t>
+          <t xml:space="preserve">steps.choose</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -845,7 +845,7 @@
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">Choose a video</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -867,7 +867,7 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.preset</t>
+          <t xml:space="preserve">steps.trim</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -877,7 +877,7 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">Trim</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -899,7 +899,7 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">steps.create</t>
+          <t xml:space="preserve">steps.closing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -909,7 +909,7 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -931,17 +931,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHint</t>
+          <t xml:space="preserve">steps.preset</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Or drop it here.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -963,17 +963,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.dropHeld</t>
+          <t xml:space="preserve">steps.create</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1, Choose a video</t>
+          <t xml:space="preserve">The heading of each of the five steps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Let go to read this video.</t>
+          <t xml:space="preserve">Create</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -995,7 +995,7 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.reading</t>
+          <t xml:space="preserve">choose.dropHint</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">Or drop it here.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -1027,17 +1027,17 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.making</t>
+          <t xml:space="preserve">choose.dropHeld</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">Let go to read this video.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -1059,17 +1059,17 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.saving</t>
+          <t xml:space="preserve">choose.reading</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
+          <t xml:space="preserve">Step 1, Choose a video</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -1091,7 +1091,7 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.starting</t>
+          <t xml:space="preserve">choose.drop.making</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
+          <t xml:space="preserve">A video is being made. Cancel it, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
@@ -1123,7 +1123,7 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.unavailable</t>
+          <t xml:space="preserve">choose.drop.saving</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
+          <t xml:space="preserve">A video is being saved. Stop the save, or wait for it to finish, before choosing another.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
@@ -1155,7 +1155,7 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.nothing</t>
+          <t xml:space="preserve">choose.drop.starting</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
+          <t xml:space="preserve">The tool is still getting ready. Drop the video again in a moment.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -1187,7 +1187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.several</t>
+          <t xml:space="preserve">choose.drop.unavailable</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
+          <t xml:space="preserve">This browser cannot run the tool, so no video can be read here. The message below says what to do.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1219,7 +1219,7 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">choose.drop.notVideo</t>
+          <t xml:space="preserve">choose.drop.nothing</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
+          <t xml:space="preserve">Nothing was dropped that could be read. Drop a video file.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
@@ -1251,22 +1251,22 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.readSummary</t>
+          <t xml:space="preserve">choose.drop.several</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video read. {facts}.</t>
+          <t xml:space="preserve">That was {count} files. Drop one video at a time.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
+          <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1283,17 +1283,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variableFrameRate</t>
+          <t xml:space="preserve">choose.drop.notVideo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: the message when something is dropped on the drop area</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">variable frame rate</t>
+          <t xml:space="preserve">That is not a video file. Drop a video — a file whose name ends .mp4 or .mov, say — or choose one above.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -1315,7 +1315,7 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSound</t>
+          <t xml:space="preserve">source.readSummary</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no sound</t>
+          <t xml:space="preserve">Video read. {facts}.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {facts} as written: {facts} is a list of facts about the video, like "4 minutes 12 seconds, 1920 × 1080, stereo (two channels)".</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1347,7 +1347,7 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.properties</t>
+          <t xml:space="preserve">source.variableFrameRate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video properties</t>
+          <t xml:space="preserve">variable frame rate</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
@@ -1379,7 +1379,7 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.lossesTitle</t>
+          <t xml:space="preserve">source.noSound</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not carried into the new file</t>
+          <t xml:space="preserve">no sound</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -1411,17 +1411,17 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.duration</t>
+          <t xml:space="preserve">source.properties</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Duration</t>
+          <t xml:space="preserve">Video properties</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -1443,17 +1443,17 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.videoFormat</t>
+          <t xml:space="preserve">source.lossesTitle</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format</t>
+          <t xml:space="preserve">Not carried into the new file</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -1475,7 +1475,7 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileSize</t>
+          <t xml:space="preserve">source.rows.duration</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size</t>
+          <t xml:space="preserve">Duration</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -1507,7 +1507,7 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.resolution</t>
+          <t xml:space="preserve">source.rows.videoFormat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Resolution</t>
+          <t xml:space="preserve">Video format</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -1539,7 +1539,7 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.frameRate</t>
+          <t xml:space="preserve">source.rows.fileSize</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Frame rate</t>
+          <t xml:space="preserve">File size</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -1571,7 +1571,7 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundFormat</t>
+          <t xml:space="preserve">source.rows.resolution</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format</t>
+          <t xml:space="preserve">Resolution</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -1603,7 +1603,7 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.soundChannels</t>
+          <t xml:space="preserve">source.rows.frameRate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound channels</t>
+          <t xml:space="preserve">Frame rate</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
@@ -1635,7 +1635,7 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sampleRate</t>
+          <t xml:space="preserve">source.rows.soundFormat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound sample rate</t>
+          <t xml:space="preserve">Sound format</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -1667,7 +1667,7 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.sound</t>
+          <t xml:space="preserve">source.rows.soundChannels</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound</t>
+          <t xml:space="preserve">Sound channels</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
@@ -1699,7 +1699,7 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.captions</t>
+          <t xml:space="preserve">source.rows.sampleRate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Captions</t>
+          <t xml:space="preserve">Sound sample rate</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
@@ -1731,7 +1731,7 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rows.fileType</t>
+          <t xml:space="preserve">source.rows.sound</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File type</t>
+          <t xml:space="preserve">Sound</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="2">
@@ -1763,17 +1763,17 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeVideo</t>
+          <t xml:space="preserve">source.rows.captions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this video format.</t>
+          <t xml:space="preserve">Captions</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
@@ -1795,17 +1795,17 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.cannotDecodeAudio</t>
+          <t xml:space="preserve">source.rows.fileType</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
+          <t xml:space="preserve">Step 1: Video properties, the name of each row</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read this audio format.</t>
+          <t xml:space="preserve">File type</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
@@ -1827,7 +1827,7 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.rotated</t>
+          <t xml:space="preserve">source.cannotDecodeVideo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
+          <t xml:space="preserve">This browser cannot read this video format.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -1859,7 +1859,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesOnAverage</t>
+          <t xml:space="preserve">source.cannotDecodeAudio</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} on average, but it varies</t>
+          <t xml:space="preserve">This browser cannot read this audio format.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -1891,7 +1891,7 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.variesNote</t>
+          <t xml:space="preserve">source.rotated</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
+          <t xml:space="preserve">Rotated {degrees}°. The output will be upright.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {degrees} as written: {degrees} is a number of degrees.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -1923,7 +1923,7 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.outputRate</t>
+          <t xml:space="preserve">source.variesOnAverage</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
+          <t xml:space="preserve">{rate} on average, but it varies</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="2">
@@ -1955,7 +1955,7 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.sampleRate</t>
+          <t xml:space="preserve">source.variesNote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
+          <t xml:space="preserve">Recordings from Teams, Zoom and screen capture often vary. The output will use a steady frame rate, which keeps sound and picture in step.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -1987,7 +1987,7 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundTrack</t>
+          <t xml:space="preserve">source.outputRate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No sound track found</t>
+          <t xml:space="preserve">The output will run at {rate}, so some frames will be repeated.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2019,7 +2019,7 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.noSoundNote</t>
+          <t xml:space="preserve">source.sampleRate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
+          <t xml:space="preserve">{kilohertz} kHz — {hertz} samples a second</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {kilohertz}, {hertz} as written: {kilohertz} is a number; {hertz} is a number.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2051,7 +2051,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsUnchecked</t>
+          <t xml:space="preserve">source.noSoundTrack</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not be checked in this kind of file</t>
+          <t xml:space="preserve">No sound track found</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="2">
@@ -2083,7 +2083,7 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsFound</t>
+          <t xml:space="preserve">source.noSoundNote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Found {found}</t>
+          <t xml:space="preserve">Levelling needs sound. The rest of the job still runs.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2115,7 +2115,7 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionsNone</t>
+          <t xml:space="preserve">source.captionsUnchecked</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None found in this file</t>
+          <t xml:space="preserve">Could not be checked in this kind of file</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="2">
@@ -2147,7 +2147,7 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.one</t>
+          <t xml:space="preserve">source.captionsFound</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption track</t>
+          <t xml:space="preserve">Found {found}</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2179,7 +2179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.captionTracks.other</t>
+          <t xml:space="preserve">source.captionsNone</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} caption tracks</t>
+          <t xml:space="preserve">None found in this file</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2211,7 +2211,7 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.one</t>
+          <t xml:space="preserve">source.captionTracks.one</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter track</t>
+          <t xml:space="preserve">{count} caption track</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="2">
@@ -2243,7 +2243,7 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.chapterTracks.other</t>
+          <t xml:space="preserve">source.captionTracks.other</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} chapter tracks</t>
+          <t xml:space="preserve">{count} caption tracks</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="2">
@@ -2275,7 +2275,7 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.one</t>
+          <t xml:space="preserve">source.chapterTracks.one</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video track</t>
+          <t xml:space="preserve">{count} chapter track</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="2">
@@ -2307,7 +2307,7 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreVideoTracks.other</t>
+          <t xml:space="preserve">source.chapterTracks.other</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more video tracks</t>
+          <t xml:space="preserve">{count} chapter tracks</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="2">
@@ -2339,7 +2339,7 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.one</t>
+          <t xml:space="preserve">source.moreVideoTracks.one</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound track</t>
+          <t xml:space="preserve">{count} more video track</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="2">
@@ -2371,7 +2371,7 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.moreSoundTracks.other</t>
+          <t xml:space="preserve">source.moreVideoTracks.other</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} more sound tracks</t>
+          <t xml:space="preserve">{count} more video tracks</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="2">
@@ -2403,22 +2403,22 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksTitle</t>
+          <t xml:space="preserve">source.moreSoundTracks.one</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has {found}</t>
+          <t xml:space="preserve">{count} more sound track</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2435,22 +2435,22 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.extraTracksDetail</t>
+          <t xml:space="preserve">source.moreSoundTracks.other</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
+          <t xml:space="preserve">Step 1: what the video is, once it has been read</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
+          <t xml:space="preserve">{count} more sound tracks</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2467,7 +2467,7 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedTitle</t>
+          <t xml:space="preserve">source.losses.extraTracksTitle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
+          <t xml:space="preserve">This file has {found}</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {found} as written: {found} is a list, like "2 caption tracks and 1 chapter track".</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2499,7 +2499,7 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.uncheckedDetail</t>
+          <t xml:space="preserve">source.losses.extraTracksDetail</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
+          <t xml:space="preserve">The new file keeps one picture and one sound track — the ones listed under Video properties. The others will not be carried over, and one of them may hold an alternative, such as another language or an audio description. If you need them, keep the original alongside.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="2">
@@ -2531,7 +2531,7 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.captionsConsequence</t>
+          <t xml:space="preserve">source.losses.uncheckedTitle</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
+          <t xml:space="preserve">Caption and chapter tracks could not be checked</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="2">
@@ -2563,7 +2563,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.chaptersConsequence</t>
+          <t xml:space="preserve">source.losses.uncheckedDetail</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The chapters will not be in the new file.</t>
+          <t xml:space="preserve">This kind of file cannot be checked for them. If yours has them, they will not be carried over.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="2">
@@ -2595,7 +2595,7 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">source.losses.keepOriginals</t>
+          <t xml:space="preserve">source.losses.captionsConsequence</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
+          <t xml:space="preserve">The new file will have no caption track, so wherever you publish it must supply captions. EchoVideo makes its own after upload — check them. A file sent directly needs captions added by you. Captions drawn into the picture stay.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="2">
@@ -2627,17 +2627,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.intro</t>
+          <t xml:space="preserve">source.losses.chaptersConsequence</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
+          <t xml:space="preserve">The chapters will not be in the new file.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="2">
@@ -2659,17 +2659,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.noPreview</t>
+          <t xml:space="preserve">source.losses.keepOriginals</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 1: the box listing what will not be carried into the new file</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
+          <t xml:space="preserve">If you need the originals, keep this file alongside.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="2">
@@ -2691,7 +2691,7 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.start</t>
+          <t xml:space="preserve">trim.intro</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start</t>
+          <t xml:space="preserve">Optional. Cut unwanted material from the start or the end. Left alone, the whole video is kept. The preview plays your original as it is now: the sound is levelled and the closing added when the video is made.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="2">
@@ -2723,7 +2723,7 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.end</t>
+          <t xml:space="preserve">trim.noPreview</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End</t>
+          <t xml:space="preserve">A preview is not available for this file. You can still set the times.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="2">
@@ -2755,7 +2755,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.startTime</t>
+          <t xml:space="preserve">trim.start</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Start time</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="2">
@@ -2787,7 +2787,7 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.endTime</t>
+          <t xml:space="preserve">trim.end</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End time</t>
+          <t xml:space="preserve">End</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="2">
@@ -2819,7 +2819,7 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setStart</t>
+          <t xml:space="preserve">trim.startTime</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set start here</t>
+          <t xml:space="preserve">Start time</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="2">
@@ -2851,7 +2851,7 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.setEnd</t>
+          <t xml:space="preserve">trim.endTime</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set end here</t>
+          <t xml:space="preserve">End time</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="2">
@@ -2883,7 +2883,7 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.format</t>
+          <t xml:space="preserve">trim.setStart</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
+          <t xml:space="preserve">Set start here</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -2915,7 +2915,7 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.useWhole</t>
+          <t xml:space="preserve">trim.setEnd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the whole video</t>
+          <t xml:space="preserve">Set end here</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="2">
@@ -2947,7 +2947,7 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.reading</t>
+          <t xml:space="preserve">trim.format</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading the video…</t>
+          <t xml:space="preserve">Minutes and seconds, like 1:05.5, or seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -2979,7 +2979,7 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.unreadable</t>
+          <t xml:space="preserve">trim.useWhole</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
+          <t xml:space="preserve">Use the whole video</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="2">
@@ -3011,7 +3011,7 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.tooShort</t>
+          <t xml:space="preserve">trim.reading</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
+          <t xml:space="preserve">Reading the video…</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3043,7 +3043,7 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keepingWhole</t>
+          <t xml:space="preserve">trim.unreadable</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
+          <t xml:space="preserve">There is no video to trim: that file could not be read.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3075,7 +3075,7 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.keeping</t>
+          <t xml:space="preserve">trim.tooShort</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
+          <t xml:space="preserve">It is shorter than {seconds} seconds, so it cannot be trimmed.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3107,7 +3107,7 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleBeginning</t>
+          <t xml:space="preserve">trim.keepingWhole</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the beginning</t>
+          <t xml:space="preserve">Keeping the whole video, {duration}.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3139,7 +3139,7 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.handleEnd</t>
+          <t xml:space="preserve">trim.keeping</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the end</t>
+          <t xml:space="preserve">Keeping {kept} of {duration}.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
+          <t xml:space="preserve">Keep {kept}, {duration} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3171,22 +3171,22 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.start</t>
+          <t xml:space="preserve">trim.handleBeginning</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">the beginning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
+          <t xml:space="preserve">Completes "Start, at the beginning" for screen readers.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3203,22 +3203,22 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notATime.end</t>
+          <t xml:space="preserve">trim.handleEnd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
+          <t xml:space="preserve">the end</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
+          <t xml:space="preserve">Completes "End, at the end" for screen readers.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3235,7 +3235,7 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.start</t>
+          <t xml:space="preserve">trim.problem.notATime.start</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">Write the start time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the start time.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3267,7 +3267,7 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.afterEnd.end</t>
+          <t xml:space="preserve">trim.problem.notATime.end</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
+          <t xml:space="preserve">Write the end time as minutes and seconds, like 1:05.5, or as seconds, like 65.5.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
+          <t xml:space="preserve">Keep the example times 1:05.5 and 65.5 as they are. About the end time.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3299,7 +3299,7 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.notTimes</t>
+          <t xml:space="preserve">trim.problem.afterEnd.start</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start or end of the video is not a time.</t>
+          <t xml:space="preserve">The start time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About the start time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3331,7 +3331,7 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.startAfterEnd</t>
+          <t xml:space="preserve">trim.problem.afterEnd.end</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start is after the end of the video.</t>
+          <t xml:space="preserve">The end time is after the end of the video, which is {length} long.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">About the end time. Keep {length} as written: {length} is a time, like 2:10.4.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3363,7 +3363,7 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.endBeforeStart</t>
+          <t xml:space="preserve">trim.problem.notTimes</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The end must come after the start.</t>
+          <t xml:space="preserve">The start or end of the video is not a time.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="2">
@@ -3395,7 +3395,7 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.problem.keepAtLeast</t>
+          <t xml:space="preserve">trim.problem.startAfterEnd</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
+          <t xml:space="preserve">The start is after the end of the video.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3427,17 +3427,17 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">trim.correctToContinue</t>
+          <t xml:space="preserve">trim.problem.endBeforeStart</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 2, Trim</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
+          <t xml:space="preserve">The end must come after the start.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="2">
@@ -3459,22 +3459,22 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.legend</t>
+          <t xml:space="preserve">trim.problem.keepAtLeast</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2: the error beside a start or end time that cannot be used</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">Keep at least {seconds} seconds of the video.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {seconds} as written: {seconds} is a number of seconds.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3491,17 +3491,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.typeLabel</t>
+          <t xml:space="preserve">trim.correctToContinue</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Step 2, Trim</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation type</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 to continue.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="2">
@@ -3523,7 +3523,7 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.cut</t>
+          <t xml:space="preserve">closing.legend</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cut</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="2">
@@ -3555,7 +3555,7 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.fade</t>
+          <t xml:space="preserve">closing.typeLabel</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Fade</t>
+          <t xml:space="preserve">Animation type</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="2">
@@ -3587,7 +3587,7 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.slide</t>
+          <t xml:space="preserve">closing.types.cut</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Slide</t>
+          <t xml:space="preserve">Cut</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="2">
@@ -3619,7 +3619,7 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.none</t>
+          <t xml:space="preserve">closing.types.fade</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Fade</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="2">
@@ -3651,7 +3651,7 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsetLabel</t>
+          <t xml:space="preserve">closing.types.slide</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation onset</t>
+          <t xml:space="preserve">Slide</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="2">
@@ -3683,7 +3683,7 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.existing</t>
+          <t xml:space="preserve">closing.types.none</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="2">
@@ -3715,7 +3715,7 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.freeze</t>
+          <t xml:space="preserve">closing.onsetLabel</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">Animation onset</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="2">
@@ -3747,7 +3747,7 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpLabel</t>
+          <t xml:space="preserve">closing.onsets.existing</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About animation onset</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="2">
@@ -3779,7 +3779,7 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingTerm</t>
+          <t xml:space="preserve">closing.onsets.freeze</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="2">
@@ -3811,7 +3811,7 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingText</t>
+          <t xml:space="preserve">closing.helpLabel</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
+          <t xml:space="preserve">About animation onset</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -3843,7 +3843,7 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeTerm</t>
+          <t xml:space="preserve">closing.helpExistingTerm</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="2">
@@ -3875,7 +3875,7 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeText</t>
+          <t xml:space="preserve">closing.helpExistingText</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
+          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -3907,7 +3907,7 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colourLabel</t>
+          <t xml:space="preserve">closing.helpFreezeTerm</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Colour</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="2">
@@ -3939,7 +3939,7 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.blue</t>
+          <t xml:space="preserve">closing.helpFreezeText</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Blue</t>
+          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -3971,7 +3971,7 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.white</t>
+          <t xml:space="preserve">closing.colourLabel</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">White</t>
+          <t xml:space="preserve">Colour</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4003,7 +4003,7 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalLabel</t>
+          <t xml:space="preserve">closing.colours.blue</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">Blue</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4035,22 +4035,22 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalWords</t>
+          <t xml:space="preserve">closing.colours.white</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">White</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4067,7 +4067,7 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.cut</t>
+          <t xml:space="preserve">closing.internalLabel</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with Cut.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
+          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4099,22 +4099,22 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.none</t>
+          <t xml:space="preserve">closing.internalWords</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with None.</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
+          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4131,7 +4131,7 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalForSubmission</t>
+          <t xml:space="preserve">closing.notUsedWith.cut</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Always on for a student submission.</t>
+          <t xml:space="preserve">Not used with Cut.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Why the "Internal use only" checkbox cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
+          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4163,22 +4163,22 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.none</t>
+          <t xml:space="preserve">closing.notUsedWith.none</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No University closing will be added.</t>
+          <t xml:space="preserve">Not used with None.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4195,22 +4195,22 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.one</t>
+          <t xml:space="preserve">closing.internalForSubmission</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 3, Closing branding</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} second.</t>
+          <t xml:space="preserve">Always on for a student submission.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Why the "Internal use only" checkbox cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4227,7 +4227,7 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.other</t>
+          <t xml:space="preserve">closing.result.none</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} seconds.</t>
+          <t xml:space="preserve">No University closing will be added.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4259,7 +4259,7 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.internal</t>
+          <t xml:space="preserve">closing.result.adds.one</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The card says “{words}” under the logo.</t>
+          <t xml:space="preserve">Adds {count} second.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4291,7 +4291,7 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.blue</t>
+          <t xml:space="preserve">closing.result.adds.other</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
+          <t xml:space="preserve">Adds {count} seconds.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4323,7 +4323,7 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.white</t>
+          <t xml:space="preserve">closing.result.internal</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
+          <t xml:space="preserve">The card says “{words}” under the logo.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4355,7 +4355,7 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
+          <t xml:space="preserve">closing.result.cut.blue</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4387,7 +4387,7 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
+          <t xml:space="preserve">closing.result.cut.white</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4419,7 +4419,7 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4451,7 +4451,7 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4483,7 +4483,7 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4515,7 +4515,7 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4547,7 +4547,7 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4579,7 +4579,7 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4589,12 +4589,12 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4611,22 +4611,22 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.legend</t>
+          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4643,22 +4643,22 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.best</t>
+          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, File size / quality</t>
+          <t xml:space="preserve">Step 3: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larger / better</t>
+          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4675,7 +4675,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.smaller</t>
+          <t xml:space="preserve">preset.legend</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Smaller / reduced</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4707,7 +4707,7 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.best</t>
+          <t xml:space="preserve">preset.labels.best</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
+          <t xml:space="preserve">Larger / better</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4739,7 +4739,7 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.smaller</t>
+          <t xml:space="preserve">preset.labels.smaller</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For messaging or email etc.</t>
+          <t xml:space="preserve">Smaller / reduced</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4771,17 +4771,17 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.note</t>
+          <t xml:space="preserve">preset.details.best</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
+          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="2">
@@ -4803,17 +4803,17 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceProgress</t>
+          <t xml:space="preserve">preset.details.smaller</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, File size / quality</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Announce progress</t>
+          <t xml:space="preserve">For messaging or email etc.</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="2">
@@ -4835,7 +4835,7 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceHelp</t>
+          <t xml:space="preserve">create.note</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
+          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="2">
@@ -4867,7 +4867,7 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.progressLabel</t>
+          <t xml:space="preserve">create.announceProgress</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video</t>
+          <t xml:space="preserve">Announce progress</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="2">
@@ -4899,7 +4899,7 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.create</t>
+          <t xml:space="preserve">create.announceHelp</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create the video</t>
+          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="2">
@@ -4931,7 +4931,7 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.cancel</t>
+          <t xml:space="preserve">create.progressLabel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">Creating your video</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="2">
@@ -4963,7 +4963,7 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.continueAnyway</t>
+          <t xml:space="preserve">create.create</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Continue anyway</t>
+          <t xml:space="preserve">Create the video</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="2">
@@ -4995,7 +4995,7 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopCheck</t>
+          <t xml:space="preserve">create.cancel</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop the check</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="2">
@@ -5027,7 +5027,7 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.checkAgain</t>
+          <t xml:space="preserve">create.continueAnyway</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check again</t>
+          <t xml:space="preserve">Continue anyway</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="2">
@@ -5059,7 +5059,7 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopSaving</t>
+          <t xml:space="preserve">create.stopCheck</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop saving</t>
+          <t xml:space="preserve">Stop the check</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="2">
@@ -5091,7 +5091,7 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.save</t>
+          <t xml:space="preserve">create.checkAgain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save the video</t>
+          <t xml:space="preserve">Check again</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="2">
@@ -5123,7 +5123,7 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.saved</t>
+          <t xml:space="preserve">create.stopSaving</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved</t>
+          <t xml:space="preserve">Stop saving</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="2">
@@ -5155,7 +5155,7 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.discard</t>
+          <t xml:space="preserve">create.save</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Discard it and start again</t>
+          <t xml:space="preserve">Save the video</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="2">
@@ -5187,7 +5187,7 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.keep</t>
+          <t xml:space="preserve">create.saved</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep it</t>
+          <t xml:space="preserve">Saved</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="2">
@@ -5219,7 +5219,7 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedMaking</t>
+          <t xml:space="preserve">create.discard</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being made.</t>
+          <t xml:space="preserve">Discard it and start again</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="2">
@@ -5251,7 +5251,7 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedSaving</t>
+          <t xml:space="preserve">create.keep</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being saved.</t>
+          <t xml:space="preserve">Keep it</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="2">
@@ -5283,17 +5283,17 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checking</t>
+          <t xml:space="preserve">create.lockedMaking</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking this video against your device…</t>
+          <t xml:space="preserve">Locked while your video is being made.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="2">
@@ -5315,17 +5315,17 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checkStopped</t>
+          <t xml:space="preserve">create.lockedSaving</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check stopped.</t>
+          <t xml:space="preserve">Locked while your video is being saved.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.stoppingSave</t>
+          <t xml:space="preserve">status.checking</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stopping the save…</t>
+          <t xml:space="preserve">Checking this video against your device…</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="2">
@@ -5379,7 +5379,7 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelling</t>
+          <t xml:space="preserve">status.checkStopped</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelling…</t>
+          <t xml:space="preserve">Check stopped.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="2">
@@ -5411,7 +5411,7 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelled</t>
+          <t xml:space="preserve">status.stoppingSave</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
+          <t xml:space="preserve">Stopping the save…</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="2">
@@ -5443,7 +5443,7 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saving</t>
+          <t xml:space="preserve">status.cancelling</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving…</t>
+          <t xml:space="preserve">Cancelling…</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="2">
@@ -5475,7 +5475,7 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveStopped</t>
+          <t xml:space="preserve">status.cancelled</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
+          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="2">
@@ -5507,7 +5507,7 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.notSaved</t>
+          <t xml:space="preserve">status.saving</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
+          <t xml:space="preserve">Saving…</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="2">
@@ -5539,7 +5539,7 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.refusedSource</t>
+          <t xml:space="preserve">status.saveStopped</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
+          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="2">
@@ -5571,7 +5571,7 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saved</t>
+          <t xml:space="preserve">status.notSaved</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
+          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="2">
@@ -5603,7 +5603,7 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveFailed</t>
+          <t xml:space="preserve">status.refusedSource</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
+          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="2">
@@ -5635,7 +5635,7 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.storageWayOut</t>
+          <t xml:space="preserve">status.saved</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
+          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5667,7 +5667,7 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.creating</t>
+          <t xml:space="preserve">status.saveFailed</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video. {notice}</t>
+          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5699,7 +5699,7 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.ready</t>
+          <t xml:space="preserve">status.storageWayOut</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is ready.</t>
+          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5731,7 +5731,7 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.couldNotCreate</t>
+          <t xml:space="preserve">status.creating</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be created. {sentence}</t>
+          <t xml:space="preserve">Creating your video. {notice}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
+          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5763,22 +5763,22 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.verdictSpoken</t>
+          <t xml:space="preserve">status.ready</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Device check complete. {heading}.</t>
+          <t xml:space="preserve">Your video is ready.</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -5795,22 +5795,22 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.title</t>
+          <t xml:space="preserve">status.couldNotCreate</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 5: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet</t>
+          <t xml:space="preserve">The video could not be created. {sentence}</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -5827,22 +5827,22 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.delivered</t>
+          <t xml:space="preserve">status.verdictSpoken</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
+          <t xml:space="preserve">Device check complete. {heading}.</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -5859,7 +5859,7 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.unsaved</t>
+          <t xml:space="preserve">discard.title</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
+          <t xml:space="preserve">This video is not saved yet</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="2">
@@ -5891,22 +5891,22 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.spoken</t>
+          <t xml:space="preserve">discard.delivered</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet. {question}</t>
+          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -5923,22 +5923,22 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.finished</t>
+          <t xml:space="preserve">discard.unsaved</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 5: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finished video — {size}</t>
+          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -5955,22 +5955,22 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.previous</t>
+          <t xml:space="preserve">discard.spoken</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Previous video — {size}</t>
+          <t xml:space="preserve">This video is not saved yet. {question}</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -5987,7 +5987,7 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetime</t>
+          <t xml:space="preserve">result.finished</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
+          <t xml:space="preserve">Finished video — {size}</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6019,7 +6019,7 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetimeDelivered</t>
+          <t xml:space="preserve">result.previous</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
+          <t xml:space="preserve">Previous video — {size}</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptWhole</t>
+          <t xml:space="preserve">result.lifetime</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the whole video ({duration})</t>
+          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6083,7 +6083,7 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptPart</t>
+          <t xml:space="preserve">result.lifetimeDelivered</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
+          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6115,7 +6115,7 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingNone</t>
+          <t xml:space="preserve">result.keptWhole</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no University closing</t>
+          <t xml:space="preserve">the whole video ({duration})</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6147,7 +6147,7 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingInternal</t>
+          <t xml:space="preserve">result.keptPart</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{closing}, marked “{words}”</t>
+          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6179,7 +6179,7 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.blue</t>
+          <t xml:space="preserve">result.closingNone</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the blue closing card</t>
+          <t xml:space="preserve">no University closing</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.white</t>
+          <t xml:space="preserve">result.closingInternal</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the white closing card</t>
+          <t xml:space="preserve">{closing}, marked “{words}”</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6243,7 +6243,7 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
+          <t xml:space="preserve">result.closingCut.blue</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6253,12 +6253,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
+          <t xml:space="preserve">a cut to the blue closing card</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6275,7 +6275,7 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
+          <t xml:space="preserve">result.closingCut.white</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
+          <t xml:space="preserve">a cut to the white closing card</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6307,7 +6307,7 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over a held last frame</t>
+          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6339,7 +6339,7 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
+          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6371,7 +6371,7 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over the picture</t>
+          <t xml:space="preserve">the white closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6403,7 +6403,7 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over the picture</t>
+          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6435,7 +6435,7 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over the picture</t>
+          <t xml:space="preserve">the blue closing fading in over the picture</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6467,7 +6467,7 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over the picture</t>
+          <t xml:space="preserve">the blue closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6499,7 +6499,7 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summary</t>
+          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">the white closing fading in over the picture</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6531,7 +6531,7 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">the white closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6563,7 +6563,7 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.summary</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6595,7 +6595,7 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6627,7 +6627,7 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6659,7 +6659,7 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6691,7 +6691,7 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6723,7 +6723,7 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6755,7 +6755,7 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -6787,7 +6787,7 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -6819,7 +6819,7 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -6851,7 +6851,7 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -6883,7 +6883,7 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -6915,7 +6915,7 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -6947,22 +6947,22 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -6979,22 +6979,22 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 5: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7011,7 +7011,7 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="2">
@@ -7043,7 +7043,7 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="2">
@@ -7075,7 +7075,7 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
@@ -7107,7 +7107,7 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,7 +7203,7 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7299,22 +7299,22 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,22 +7331,22 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 5: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,7 +7395,7 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
@@ -7427,22 +7427,22 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: said when the video starts being made</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7459,22 +7459,22 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,17 +7491,17 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the heading of the device check</t>
+          <t xml:space="preserve">Step 5: said when the video starts being made</t>
         </is>
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
@@ -7523,7 +7523,7 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7555,7 +7555,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7587,7 +7587,7 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7619,7 +7619,7 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7651,7 +7651,7 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,7 +7683,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,7 +7715,7 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7747,7 +7747,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
@@ -7811,17 +7811,17 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
@@ -7843,17 +7843,17 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: the heading of the device check</t>
         </is>
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
@@ -7875,22 +7875,22 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,22 +7907,22 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: one reason in the device check</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
@@ -7971,7 +7971,7 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
@@ -8003,7 +8003,7 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8195,7 +8195,7 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,7 +8227,7 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8259,7 +8259,7 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8291,7 +8291,7 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
@@ -8323,7 +8323,7 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
@@ -8355,7 +8355,7 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
@@ -8387,7 +8387,7 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8419,7 +8419,7 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
@@ -8451,22 +8451,22 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8483,17 +8483,17 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 5: one reason in the device check</t>
         </is>
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
@@ -8515,7 +8515,7 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8611,17 +8611,17 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
@@ -8643,22 +8643,22 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 5: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
@@ -8707,22 +8707,22 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
@@ -8771,22 +8771,22 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -8803,7 +8803,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
@@ -8835,7 +8835,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
@@ -8867,7 +8867,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
@@ -8899,7 +8899,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
@@ -8931,7 +8931,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
@@ -8963,7 +8963,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
@@ -8995,7 +8995,7 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
@@ -9027,7 +9027,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
@@ -9059,7 +9059,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
@@ -9091,7 +9091,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,7 +9123,7 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
@@ -9155,7 +9155,7 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9187,7 +9187,7 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
@@ -9219,7 +9219,7 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
@@ -9251,22 +9251,22 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9283,22 +9283,22 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 5: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9315,7 +9315,7 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9347,7 +9347,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9379,7 +9379,7 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9411,7 +9411,7 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9443,22 +9443,22 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9475,22 +9475,22 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
@@ -9955,7 +9955,7 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,7 +9987,7 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
@@ -10019,7 +10019,7 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10051,7 +10051,7 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
@@ -10083,7 +10083,7 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
@@ -10115,7 +10115,7 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
@@ -10147,7 +10147,7 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
@@ -10179,7 +10179,7 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
@@ -10211,17 +10211,17 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
@@ -10243,22 +10243,22 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10275,7 +10275,7 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10307,7 +10307,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
@@ -10339,7 +10339,7 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10371,22 +10371,22 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10403,22 +10403,22 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10435,22 +10435,22 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10467,7 +10467,7 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10499,7 +10499,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
@@ -10563,7 +10563,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10595,7 +10595,7 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10627,7 +10627,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,12 +10797,12 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -10819,7 +10819,7 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,7 +10851,7 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
@@ -10883,7 +10883,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,7 +10915,7 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,7 +10947,7 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
@@ -10979,7 +10979,7 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
@@ -11011,7 +11011,7 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,7 +11043,7 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
@@ -11075,7 +11075,7 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
@@ -11107,7 +11107,7 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
@@ -11139,7 +11139,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
@@ -11171,7 +11171,7 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11181,12 +11181,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11203,7 +11203,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
@@ -11235,22 +11235,22 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11267,17 +11267,17 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
@@ -11299,7 +11299,7 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
@@ -11331,17 +11331,17 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
@@ -11363,17 +11363,17 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11427,7 +11427,7 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
@@ -11459,7 +11459,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11491,7 +11491,7 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
@@ -11523,7 +11523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
@@ -11555,7 +11555,7 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
@@ -11587,7 +11587,7 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
@@ -11619,7 +11619,7 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
@@ -11651,7 +11651,7 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -11683,7 +11683,7 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,7 +11715,7 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,7 +11747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
@@ -11779,7 +11779,7 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
@@ -11811,7 +11811,7 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,22 +11843,22 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -11875,22 +11875,22 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -11907,22 +11907,22 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,22 +11939,22 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,22 +11971,22 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12003,7 +12003,7 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
@@ -12035,7 +12035,7 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
@@ -12067,7 +12067,7 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
@@ -12099,22 +12099,22 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12131,22 +12131,22 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12163,7 +12163,7 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12195,22 +12195,22 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12227,22 +12227,22 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12259,7 +12259,7 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12291,7 +12291,7 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12323,7 +12323,7 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12355,17 +12355,17 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
@@ -12387,22 +12387,22 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12419,7 +12419,7 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
@@ -12451,7 +12451,7 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,22 +12483,22 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.enforcement.heading</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Equality Advisory and Support Service</t>
+          <t xml:space="preserve">Enforcement procedure</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12515,22 +12515,22 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.heading</t>
+          <t xml:space="preserve">statement.enforcement.text</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance status</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12547,7 +12547,7 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.text</t>
+          <t xml:space="preserve">statement.enforcement.service</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12557,12 +12557,12 @@
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12579,7 +12579,7 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.heading</t>
+          <t xml:space="preserve">statement.compliance.heading</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How we tested this tool</t>
+          <t xml:space="preserve">Compliance status</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
@@ -12611,7 +12611,7 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.wave</t>
+          <t xml:space="preserve">statement.compliance.text</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12621,12 +12621,12 @@
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12643,17 +12643,17 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.automated</t>
+          <t xml:space="preserve">statement.testing.heading</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+          <t xml:space="preserve">How we tested this tool</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
@@ -12675,7 +12675,7 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.manual</t>
+          <t xml:space="preserve">statement.testing.wave</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12685,12 +12685,12 @@
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12707,17 +12707,17 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.heading</t>
+          <t xml:space="preserve">statement.testing.automated</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What we plan to test next</t>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
@@ -12739,7 +12739,7 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.intro</t>
+          <t xml:space="preserve">statement.testing.manual</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -12749,12 +12749,12 @@
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -12771,22 +12771,22 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.0</t>
+          <t xml:space="preserve">statement.plans.heading</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using the tool with a keyboard alone</t>
+          <t xml:space="preserve">What we plan to test next</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -12803,22 +12803,22 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.1</t>
+          <t xml:space="preserve">statement.plans.intro</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -12835,7 +12835,7 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.2</t>
+          <t xml:space="preserve">statement.plans.items.0</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
@@ -12867,7 +12867,7 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.3</t>
+          <t xml:space="preserve">statement.plans.items.1</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Windows contrast themes</t>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,7 +12899,7 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.4</t>
+          <t xml:space="preserve">statement.plans.items.2</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -12909,12 +12909,12 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -12931,7 +12931,7 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.5</t>
+          <t xml:space="preserve">statement.plans.items.3</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+          <t xml:space="preserve">Windows contrast themes</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,22 +12963,22 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.heading</t>
+          <t xml:space="preserve">statement.plans.items.4</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About this statement</t>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,22 +12995,22 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.dates</t>
+          <t xml:space="preserve">statement.plans.items.5</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13027,22 +13027,22 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.intro</t>
+          <t xml:space="preserve">statement.about.heading</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For help with this tool:</t>
+          <t xml:space="preserve">About this statement</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,22 +13059,22 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.creators</t>
+          <t xml:space="preserve">statement.about.dates</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the creators team</t>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13091,22 +13091,22 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.learningContent</t>
+          <t xml:space="preserve">footer.contact.intro</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
         </is>
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the learning content team</t>
+          <t xml:space="preserve">For help with this tool:</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13123,22 +13123,22 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">footer.contact.creators</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">Email the creators team</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13155,22 +13155,22 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">footer.contact.learningContent</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">Email the learning content team</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13187,22 +13187,22 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">save.pickerDescription</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
         </is>
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,7 +13219,7 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">save.stem</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">video</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,7 +13251,7 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">save.marks.branded</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">branded</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13283,7 +13283,7 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">save.marks.levelled</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">levelled</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13315,22 +13315,22 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">save.marks.converted</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">converted</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,22 +13347,22 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">save.fileName</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,7 +13379,7 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">save.downloadIos</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13411,22 +13411,22 @@
     <row r="418">
       <c r="A418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">save.downloadOther</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">Saving to your downloads folder</t>
         </is>
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13443,22 +13443,22 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">save.download</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 5: saving the finished video</t>
         </is>
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13475,7 +13475,7 @@
     <row r="420">
       <c r="A420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">format.unknown</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13507,7 +13507,7 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">format.lessThanASecond</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">less than a second</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13539,7 +13539,7 @@
     <row r="422">
       <c r="A422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">format.fewSeconds</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">a few seconds</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13571,7 +13571,7 @@
     <row r="423">
       <c r="A423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">format.frameRate</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">{rate} frames a second</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13603,7 +13603,7 @@
     <row r="424">
       <c r="A424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">format.resolution</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13613,12 +13613,12 @@
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">{width} × {height}</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13635,7 +13635,7 @@
     <row r="425">
       <c r="A425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">format.channels.mono</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">Mono (one channel)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="2">
@@ -13667,7 +13667,7 @@
     <row r="426">
       <c r="A426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">format.channels.stereo</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">Stereo (two channels)</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="2">
@@ -13699,30 +13699,94 @@
     <row r="427">
       <c r="A427" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr" s="2">
+      <c r="B429" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr" s="2">
+      <c r="C429" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr" s="2">
+      <c r="D429" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr" s="2">
+      <c r="E429" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -7075,7 +7075,7 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.summaryWithCard</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">Made from {name}: a {seconds}-second title card, then {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {name}, {seconds}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {seconds} is a number of seconds; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7107,7 +7107,7 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,7 +7203,7 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7299,7 +7299,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,7 +7331,7 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,7 +7395,7 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7459,7 +7459,7 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,22 +7491,22 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7523,7 +7523,7 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
@@ -7555,7 +7555,7 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
@@ -7587,7 +7587,7 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
@@ -7619,7 +7619,7 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
@@ -7651,7 +7651,7 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,7 +7683,7 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,7 +7715,7 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7747,7 +7747,7 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -7811,7 +7811,7 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -7843,22 +7843,22 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
@@ -7971,22 +7971,22 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: said when the video starts being made</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8003,17 +8003,17 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: said when the video starts being made</t>
         </is>
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8195,7 +8195,7 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,7 +8227,7 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8259,7 +8259,7 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8291,7 +8291,7 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
@@ -8323,7 +8323,7 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
@@ -8355,17 +8355,17 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
@@ -8387,7 +8387,7 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
@@ -8419,22 +8419,22 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8451,7 +8451,7 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
@@ -8483,7 +8483,7 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
@@ -8515,7 +8515,7 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8643,7 +8643,7 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8707,7 +8707,7 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8771,7 +8771,7 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -8803,7 +8803,7 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8813,12 +8813,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -8835,7 +8835,7 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -8867,7 +8867,7 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -8899,7 +8899,7 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -8931,7 +8931,7 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
@@ -8963,7 +8963,7 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
@@ -8995,22 +8995,22 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9027,7 +9027,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9059,7 +9059,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9091,7 +9091,7 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,7 +9123,7 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9155,22 +9155,22 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9187,7 +9187,7 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
@@ -9219,7 +9219,7 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
@@ -9251,22 +9251,22 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9283,22 +9283,22 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9315,7 +9315,7 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
@@ -9347,7 +9347,7 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
@@ -9379,7 +9379,7 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
@@ -9411,7 +9411,7 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
@@ -9795,22 +9795,22 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -9955,7 +9955,7 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,22 +9987,22 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10019,7 +10019,7 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
@@ -10051,7 +10051,7 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
@@ -10083,7 +10083,7 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
@@ -10115,7 +10115,7 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
@@ -10147,7 +10147,7 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
@@ -10179,7 +10179,7 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
@@ -10211,7 +10211,7 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
@@ -10243,7 +10243,7 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
@@ -10275,7 +10275,7 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
@@ -10307,7 +10307,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
@@ -10339,7 +10339,7 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
@@ -10371,7 +10371,7 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
@@ -10403,7 +10403,7 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
@@ -10435,7 +10435,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
@@ -10467,7 +10467,7 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
@@ -10499,7 +10499,7 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10563,7 +10563,7 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
@@ -10595,7 +10595,7 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
@@ -10627,7 +10627,7 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.what</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.next</t>
+          <t xml:space="preserve">failure.titleCardRefused.what</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
+          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.titleCardRefused.next</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
@@ -10819,17 +10819,17 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,7 +10851,7 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -10883,7 +10883,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,7 +10915,7 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,7 +10947,7 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -10979,17 +10979,17 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
@@ -11011,22 +11011,22 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11043,7 +11043,7 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11075,7 +11075,7 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11085,12 +11085,12 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11107,7 +11107,7 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11139,7 +11139,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11171,7 +11171,7 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11181,12 +11181,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11203,7 +11203,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
@@ -11235,7 +11235,7 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11267,7 +11267,7 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11299,7 +11299,7 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11331,7 +11331,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11363,7 +11363,7 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
@@ -11427,7 +11427,7 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
@@ -11459,7 +11459,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
@@ -11491,7 +11491,7 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
@@ -11523,7 +11523,7 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
@@ -11555,7 +11555,7 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
@@ -11587,7 +11587,7 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
@@ -11619,7 +11619,7 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
@@ -11651,7 +11651,7 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
@@ -11683,7 +11683,7 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
@@ -11715,7 +11715,7 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
@@ -11747,7 +11747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
@@ -11779,7 +11779,7 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,7 +11811,7 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,17 +11843,17 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
@@ -11875,7 +11875,7 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
@@ -11907,7 +11907,7 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
@@ -11939,17 +11939,17 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
@@ -11971,7 +11971,7 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12003,7 +12003,7 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,7 +12035,7 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12067,7 +12067,7 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
@@ -12099,7 +12099,7 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
@@ -12131,7 +12131,7 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
@@ -12163,7 +12163,7 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
@@ -12195,7 +12195,7 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
@@ -12227,7 +12227,7 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
@@ -12259,7 +12259,7 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12291,7 +12291,7 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
@@ -12323,7 +12323,7 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12355,7 +12355,7 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12387,7 +12387,7 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12419,7 +12419,7 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
@@ -12451,22 +12451,22 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,22 +12483,22 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12515,7 +12515,7 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12547,22 +12547,22 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12579,7 +12579,7 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
@@ -12611,7 +12611,7 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
@@ -12643,7 +12643,7 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12653,7 +12653,7 @@
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
@@ -12675,7 +12675,7 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
@@ -12707,22 +12707,22 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12739,17 +12739,17 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
@@ -12771,22 +12771,22 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -12803,22 +12803,22 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -12835,7 +12835,7 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -12867,7 +12867,7 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,7 +12899,7 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
@@ -12931,7 +12931,7 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,22 +12963,22 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,22 +12995,22 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13027,22 +13027,22 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,22 +13059,22 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">statement.enforcement.heading</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">Enforcement procedure</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13091,7 +13091,7 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.enforcement.text</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13101,12 +13101,12 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Equality Advisory and Support Service</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13123,22 +13123,22 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.heading</t>
+          <t xml:space="preserve">statement.enforcement.service</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance status</t>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13155,22 +13155,22 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.text</t>
+          <t xml:space="preserve">statement.compliance.heading</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+          <t xml:space="preserve">Compliance status</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13187,22 +13187,22 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.heading</t>
+          <t xml:space="preserve">statement.compliance.text</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How we tested this tool</t>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,22 +13219,22 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.wave</t>
+          <t xml:space="preserve">statement.testing.heading</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+          <t xml:space="preserve">How we tested this tool</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,7 +13251,7 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.automated</t>
+          <t xml:space="preserve">statement.testing.wave</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13283,7 +13283,7 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.manual</t>
+          <t xml:space="preserve">statement.testing.automated</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13315,22 +13315,22 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.heading</t>
+          <t xml:space="preserve">statement.testing.manual</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What we plan to test next</t>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,22 +13347,22 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.intro</t>
+          <t xml:space="preserve">statement.plans.heading</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+          <t xml:space="preserve">What we plan to test next</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,22 +13379,22 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.0</t>
+          <t xml:space="preserve">statement.plans.intro</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using the tool with a keyboard alone</t>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13411,7 +13411,7 @@
     <row r="418">
       <c r="A418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.1</t>
+          <t xml:space="preserve">statement.plans.items.0</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="C418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
         </is>
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13443,7 +13443,7 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.2</t>
+          <t xml:space="preserve">statement.plans.items.1</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13453,12 +13453,12 @@
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13475,7 +13475,7 @@
     <row r="420">
       <c r="A420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.3</t>
+          <t xml:space="preserve">statement.plans.items.2</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Windows contrast themes</t>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13507,7 +13507,7 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.4</t>
+          <t xml:space="preserve">statement.plans.items.3</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+          <t xml:space="preserve">Windows contrast themes</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13539,7 +13539,7 @@
     <row r="422">
       <c r="A422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.5</t>
+          <t xml:space="preserve">statement.plans.items.4</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13571,22 +13571,22 @@
     <row r="423">
       <c r="A423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.heading</t>
+          <t xml:space="preserve">statement.plans.items.5</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About this statement</t>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13603,22 +13603,22 @@
     <row r="424">
       <c r="A424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.dates</t>
+          <t xml:space="preserve">statement.about.heading</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+          <t xml:space="preserve">About this statement</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13635,22 +13635,22 @@
     <row r="425">
       <c r="A425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.intro</t>
+          <t xml:space="preserve">statement.about.dates</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For help with this tool:</t>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13667,22 +13667,22 @@
     <row r="426">
       <c r="A426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.creators</t>
+          <t xml:space="preserve">footer.contact.intro</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
         </is>
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the creators team</t>
+          <t xml:space="preserve">For help with this tool:</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -13699,22 +13699,22 @@
     <row r="427">
       <c r="A427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.learningContent</t>
+          <t xml:space="preserve">footer.contact.creators</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
         </is>
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the learning content team</t>
+          <t xml:space="preserve">Email the creators team</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -13731,22 +13731,22 @@
     <row r="428">
       <c r="A428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">footer.contact.learningContent</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
         </is>
       </c>
       <c r="C428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">Email the learning content team</t>
         </is>
       </c>
       <c r="D428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -13763,22 +13763,22 @@
     <row r="429">
       <c r="A429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">save.pickerDescription</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
         </is>
       </c>
       <c r="C429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
         </is>
       </c>
       <c r="D429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -13795,7 +13795,7 @@
     <row r="430">
       <c r="A430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">save.stem</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -13805,12 +13805,12 @@
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">video</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -13827,7 +13827,7 @@
     <row r="431">
       <c r="A431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">save.marks.branded</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">branded</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -13859,7 +13859,7 @@
     <row r="432">
       <c r="A432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">save.marks.levelled</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="C432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">levelled</t>
         </is>
       </c>
       <c r="D432" t="inlineStr" s="2">
@@ -13891,7 +13891,7 @@
     <row r="433">
       <c r="A433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">save.marks.converted</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="C433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">converted</t>
         </is>
       </c>
       <c r="D433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -13923,22 +13923,22 @@
     <row r="434">
       <c r="A434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">save.fileName</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: saving the finished video</t>
+          <t xml:space="preserve">The name suggested for the saved file</t>
         </is>
       </c>
       <c r="C434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
         </is>
       </c>
       <c r="D434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -13955,7 +13955,7 @@
     <row r="435">
       <c r="A435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">save.downloadIos</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="C435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
         </is>
       </c>
       <c r="D435" t="inlineStr" s="2">
@@ -13987,7 +13987,7 @@
     <row r="436">
       <c r="A436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">save.downloadOther</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="C436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">Saving to your downloads folder</t>
         </is>
       </c>
       <c r="D436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14019,22 +14019,22 @@
     <row r="437">
       <c r="A437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">save.download</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">Step 6: saving the finished video</t>
         </is>
       </c>
       <c r="C437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
         </is>
       </c>
       <c r="D437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14051,7 +14051,7 @@
     <row r="438">
       <c r="A438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">format.unknown</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="C438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="D438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14083,7 +14083,7 @@
     <row r="439">
       <c r="A439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">format.lessThanASecond</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="C439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">less than a second</t>
         </is>
       </c>
       <c r="D439" t="inlineStr" s="2">
@@ -14115,7 +14115,7 @@
     <row r="440">
       <c r="A440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">format.fewSeconds</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14125,12 +14125,12 @@
       </c>
       <c r="C440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">a few seconds</t>
         </is>
       </c>
       <c r="D440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14147,7 +14147,7 @@
     <row r="441">
       <c r="A441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">format.frameRate</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="C441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">{rate} frames a second</t>
         </is>
       </c>
       <c r="D441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14179,7 +14179,7 @@
     <row r="442">
       <c r="A442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">format.resolution</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="C442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">{width} × {height}</t>
         </is>
       </c>
       <c r="D442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14211,7 +14211,7 @@
     <row r="443">
       <c r="A443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">format.channels.mono</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">Mono (one channel)</t>
         </is>
       </c>
       <c r="D443" t="inlineStr" s="2">
@@ -14243,7 +14243,7 @@
     <row r="444">
       <c r="A444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">format.channels.stereo</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="C444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">Stereo (two channels)</t>
         </is>
       </c>
       <c r="D444" t="inlineStr" s="2">
@@ -14275,7 +14275,7 @@
     <row r="445">
       <c r="A445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">format.channels.surround51</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">5.1 surround</t>
         </is>
       </c>
       <c r="D445" t="inlineStr" s="2">
@@ -14307,30 +14307,62 @@
     <row r="446">
       <c r="A446" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr" s="2">
+      <c r="B447" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr" s="2">
+      <c r="C447" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr" s="2">
+      <c r="D447" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr" s="2">
+      <c r="E447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -3821,12 +3821,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used for a student submission.</t>
+          <t xml:space="preserve">A student submission always has a title card.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Why the checkbox titleCard.add cannot be ticked. Use the same words for "student submission" as videoKind.options.submission.</t>
+          <t xml:space="preserve">Why the checkbox titleCard.add is ticked and cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4003,17 +4003,17 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.legend</t>
+          <t xml:space="preserve">titleCard.submission.assignment</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Closing branding</t>
+          <t xml:space="preserve">Assignment title or number</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="2">
@@ -4035,17 +4035,17 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.typeLabel</t>
+          <t xml:space="preserve">titleCard.submission.module</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation type</t>
+          <t xml:space="preserve">Module code and title</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="2">
@@ -4067,17 +4067,17 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.cut</t>
+          <t xml:space="preserve">titleCard.submission.convenor</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cut</t>
+          <t xml:space="preserve">Module convenor or tutor</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="2">
@@ -4099,17 +4099,17 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.fade</t>
+          <t xml:space="preserve">titleCard.submission.ids</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Fade</t>
+          <t xml:space="preserve">Student ID numbers</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="2">
@@ -4131,22 +4131,22 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.slide</t>
+          <t xml:space="preserve">titleCard.submission.idsHelper</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Slide</t>
+          <t xml:space="preserve">Each student ID (identity) number is 8 digits. Type one to eight, with spaces, commas or new lines between them. Do not add names.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A University student ID number is 8 digits. Use the same words for "student ID number" as titleCard.submission.ids.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4163,22 +4163,22 @@
     <row r="129">
       <c r="A129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.types.none</t>
+          <t xml:space="preserve">titleCard.submission.filled</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3, Title card, for a student submission: the four fields for the card shown before the video</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">The card also shows the running time, {running}, and today’s date, marked as the date the card was made, not the submission date.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Use the same words for "running time" as titleCard.card.running, and for "the date the card was made" as titleCard.card.made. Keep {running} as written: {running} is a length of time as a clock shows it, like 12:34.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4195,17 +4195,17 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsetLabel</t>
+          <t xml:space="preserve">titleCard.submission.missing.assignment</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside a student submission's field left empty, when Create is pressed</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Animation onset</t>
+          <t xml:space="preserve">Type the assignment’s title or number.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="2">
@@ -4227,17 +4227,17 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.existing</t>
+          <t xml:space="preserve">titleCard.submission.missing.module</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside a student submission's field left empty, when Create is pressed</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">Type the module’s code and title.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="2">
@@ -4259,17 +4259,17 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.onsets.freeze</t>
+          <t xml:space="preserve">titleCard.submission.missing.convenor</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside a student submission's field left empty, when Create is pressed</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">Type the name of the module convenor or tutor.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="2">
@@ -4291,17 +4291,17 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpLabel</t>
+          <t xml:space="preserve">titleCard.submission.missing.ids</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside a student submission's field left empty, when Create is pressed</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About animation onset</t>
+          <t xml:space="preserve">Type at least one student ID number.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="2">
@@ -4323,22 +4323,22 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingTerm</t>
+          <t xml:space="preserve">titleCard.submission.idNotAnId</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside the student ID numbers, when Create is pressed</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over existing</t>
+          <t xml:space="preserve">“{id}” is not a student ID number. Each is 8 digits.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {id} as written: {id} is what the student typed as a student ID number, like 20412345.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4355,22 +4355,22 @@
     <row r="135">
       <c r="A135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpExistingText</t>
+          <t xml:space="preserve">titleCard.submission.idTwice</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside the student ID numbers, when Create is pressed</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
+          <t xml:space="preserve">{id} is in the list twice. Take one out.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve">Keep {id} as written: {id} is what the student typed as a student ID number, like 20412345.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4387,22 +4387,22 @@
     <row r="136">
       <c r="A136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeTerm</t>
+          <t xml:space="preserve">titleCard.submission.idsTooMany</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Step 3: the error beside the student ID numbers, when Create is pressed</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Over generated freeze frame</t>
+          <t xml:space="preserve">That is {count} numbers. The card takes up to {max}.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {count}, {max} as written: {count} is a number; {max} is a number.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4419,22 +4419,22 @@
     <row r="137">
       <c r="A137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.helpFreezeText</t>
+          <t xml:space="preserve">titleCard.card.module</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
+          <t xml:space="preserve">Module</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4451,17 +4451,17 @@
     <row r="138">
       <c r="A138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colourLabel</t>
+          <t xml:space="preserve">titleCard.card.convenor</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Colour</t>
+          <t xml:space="preserve">Convenor or tutor</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="2">
@@ -4483,22 +4483,22 @@
     <row r="139">
       <c r="A139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.blue</t>
+          <t xml:space="preserve">titleCard.card.ids.one</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Blue</t>
+          <t xml:space="preserve">Student ID number</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve">Used when the count is 1.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4515,22 +4515,22 @@
     <row r="140">
       <c r="A140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.colours.white</t>
+          <t xml:space="preserve">titleCard.card.ids.other</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">White</t>
+          <t xml:space="preserve">Student ID numbers</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4547,22 +4547,22 @@
     <row r="141">
       <c r="A141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalLabel</t>
+          <t xml:space="preserve">titleCard.card.running</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">Running time</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4579,22 +4579,22 @@
     <row r="142">
       <c r="A142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalWords</t>
+          <t xml:space="preserve">titleCard.card.made</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Internal use only</t>
+          <t xml:space="preserve">Card made</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4611,22 +4611,22 @@
     <row r="143">
       <c r="A143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.cut</t>
+          <t xml:space="preserve">titleCard.card.madeValue</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4, Closing branding</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on a student submission's title card, as a label before what the student typed</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with Cut.</t>
+          <t xml:space="preserve">{date} — not the submission date</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
+          <t xml:space="preserve">Drawn after titleCard.card.made. It must say plainly that {date} is not the date the work was submitted. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4643,7 +4643,7 @@
     <row r="144">
       <c r="A144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.notUsedWith.none</t>
+          <t xml:space="preserve">closing.legend</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not used with None.</t>
+          <t xml:space="preserve">Closing branding</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4675,7 +4675,7 @@
     <row r="145">
       <c r="A145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.internalForSubmission</t>
+          <t xml:space="preserve">closing.typeLabel</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Always on for a student submission.</t>
+          <t xml:space="preserve">Animation type</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Why the "Internal use only" checkbox cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4707,17 +4707,17 @@
     <row r="146">
       <c r="A146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.none</t>
+          <t xml:space="preserve">closing.types.cut</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No University closing will be added.</t>
+          <t xml:space="preserve">Cut</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="2">
@@ -4739,22 +4739,22 @@
     <row r="147">
       <c r="A147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.one</t>
+          <t xml:space="preserve">closing.types.fade</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} second.</t>
+          <t xml:space="preserve">Fade</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4771,22 +4771,22 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.adds.other</t>
+          <t xml:space="preserve">closing.types.slide</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds {count} seconds.</t>
+          <t xml:space="preserve">Slide</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -4803,22 +4803,22 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.internal</t>
+          <t xml:space="preserve">closing.types.none</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The card says “{words}” under the logo.</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -4835,22 +4835,22 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.blue</t>
+          <t xml:space="preserve">closing.onsetLabel</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
+          <t xml:space="preserve">Animation onset</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -4867,22 +4867,22 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.cut.white</t>
+          <t xml:space="preserve">closing.onsets.existing</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -4899,22 +4899,22 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
+          <t xml:space="preserve">closing.onsets.freeze</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -4931,22 +4931,22 @@
     <row r="153">
       <c r="A153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
+          <t xml:space="preserve">closing.helpLabel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">About animation onset</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -4963,22 +4963,22 @@
     <row r="154">
       <c r="A154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
+          <t xml:space="preserve">closing.helpExistingTerm</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">Over existing</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -4995,22 +4995,22 @@
     <row r="155">
       <c r="A155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
+          <t xml:space="preserve">closing.helpExistingText</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
+          <t xml:space="preserve">— the closing plays over the last second of your video. It covers that second as it builds.</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Follows "Over existing" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5027,22 +5027,22 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
+          <t xml:space="preserve">closing.helpFreezeTerm</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Over generated freeze frame</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5059,22 +5059,22 @@
     <row r="157">
       <c r="A157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
+          <t xml:space="preserve">closing.helpFreezeText</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">— your last frame is held for one extra second. The closing plays over that, so nothing in your video is covered.</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Follows "Over generated freeze frame" on the same line, so it starts with a dash.</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5091,22 +5091,22 @@
     <row r="158">
       <c r="A158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
+          <t xml:space="preserve">closing.colourLabel</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Colour</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5123,22 +5123,22 @@
     <row r="159">
       <c r="A159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
+          <t xml:space="preserve">closing.colours.blue</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
+          <t xml:space="preserve">Blue</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5155,22 +5155,22 @@
     <row r="160">
       <c r="A160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.legend</t>
+          <t xml:space="preserve">closing.colours.white</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, File size / quality</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File size / quality</t>
+          <t xml:space="preserve">White</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5187,22 +5187,22 @@
     <row r="161">
       <c r="A161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.best</t>
+          <t xml:space="preserve">closing.internalLabel</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, File size / quality</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Larger / better</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
+          <t xml:space="preserve">The label of a checkbox that adds the words of closing.internalWords to the closing card. Use the same words.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5219,22 +5219,22 @@
     <row r="162">
       <c r="A162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.labels.smaller</t>
+          <t xml:space="preserve">closing.internalWords</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, File size / quality</t>
+          <t xml:space="preserve">Not on the page: drawn on the finished video itself, on the closing card, under the University logo</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Smaller / reduced</t>
+          <t xml:space="preserve">Internal use only</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
+          <t xml:space="preserve">Drawn in bold under the logo at the end of the video, like a stamp on a document, so it must fit on one line: keep it about as short as the English. A change here means the closing videos are built again.</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5251,22 +5251,22 @@
     <row r="163">
       <c r="A163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.best</t>
+          <t xml:space="preserve">closing.notUsedWith.cut</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, File size / quality</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
+          <t xml:space="preserve">Not used with Cut.</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Names the animation type "Cut"; use the same word as closing.types.cut.</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5283,22 +5283,22 @@
     <row r="164">
       <c r="A164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preset.details.smaller</t>
+          <t xml:space="preserve">closing.notUsedWith.none</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 5, File size / quality</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For messaging or email etc.</t>
+          <t xml:space="preserve">Not used with None.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Names the animation type "None"; use the same word as closing.types.none.</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5315,22 +5315,22 @@
     <row r="165">
       <c r="A165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.note</t>
+          <t xml:space="preserve">closing.internalForSubmission</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4, Closing branding</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
+          <t xml:space="preserve">Always on for a student submission.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Why the "Internal use only" checkbox cannot be unticked. Use the same words for "student submission" as videoKind.options.submission.</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5347,17 +5347,17 @@
     <row r="166">
       <c r="A166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceProgress</t>
+          <t xml:space="preserve">closing.result.none</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Announce progress</t>
+          <t xml:space="preserve">No University closing will be added.</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="2">
@@ -5379,22 +5379,22 @@
     <row r="167">
       <c r="A167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.announceHelp</t>
+          <t xml:space="preserve">closing.result.adds.one</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
+          <t xml:space="preserve">Adds {count} second.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5411,22 +5411,22 @@
     <row r="168">
       <c r="A168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.progressLabel</t>
+          <t xml:space="preserve">closing.result.adds.other</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video</t>
+          <t xml:space="preserve">Adds {count} seconds.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5443,22 +5443,22 @@
     <row r="169">
       <c r="A169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.create</t>
+          <t xml:space="preserve">closing.result.internal</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Create the video</t>
+          <t xml:space="preserve">The card says “{words}” under the logo.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {words} as written: {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5475,22 +5475,22 @@
     <row r="170">
       <c r="A170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.cancel</t>
+          <t xml:space="preserve">closing.result.cut.blue</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancel</t>
+          <t xml:space="preserve">Your video cuts to the blue closing card. {adds}</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5507,22 +5507,22 @@
     <row r="171">
       <c r="A171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.continueAnyway</t>
+          <t xml:space="preserve">closing.result.cut.white</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Continue anyway</t>
+          <t xml:space="preserve">Your video cuts to the white closing card. {adds}</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5539,22 +5539,22 @@
     <row r="172">
       <c r="A172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopCheck</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop the check</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5571,22 +5571,22 @@
     <row r="173">
       <c r="A173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.checkAgain</t>
+          <t xml:space="preserve">closing.result.overFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check again</t>
+          <t xml:space="preserve">Your last frame is held while the blue closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5603,22 +5603,22 @@
     <row r="174">
       <c r="A174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.stopSaving</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.fade</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stop saving</t>
+          <t xml:space="preserve">Your last frame is held while the white closing fades in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5635,22 +5635,22 @@
     <row r="175">
       <c r="A175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.save</t>
+          <t xml:space="preserve">closing.result.overFreeze.white.slide</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save the video</t>
+          <t xml:space="preserve">Your last frame is held while the white closing slides in, so nothing is covered. {adds}</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5667,22 +5667,22 @@
     <row r="176">
       <c r="A176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.saved</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.fade</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved</t>
+          <t xml:space="preserve">The blue closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5699,22 +5699,22 @@
     <row r="177">
       <c r="A177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.discard</t>
+          <t xml:space="preserve">closing.result.overPicture.blue.slide</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Discard it and start again</t>
+          <t xml:space="preserve">The blue closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5731,22 +5731,22 @@
     <row r="178">
       <c r="A178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.keep</t>
+          <t xml:space="preserve">closing.result.overPicture.white.fade</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep it</t>
+          <t xml:space="preserve">The white closing fades in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5763,22 +5763,22 @@
     <row r="179">
       <c r="A179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedMaking</t>
+          <t xml:space="preserve">closing.result.overPicture.white.slide</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 4: the line under the controls saying what the closing will do</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being made.</t>
+          <t xml:space="preserve">The white closing slides in over your last second of video, covering it as it builds. {adds}</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in. Keep {adds} as written: {adds} is the sentence from closing.result.adds.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -5795,17 +5795,17 @@
     <row r="180">
       <c r="A180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">create.lockedSaving</t>
+          <t xml:space="preserve">preset.legend</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
+          <t xml:space="preserve">Step 5, File size / quality</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Locked while your video is being saved.</t>
+          <t xml:space="preserve">File size / quality</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="2">
@@ -5827,22 +5827,22 @@
     <row r="181">
       <c r="A181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checking</t>
+          <t xml:space="preserve">preset.labels.best</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, File size / quality</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking this video against your device…</t>
+          <t xml:space="preserve">Larger / better</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the larger output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -5859,22 +5859,22 @@
     <row r="182">
       <c r="A182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.checkStopped</t>
+          <t xml:space="preserve">preset.labels.smaller</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, File size / quality</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Check stopped.</t>
+          <t xml:space="preserve">Smaller / reduced</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of the smaller output. Other rows quote it.</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -5891,17 +5891,17 @@
     <row r="183">
       <c r="A183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.stoppingSave</t>
+          <t xml:space="preserve">preset.details.best</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, File size / quality</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stopping the save…</t>
+          <t xml:space="preserve">For EchoVideo or YouTube etc.</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="2">
@@ -5923,17 +5923,17 @@
     <row r="184">
       <c r="A184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelling</t>
+          <t xml:space="preserve">preset.details.smaller</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 5, File size / quality</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelling…</t>
+          <t xml:space="preserve">For messaging or email etc.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="2">
@@ -5955,17 +5955,17 @@
     <row r="185">
       <c r="A185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.cancelled</t>
+          <t xml:space="preserve">create.note</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
+          <t xml:space="preserve">The finished video is kept here until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="2">
@@ -5987,17 +5987,17 @@
     <row r="186">
       <c r="A186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saving</t>
+          <t xml:space="preserve">create.announceProgress</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving…</t>
+          <t xml:space="preserve">Announce progress</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="2">
@@ -6019,17 +6019,17 @@
     <row r="187">
       <c r="A187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveStopped</t>
+          <t xml:space="preserve">create.announceHelp</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
+          <t xml:space="preserve">Says each stage out loud for a screen reader as the video is made. The result is always announced.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="2">
@@ -6051,17 +6051,17 @@
     <row r="188">
       <c r="A188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.notSaved</t>
+          <t xml:space="preserve">create.progressLabel</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
+          <t xml:space="preserve">Creating your video</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="2">
@@ -6083,17 +6083,17 @@
     <row r="189">
       <c r="A189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.refusedSource</t>
+          <t xml:space="preserve">create.create</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
+          <t xml:space="preserve">Create the video</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="2">
@@ -6115,17 +6115,17 @@
     <row r="190">
       <c r="A190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saved</t>
+          <t xml:space="preserve">create.cancel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
+          <t xml:space="preserve">Cancel</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="2">
@@ -6147,17 +6147,17 @@
     <row r="191">
       <c r="A191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.saveFailed</t>
+          <t xml:space="preserve">create.continueAnyway</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
+          <t xml:space="preserve">Continue anyway</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="2">
@@ -6179,22 +6179,22 @@
     <row r="192">
       <c r="A192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.storageWayOut</t>
+          <t xml:space="preserve">create.stopCheck</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
+          <t xml:space="preserve">Stop the check</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6211,22 +6211,22 @@
     <row r="193">
       <c r="A193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.creating</t>
+          <t xml:space="preserve">create.checkAgain</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Creating your video. {notice}</t>
+          <t xml:space="preserve">Check again</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6243,17 +6243,17 @@
     <row r="194">
       <c r="A194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.ready</t>
+          <t xml:space="preserve">create.stopSaving</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is ready.</t>
+          <t xml:space="preserve">Stop saving</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="2">
@@ -6275,22 +6275,22 @@
     <row r="195">
       <c r="A195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.couldNotCreate</t>
+          <t xml:space="preserve">create.save</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video could not be created. {sentence}</t>
+          <t xml:space="preserve">Save the video</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6307,22 +6307,22 @@
     <row r="196">
       <c r="A196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">status.verdictSpoken</t>
+          <t xml:space="preserve">create.saved</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Device check complete. {heading}.</t>
+          <t xml:space="preserve">Saved</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6339,17 +6339,17 @@
     <row r="197">
       <c r="A197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.title</t>
+          <t xml:space="preserve">create.discard</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet</t>
+          <t xml:space="preserve">Discard it and start again</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="2">
@@ -6371,17 +6371,17 @@
     <row r="198">
       <c r="A198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.delivered</t>
+          <t xml:space="preserve">create.keep</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
+          <t xml:space="preserve">Keep it</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="2">
@@ -6403,17 +6403,17 @@
     <row r="199">
       <c r="A199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.unsaved</t>
+          <t xml:space="preserve">create.lockedMaking</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
+          <t xml:space="preserve">Locked while your video is being made.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="2">
@@ -6435,22 +6435,22 @@
     <row r="200">
       <c r="A200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">discard.spoken</t>
+          <t xml:space="preserve">create.lockedSaving</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
+          <t xml:space="preserve">Step 6, Create: buttons and labels</t>
         </is>
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video is not saved yet. {question}</t>
+          <t xml:space="preserve">Locked while your video is being saved.</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6467,22 +6467,22 @@
     <row r="201">
       <c r="A201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.finished</t>
+          <t xml:space="preserve">status.checking</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finished video — {size}</t>
+          <t xml:space="preserve">Checking this video against your device…</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6499,22 +6499,22 @@
     <row r="202">
       <c r="A202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.previous</t>
+          <t xml:space="preserve">status.checkStopped</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Previous video — {size}</t>
+          <t xml:space="preserve">Check stopped.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6531,17 +6531,17 @@
     <row r="203">
       <c r="A203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetime</t>
+          <t xml:space="preserve">status.stoppingSave</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
+          <t xml:space="preserve">Stopping the save…</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="2">
@@ -6563,17 +6563,17 @@
     <row r="204">
       <c r="A204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.lifetimeDelivered</t>
+          <t xml:space="preserve">status.cancelling</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
+          <t xml:space="preserve">Cancelling…</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="2">
@@ -6595,22 +6595,22 @@
     <row r="205">
       <c r="A205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptWhole</t>
+          <t xml:space="preserve">status.cancelled</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the whole video ({duration})</t>
+          <t xml:space="preserve">Cancelled. Nothing was saved, and your original file is unchanged.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6627,22 +6627,22 @@
     <row r="206">
       <c r="A206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.keptPart</t>
+          <t xml:space="preserve">status.saving</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
+          <t xml:space="preserve">Saving…</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6659,17 +6659,17 @@
     <row r="207">
       <c r="A207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingNone</t>
+          <t xml:space="preserve">status.saveStopped</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">no University closing</t>
+          <t xml:space="preserve">Save stopped. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="2">
@@ -6691,22 +6691,22 @@
     <row r="208">
       <c r="A208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingInternal</t>
+          <t xml:space="preserve">status.notSaved</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{closing}, marked “{words}”</t>
+          <t xml:space="preserve">Not saved. The video is still here when you want it.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6723,22 +6723,22 @@
     <row r="209">
       <c r="A209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.blue</t>
+          <t xml:space="preserve">status.refusedSource</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the blue closing card</t>
+          <t xml:space="preserve">That is the file you started with. Choose a different name or folder — this tool never changes your original.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6755,22 +6755,22 @@
     <row r="210">
       <c r="A210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingCut.white</t>
+          <t xml:space="preserve">status.saved</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a cut to the white closing card</t>
+          <t xml:space="preserve">Saved. Check it where you saved it, then upload it where it is going — or choose another video in step 1.</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -6787,22 +6787,22 @@
     <row r="211">
       <c r="A211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
+          <t xml:space="preserve">status.saveFailed</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
+          <t xml:space="preserve">The video could not be saved. It is still here to try again.</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -6819,22 +6819,22 @@
     <row r="212">
       <c r="A212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
+          <t xml:space="preserve">status.storageWayOut</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
+          <t xml:space="preserve">Keep less of the video, choose {smaller}, or free some space, then press Check again.</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -6851,22 +6851,22 @@
     <row r="213">
       <c r="A213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
+          <t xml:space="preserve">status.creating</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over a held last frame</t>
+          <t xml:space="preserve">Creating your video. {notice}</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {notice} as written: {notice} is another sentence from this sheet (progress.jobNotice).</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -6883,22 +6883,22 @@
     <row r="214">
       <c r="A214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
+          <t xml:space="preserve">status.ready</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
+          <t xml:space="preserve">Your video is ready.</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -6915,22 +6915,22 @@
     <row r="215">
       <c r="A215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
+          <t xml:space="preserve">status.couldNotCreate</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the status line under the buttons, also read out by screen readers</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing fading in over the picture</t>
+          <t xml:space="preserve">The video could not be created. {sentence}</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {sentence} as written: {sentence} is an error message from this sheet.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -6947,22 +6947,22 @@
     <row r="216">
       <c r="A216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
+          <t xml:space="preserve">status.verdictSpoken</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers when the device check finishes</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the blue closing sliding in over the picture</t>
+          <t xml:space="preserve">Device check complete. {heading}.</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Keep {heading} as written: {heading} is a heading from this sheet.</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -6979,22 +6979,22 @@
     <row r="217">
       <c r="A217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
+          <t xml:space="preserve">discard.title</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing fading in over the picture</t>
+          <t xml:space="preserve">This video is not saved yet</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7011,22 +7011,22 @@
     <row r="218">
       <c r="A218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
+          <t xml:space="preserve">discard.delivered</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">the white closing sliding in over the picture</t>
+          <t xml:space="preserve">Your download may still be finishing. Starting again will discard the video you just made.</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7043,22 +7043,22 @@
     <row r="219">
       <c r="A219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summary</t>
+          <t xml:space="preserve">discard.unsaved</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Step 6: the question asked before an unsaved video is discarded</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">You have not saved the video you just made. Starting again will discard it.</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7075,22 +7075,22 @@
     <row r="220">
       <c r="A220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.summaryWithCard</t>
+          <t xml:space="preserve">discard.spoken</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
+          <t xml:space="preserve">Not shown: read out by screen readers with the question</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Made from {name}: a {seconds}-second title card, then {part}, {output}, {closing}.</t>
+          <t xml:space="preserve">This video is not saved yet. {question}</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {name}, {seconds}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {seconds} is a number of seconds; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
+          <t xml:space="preserve">Keep {question} as written: {question} is the question from discard.delivered or discard.unsaved.</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7107,7 +7107,7 @@
     <row r="221">
       <c r="A221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.notLoaded</t>
+          <t xml:space="preserve">result.finished</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
+          <t xml:space="preserve">Finished video — {size}</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
     <row r="222">
       <c r="A222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
+          <t xml:space="preserve">result.previous</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">Previous video — {size}</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
     <row r="223">
       <c r="A223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
+          <t xml:space="preserve">result.lifetime</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
+          <t xml:space="preserve">It is kept here only until you save it or close this tab.</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7203,7 +7203,7 @@
     <row r="224">
       <c r="A224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
+          <t xml:space="preserve">result.lifetimeDelivered</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">It stays here until you start another video or close this tab.</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
     <row r="225">
       <c r="A225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
+          <t xml:space="preserve">result.keptWhole</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
+          <t xml:space="preserve">the whole video ({duration})</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="226">
       <c r="A226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
+          <t xml:space="preserve">result.keptPart</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">{kept} of {duration}, from {from} to {to}</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Keep {kept}, {duration}, {from}, {to} as written: {kept} is a length of time in words; {duration} is a length of time in words, like "4 minutes 12 seconds"; {from} is a time, like 0:30.0; {to} is a time, like 2:30.0.</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7299,7 +7299,7 @@
     <row r="227">
       <c r="A227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
+          <t xml:space="preserve">result.closingNone</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">no University closing</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7331,7 +7331,7 @@
     <row r="228">
       <c r="A228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
+          <t xml:space="preserve">result.closingInternal</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">{closing}, marked “{words}”</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Adds to how the video closes, like "a cut to the blue closing card, marked “Internal use only”". Keep the quotation marks. Keep {closing}, {words} as written: {closing} is how the video closes, from result.closing…; {words} is the words drawn on the closing card, from closing.internalWords.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="229">
       <c r="A229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
+          <t xml:space="preserve">result.closingCut.blue</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
+          <t xml:space="preserve">a cut to the blue closing card</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue.</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7395,7 +7395,7 @@
     <row r="230">
       <c r="A230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
+          <t xml:space="preserve">result.closingCut.white</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">a cut to the white closing card</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is white.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
     <row r="231">
       <c r="A231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">the blue closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7459,7 +7459,7 @@
     <row r="232">
       <c r="A232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
+          <t xml:space="preserve">result.closingOverFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">the blue closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7491,7 +7491,7 @@
     <row r="233">
       <c r="A233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.fade</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
+          <t xml:space="preserve">the white closing fading in over a held last frame</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7523,22 +7523,22 @@
     <row r="234">
       <c r="A234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.preparing</t>
+          <t xml:space="preserve">result.closingOverFreeze.white.slide</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Getting ready</t>
+          <t xml:space="preserve">the white closing sliding in over a held last frame</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7555,22 +7555,22 @@
     <row r="235">
       <c r="A235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.analysing</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.fade</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Analysing audio</t>
+          <t xml:space="preserve">the blue closing fading in over the picture</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7587,22 +7587,22 @@
     <row r="236">
       <c r="A236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.encoding</t>
+          <t xml:space="preserve">result.closingOverPicture.blue.slide</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Encoding video</t>
+          <t xml:space="preserve">the blue closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7619,22 +7619,22 @@
     <row r="237">
       <c r="A237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.finishing</t>
+          <t xml:space="preserve">result.closingOverPicture.white.fade</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Finishing the file</t>
+          <t xml:space="preserve">the white closing fading in over the picture</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7651,22 +7651,22 @@
     <row r="238">
       <c r="A238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stages.checking</t>
+          <t xml:space="preserve">result.closingOverPicture.white.slide</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking the file</t>
+          <t xml:space="preserve">the white closing sliding in over the picture</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7683,22 +7683,22 @@
     <row r="239">
       <c r="A239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.0</t>
+          <t xml:space="preserve">result.summary</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a quarter done</t>
+          <t xml:space="preserve">Made from {name}: {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
+          <t xml:space="preserve">Keep {name}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7715,22 +7715,22 @@
     <row r="240">
       <c r="A240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.1</t>
+          <t xml:space="preserve">result.summaryWithCard</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">half done</t>
+          <t xml:space="preserve">Made from {name}: a {seconds}-second title card, then {part}, {output}, {closing}.</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
+          <t xml:space="preserve">Keep {name}, {seconds}, {part}, {output}, {closing} as written: {name} is a name: a language's own name, or the user's file name; {seconds} is a number of seconds; {part} is what part of the video was kept, from result.keptWhole or result.keptPart; {output} is the output chosen, from preset.labels; {closing} is how the video closes, from result.closing….</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7747,22 +7747,22 @@
     <row r="241">
       <c r="A241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.milestones.2</t>
+          <t xml:space="preserve">result.notLoaded</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">three quarters done</t>
+          <t xml:space="preserve">The closing could not be loaded, so it is not in this video. Everything else was applied as asked.</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7779,22 +7779,22 @@
     <row r="242">
       <c r="A242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stagePercent</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.fade</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {percent}</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -7811,22 +7811,22 @@
     <row r="243">
       <c r="A243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.stageMilestone</t>
+          <t xml:space="preserve">result.fellBackToCut.blue.slide</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {milestone}</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the blue closing card instead.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -7843,22 +7843,22 @@
     <row r="244">
       <c r="A244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.ready</t>
+          <t xml:space="preserve">result.fellBackToCut.white.fade</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready</t>
+          <t xml:space="preserve">You chose Fade, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -7875,22 +7875,22 @@
     <row r="245">
       <c r="A245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.stage</t>
+          <t xml:space="preserve">result.fellBackToCut.white.slide</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stage} — {app}</t>
+          <t xml:space="preserve">You chose Slide, but the animation could not be loaded, so this video cuts to the white closing card instead.</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -7907,22 +7907,22 @@
     <row r="246">
       <c r="A246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.ready</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.fade</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready — {app}</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The blue closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -7939,22 +7939,22 @@
     <row r="247">
       <c r="A247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.failed</t>
+          <t xml:space="preserve">result.fellBackToFreeze.blue.slide</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not made — {app}</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The blue closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -7971,22 +7971,22 @@
     <row r="248">
       <c r="A248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.title.cancelled</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.fade</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title in the browser tab while the video is made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Cancelled — {app}</t>
+          <t xml:space="preserve">Your video is shorter than the fade animation. The white closing fades in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8003,22 +8003,22 @@
     <row r="249">
       <c r="A249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">progress.jobNotice</t>
+          <t xml:space="preserve">result.fellBackToFreeze.white.slide</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: said when the video starts being made</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
+          <t xml:space="preserve">Your video is shorter than the slide animation. The white closing slides in over a held last frame instead of over the picture.</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8035,22 +8035,22 @@
     <row r="250">
       <c r="A250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.proceed</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.fade</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready to go</t>
+          <t xml:space="preserve">The blue closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8067,22 +8067,22 @@
     <row r="251">
       <c r="A251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warn</t>
+          <t xml:space="preserve">result.fellBackToPicture.blue.slide</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with one thing to know</t>
+          <t xml:space="preserve">The blue closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the closing colour is blue. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8099,22 +8099,22 @@
     <row r="252">
       <c r="A252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.fade</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with two things to know</t>
+          <t xml:space="preserve">The white closing fades in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing fades in.</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8131,22 +8131,22 @@
     <row r="253">
       <c r="A253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
+          <t xml:space="preserve">result.fellBackToPicture.white.slide</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the finished video and its one-line summary</t>
         </is>
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with three things to know</t>
+          <t xml:space="preserve">The white closing slides in over the picture, not over a held last frame as chosen.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve">Used when the closing colour is white. Used when the closing slides in.</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8163,22 +8163,22 @@
     <row r="254">
       <c r="A254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
+          <t xml:space="preserve">progress.stages.preparing</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with four things to know</t>
+          <t xml:space="preserve">Getting ready</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8195,22 +8195,22 @@
     <row r="255">
       <c r="A255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
+          <t xml:space="preserve">progress.stages.analysing</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with five things to know</t>
+          <t xml:space="preserve">Analysing audio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 5, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8227,22 +8227,22 @@
     <row r="256">
       <c r="A256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
+          <t xml:space="preserve">progress.stages.encoding</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with six things to know</t>
+          <t xml:space="preserve">Encoding video</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 6, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8259,22 +8259,22 @@
     <row r="257">
       <c r="A257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
+          <t xml:space="preserve">progress.stages.finishing</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready, with {count} things to know</t>
+          <t xml:space="preserve">Finishing the file</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8291,17 +8291,17 @@
     <row r="258">
       <c r="A258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.discourage</t>
+          <t xml:space="preserve">progress.stages.checking</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will work, but it will be slow</t>
+          <t xml:space="preserve">Checking the file</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="2">
@@ -8323,22 +8323,22 @@
     <row r="259">
       <c r="A259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.mobile</t>
+          <t xml:space="preserve">progress.milestones.0</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This may not finish on a phone or tablet</t>
+          <t xml:space="preserve">a quarter done</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — a quarter done".</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8355,22 +8355,22 @@
     <row r="260">
       <c r="A260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.headings.block</t>
+          <t xml:space="preserve">progress.milestones.1</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the heading of the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This cannot run here</t>
+          <t xml:space="preserve">half done</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — half done".</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8387,22 +8387,22 @@
     <row r="261">
       <c r="A261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.tryChrome</t>
+          <t xml:space="preserve">progress.milestones.2</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
+          <t xml:space="preserve">three quarters done</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Follows a stage name, like "Encoding video — three quarters done".</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8419,22 +8419,22 @@
     <row r="262">
       <c r="A262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.chromeLacks</t>
+          <t xml:space="preserve">progress.stagePercent</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
+          <t xml:space="preserve">{stage} — {percent}</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {stage}, {percent} as written: {stage} is a stage name from progress.stages; {percent} is a percentage, like 14%.</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8451,22 +8451,22 @@
     <row r="263">
       <c r="A263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
+          <t xml:space="preserve">progress.stageMilestone</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
+          <t xml:space="preserve">{stage} — {milestone}</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Keep {stage}, {milestone} as written: {stage} is a stage name from progress.stages; {milestone} is a phrase from progress.milestones.</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8483,22 +8483,22 @@
     <row r="264">
       <c r="A264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
+          <t xml:space="preserve">progress.ready</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the progress bar while the video is made</t>
         </is>
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
+          <t xml:space="preserve">Ready</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8515,22 +8515,22 @@
     <row r="265">
       <c r="A265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
+          <t xml:space="preserve">progress.title.stage</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
+          <t xml:space="preserve">{stage} — {app}</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Keep {stage}, {app} as written: {stage} is a stage name from progress.stages; {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8547,22 +8547,22 @@
     <row r="266">
       <c r="A266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
+          <t xml:space="preserve">progress.title.ready</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
+          <t xml:space="preserve">Ready — {app}</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8579,22 +8579,22 @@
     <row r="267">
       <c r="A267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
+          <t xml:space="preserve">progress.title.failed</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
+          <t xml:space="preserve">Not made — {app}</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8611,22 +8611,22 @@
     <row r="268">
       <c r="A268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
+          <t xml:space="preserve">progress.title.cancelled</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">The title in the browser tab while the video is made</t>
         </is>
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
+          <t xml:space="preserve">Cancelled — {app}</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Keep {app} as written: {app} is the product name, from app.title.</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8643,17 +8643,17 @@
     <row r="269">
       <c r="A269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
+          <t xml:space="preserve">progress.jobNotice</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: said when the video starts being made</t>
         </is>
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
+          <t xml:space="preserve">Keep this tab visible and your computer awake while the video is made. Closing the tab ends the job.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="2">
@@ -8675,22 +8675,22 @@
     <row r="270">
       <c r="A270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
+          <t xml:space="preserve">preflight.headings.proceed</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
+          <t xml:space="preserve">Ready to go</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8707,17 +8707,17 @@
     <row r="271">
       <c r="A271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insecureContext</t>
+          <t xml:space="preserve">preflight.headings.warn</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
+          <t xml:space="preserve">Ready, with one thing to know</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="2">
@@ -8739,22 +8739,22 @@
     <row r="272">
       <c r="A272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
+          <t xml:space="preserve">Ready, with two things to know</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8771,22 +8771,22 @@
     <row r="273">
       <c r="A273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.3</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
+          <t xml:space="preserve">Ready, with three things to know</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -8803,22 +8803,22 @@
     <row r="274">
       <c r="A274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.4</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
+          <t xml:space="preserve">Ready, with four things to know</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -8835,22 +8835,22 @@
     <row r="275">
       <c r="A275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.5</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">Ready, with five things to know</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Used when the count is 5, said in words.</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -8867,22 +8867,22 @@
     <row r="276">
       <c r="A276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.6</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
+          <t xml:space="preserve">Ready, with six things to know</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 6, said in words.</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -8899,22 +8899,22 @@
     <row r="277">
       <c r="A277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJob</t>
+          <t xml:space="preserve">preflight.headings.warnSeveral.other</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">Ready, with {count} things to know</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Used for any count above 6, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -8931,17 +8931,17 @@
     <row r="278">
       <c r="A278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
+          <t xml:space="preserve">preflight.headings.discourage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
+          <t xml:space="preserve">This will work, but it will be slow</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="2">
@@ -8963,17 +8963,17 @@
     <row r="279">
       <c r="A279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
+          <t xml:space="preserve">preflight.headings.mobile</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
+          <t xml:space="preserve">This may not finish on a phone or tablet</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="2">
@@ -8995,17 +8995,17 @@
     <row r="280">
       <c r="A280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
+          <t xml:space="preserve">preflight.headings.block</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: one reason in the device check</t>
+          <t xml:space="preserve">Step 6: the heading of the device check</t>
         </is>
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
+          <t xml:space="preserve">This cannot run here</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="2">
@@ -9027,7 +9027,7 @@
     <row r="281">
       <c r="A281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTake</t>
+          <t xml:space="preserve">preflight.tryChrome</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take about {time}.</t>
+          <t xml:space="preserve">Chrome on a computer is the browser this tool is built for — try it there.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9059,7 +9059,7 @@
     <row r="282">
       <c r="A282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
+          <t xml:space="preserve">preflight.chromeLacks</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This should take a few seconds.</t>
+          <t xml:space="preserve">This copy of Chrome may be out of date, or a setting on this computer may have turned the feature off. Update Chrome, or ask whoever manages the computer.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="2">
@@ -9091,22 +9091,22 @@
     <row r="283">
       <c r="A283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sizeUpTo</t>
+          <t xml:space="preserve">preflight.reasons.noWebCodecs</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Estimated size up to {size}.</t>
+          <t xml:space="preserve">This browser cannot process video. {remedy}</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9123,22 +9123,22 @@
     <row r="284">
       <c r="A284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.sameSize</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeHere</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy}</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9155,22 +9155,22 @@
     <row r="285">
       <c r="A285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">preflight.slides</t>
+          <t xml:space="preserve">preflight.reasons.noAacEncodeElsewhere</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
+          <t xml:space="preserve">This browser cannot add sound to a video file. {remedy} Firefox can play video but cannot create the sound this needs.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9187,22 +9187,22 @@
     <row r="286">
       <c r="A286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.soundHeading</t>
+          <t xml:space="preserve">preflight.reasons.noH264Encode</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the sound</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs. {remedy}</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9219,17 +9219,17 @@
     <row r="287">
       <c r="A287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.finishedHeading</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeHere</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Worth knowing about the finished video</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. It was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4 — and choose that file instead.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="2">
@@ -9251,22 +9251,22 @@
     <row r="288">
       <c r="A288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.reassurance</t>
+          <t xml:space="preserve">preflight.reasons.noSourceDecodeElsewhere</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
+          <t xml:space="preserve">This browser cannot read the picture or sound inside this file. {remedy} If it will not open there either, the file was probably saved in a format made for editing software. Export it again as an MP4 — a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9283,22 +9283,22 @@
     <row r="289">
       <c r="A289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.spoken</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsHere</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{heading}: {titles}.</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. If you are browsing privately, an ordinary window usually works; otherwise a setting on this computer may be blocking site storage — ask whoever manages it.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9315,22 +9315,22 @@
     <row r="290">
       <c r="A290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.heading</t>
+          <t xml:space="preserve">preflight.reasons.noOpfsElsewhere</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This video has no sound</t>
+          <t xml:space="preserve">This browser will not give the tool the working space it needs to build your video. {remedy} If you are browsing privately, an ordinary window usually works.</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9347,17 +9347,17 @@
     <row r="291">
       <c r="A291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noAudio.detail</t>
+          <t xml:space="preserve">preflight.reasons.insecureContext</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an https:// address, or at localhost if you are running it yourself.</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="2">
@@ -9379,22 +9379,22 @@
     <row r="292">
       <c r="A292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorageResolvable</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again, keep less of the video, or choose {smaller}.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size}, {smaller} as written: {size} is a file size, like "120 MB"; {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9411,22 +9411,22 @@
     <row r="293">
       <c r="A293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">preflight.reasons.insufficientStorage</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">There is not enough free space on this device. This job needs about {size} of working space. Free some space and try again.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9443,17 +9443,17 @@
     <row r="294">
       <c r="A294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">preflight.reasons.storageUnknown</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">This browser will not say how much free space there is. If it runs out part-way, the job stops and nothing is saved — your original file is not affected.</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="2">
@@ -9475,22 +9475,22 @@
     <row r="295">
       <c r="A295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJob</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">This will take about {time}. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9507,17 +9507,17 @@
     <row r="296">
       <c r="A296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">preflight.reasons.veryLongJobUnknown</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">This will take about a long time. You can carry on, but a desktop computer would be considerably faster.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="2">
@@ -9539,22 +9539,22 @@
     <row r="297">
       <c r="A297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">preflight.reasons.longJob</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">This will take about {time}. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9571,17 +9571,17 @@
     <row r="298">
       <c r="A298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">preflight.reasons.longJobUnknown</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">This will take about a while. Keep this tab open while it runs — closing it stops the job.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="2">
@@ -9603,17 +9603,17 @@
     <row r="299">
       <c r="A299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">preflight.reasons.mobileDevice</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">Phones and tablets are much slower at this than a computer, and the browser there may end the job part-way to free memory. Use a computer if you can.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="2">
@@ -9635,17 +9635,17 @@
     <row r="300">
       <c r="A300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">preflight.reasons.estimateUnavailable</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: one reason in the device check</t>
         </is>
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">We could not work out how long this will take on this device. You can still continue.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="2">
@@ -9667,22 +9667,22 @@
     <row r="301">
       <c r="A301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">preflight.shouldTake</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">This should take about {time}.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9699,17 +9699,17 @@
     <row r="302">
       <c r="A302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">preflight.shouldTakeFewSeconds</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">This should take a few seconds.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="2">
@@ -9731,22 +9731,22 @@
     <row r="303">
       <c r="A303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">preflight.sizeUpTo</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">Estimated size up to {size}.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {size} as written: {size} is a file size, like "120 MB".</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -9763,17 +9763,17 @@
     <row r="304">
       <c r="A304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">preflight.sameSize</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">Your video is already compressed as far as this setting would take it, so the new file will be about the same size.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="2">
@@ -9795,22 +9795,22 @@
     <row r="305">
       <c r="A305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">preflight.slides</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
+          <t xml:space="preserve">Step 6: the device check, which says whether this computer can make the video</t>
         </is>
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">This looks like slides or a screen recording, so the file is made smaller still. If it is mostly camera footage, choose {best} instead.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {best} as written: {best} is the name of the larger output, from preset.labels.best.</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -9827,22 +9827,22 @@
     <row r="306">
       <c r="A306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.soundHeading</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">Worth knowing about the sound</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -9859,22 +9859,22 @@
     <row r="307">
       <c r="A307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.finishedHeading</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">Worth knowing about the finished video</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -9891,22 +9891,22 @@
     <row r="308">
       <c r="A308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">warnings.reassurance</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">None of these stop you continuing. Your original file is not changed either way.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="309">
       <c r="A309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">warnings.spoken</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">{heading}: {titles}.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve">Keep {heading}, {titles} as written: {heading} is a heading from this sheet; {titles} is warning headings from this sheet, one after another.</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -9955,22 +9955,22 @@
     <row r="310">
       <c r="A310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">warnings.noAudio.heading</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">This video has no sound</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -9987,22 +9987,22 @@
     <row r="311">
       <c r="A311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">warnings.noAudio.detail</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">There is no sound to level, so the rest of the job runs without it. If you expected sound, check the recording before publishing.</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10019,17 +10019,17 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
@@ -10051,17 +10051,17 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
@@ -10083,17 +10083,17 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
@@ -10115,17 +10115,17 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
@@ -10147,17 +10147,17 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
@@ -10179,17 +10179,17 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
@@ -10211,17 +10211,17 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
@@ -10243,17 +10243,17 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
@@ -10275,17 +10275,17 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
@@ -10307,22 +10307,22 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10339,17 +10339,17 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
@@ -10371,17 +10371,17 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
@@ -10403,17 +10403,17 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
@@ -10435,17 +10435,17 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
@@ -10467,22 +10467,22 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10499,22 +10499,22 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10531,22 +10531,22 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10563,22 +10563,22 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10595,22 +10595,22 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10627,22 +10627,22 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10659,7 +10659,7 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
@@ -10691,7 +10691,7 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
@@ -10723,7 +10723,7 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.what</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
@@ -10755,7 +10755,7 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.next</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -10787,7 +10787,7 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
@@ -10819,7 +10819,7 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
@@ -10851,17 +10851,17 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
@@ -10883,22 +10883,22 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -10915,22 +10915,22 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -10947,22 +10947,22 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -10979,17 +10979,17 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
@@ -11011,17 +11011,17 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,22 +11043,22 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11075,22 +11075,22 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11107,22 +11107,22 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11139,22 +11139,22 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11171,22 +11171,22 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11203,17 +11203,17 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
@@ -11235,17 +11235,17 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
@@ -11267,22 +11267,22 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11299,22 +11299,22 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11331,22 +11331,22 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11363,22 +11363,22 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">failure.titleCardRefused.what</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11395,22 +11395,22 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">failure.titleCardRefused.next</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11427,17 +11427,17 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
@@ -11459,17 +11459,17 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
@@ -11491,17 +11491,17 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
@@ -11523,22 +11523,22 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11555,22 +11555,22 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,22 +11587,22 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11619,17 +11619,17 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
@@ -11651,17 +11651,17 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
@@ -11683,7 +11683,7 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,7 +11715,7 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,7 +11747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11779,7 +11779,7 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,7 +11811,7 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,7 +11843,7 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
@@ -11875,17 +11875,17 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
@@ -11907,22 +11907,22 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,22 +11939,22 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,22 +11971,22 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12003,22 +12003,22 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,22 +12035,22 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12067,17 +12067,17 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
@@ -12099,17 +12099,17 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
@@ -12131,17 +12131,17 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
@@ -12163,17 +12163,17 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
@@ -12195,17 +12195,17 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
@@ -12227,17 +12227,17 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
@@ -12259,17 +12259,17 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
@@ -12291,22 +12291,22 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12323,22 +12323,22 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12355,17 +12355,17 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
@@ -12387,22 +12387,22 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12419,17 +12419,17 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
@@ -12451,22 +12451,22 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,22 +12483,22 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12515,22 +12515,22 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12547,22 +12547,22 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12579,22 +12579,22 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12611,22 +12611,22 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12643,22 +12643,22 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12675,22 +12675,22 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12707,22 +12707,22 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -12739,17 +12739,17 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
@@ -12771,17 +12771,17 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
@@ -12803,22 +12803,22 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -12835,22 +12835,22 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -12867,22 +12867,22 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,17 +12899,17 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
@@ -12931,22 +12931,22 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,22 +12963,22 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,17 +12995,17 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
@@ -13027,22 +13027,22 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,17 +13059,17 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
@@ -13091,22 +13091,22 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13123,22 +13123,22 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Equality Advisory and Support Service</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13155,22 +13155,22 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.heading</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Compliance status</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13187,7 +13187,7 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.compliance.text</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13197,12 +13197,12 @@
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,22 +13219,22 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.heading</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How we tested this tool</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,22 +13251,22 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.wave</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13283,22 +13283,22 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.automated</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13315,22 +13315,22 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.testing.manual</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Chrome as it is.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,22 +13347,22 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.heading</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What we plan to test next</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,7 +13379,7 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.intro</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13411,22 +13411,22 @@
     <row r="418">
       <c r="A418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.0</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using the tool with a keyboard alone</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13443,22 +13443,22 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.1</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13475,22 +13475,22 @@
     <row r="420">
       <c r="A420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.2</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13507,22 +13507,22 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.3</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Windows contrast themes</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13539,22 +13539,22 @@
     <row r="422">
       <c r="A422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.4</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13571,22 +13571,22 @@
     <row r="423">
       <c r="A423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plans.items.5</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a session with disabled staff who use the tool</t>
+          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13603,22 +13603,22 @@
     <row r="424">
       <c r="A424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.heading</t>
+          <t xml:space="preserve">statement.limits.items.4</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About this statement</t>
+          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13635,22 +13635,22 @@
     <row r="425">
       <c r="A425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.about.dates</t>
+          <t xml:space="preserve">statement.contact.heading</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
+          <t xml:space="preserve">Feedback and contact</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13667,22 +13667,22 @@
     <row r="426">
       <c r="A426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.intro</t>
+          <t xml:space="preserve">statement.contact.text</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">For help with this tool:</t>
+          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -13699,22 +13699,22 @@
     <row r="427">
       <c r="A427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.creators</t>
+          <t xml:space="preserve">statement.enforcement.heading</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the creators team</t>
+          <t xml:space="preserve">Enforcement procedure</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -13731,22 +13731,22 @@
     <row r="428">
       <c r="A428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">footer.contact.learningContent</t>
+          <t xml:space="preserve">statement.enforcement.text</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email the learning content team</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
         </is>
       </c>
       <c r="D428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -13763,22 +13763,22 @@
     <row r="429">
       <c r="A429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.pickerDescription</t>
+          <t xml:space="preserve">statement.enforcement.service</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MP4 video (.mp4)</t>
+          <t xml:space="preserve">Equality Advisory and Support Service</t>
         </is>
       </c>
       <c r="D429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">The name of an official UK advice service, shown as a link to its website. Give its English name with a translation in brackets, or name it as your language normally would.</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -13795,22 +13795,22 @@
     <row r="430">
       <c r="A430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.stem</t>
+          <t xml:space="preserve">statement.compliance.heading</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">video</t>
+          <t xml:space="preserve">Compliance status</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used as the file name when the original has none.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -13827,22 +13827,22 @@
     <row r="431">
       <c r="A431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.branded</t>
+          <t xml:space="preserve">statement.compliance.text</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">branded</t>
+          <t xml:space="preserve">This tool is partially compliant with version 2.2 of the Web Content Accessibility Guidelines (WCAG), at level AA, the middle of their three levels. Only automated checks have been run so far, so we cannot yet say it fully meets them. We aim for level AAA, the highest.</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+          <t xml:space="preserve">Keep WCAG, AA and AAA as they are; 2.2 is a version number. Use the usual name in your language for the Web Content Accessibility Guidelines, if there is one.</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -13859,22 +13859,22 @@
     <row r="432">
       <c r="A432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.levelled</t>
+          <t xml:space="preserve">statement.testing.heading</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">levelled</t>
+          <t xml:space="preserve">How we tested this tool</t>
         </is>
       </c>
       <c r="D432" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -13891,22 +13891,22 @@
     <row r="433">
       <c r="A433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.marks.converted</t>
+          <t xml:space="preserve">statement.testing.wave</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">converted</t>
+          <t xml:space="preserve">On {date}, we checked this page with WAVE, a web accessibility evaluation tool from WebAIM. It gave the page a score of 10 out of 10.</t>
         </is>
       </c>
       <c r="D433" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+          <t xml:space="preserve">Keep the names WAVE and WebAIM as they are. The score is 10 out of 10. Keep {date} as written: {date} is a date the app writes in your language, like "18 October 2026".</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -13923,22 +13923,22 @@
     <row r="434">
       <c r="A434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.fileName</t>
+          <t xml:space="preserve">statement.testing.automated</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The name suggested for the saved file</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+          <t xml:space="preserve">Each time the code changes, automated tests check the contrast of the text against its background, and the reading level of the words.</t>
         </is>
       </c>
       <c r="D434" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -13955,22 +13955,22 @@
     <row r="435">
       <c r="A435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadIos</t>
+          <t xml:space="preserve">statement.testing.manual</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+          <t xml:space="preserve">We have also checked it by hand in Chrome, at computer and phone widths, while building it.</t>
         </is>
       </c>
       <c r="D435" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Chrome as it is.</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -13987,17 +13987,17 @@
     <row r="436">
       <c r="A436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.downloadOther</t>
+          <t xml:space="preserve">statement.plans.heading</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C436" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saving to your downloads folder</t>
+          <t xml:space="preserve">What we plan to test next</t>
         </is>
       </c>
       <c r="D436" t="inlineStr" s="2">
@@ -14019,22 +14019,22 @@
     <row r="437">
       <c r="A437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">save.download</t>
+          <t xml:space="preserve">statement.plans.intro</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 6: saving the finished video</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+          <t xml:space="preserve">We have not yet chosen the next tests. We are thinking of:</t>
         </is>
       </c>
       <c r="D437" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+          <t xml:space="preserve">Introduces the six lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14051,22 +14051,22 @@
     <row r="438">
       <c r="A438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.unknown</t>
+          <t xml:space="preserve">statement.plans.items.0</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">using the tool with a keyboard alone</t>
         </is>
       </c>
       <c r="D438" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14083,22 +14083,22 @@
     <row r="439">
       <c r="A439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.lessThanASecond</t>
+          <t xml:space="preserve">statement.plans.items.1</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">less than a second</t>
+          <t xml:space="preserve">using it with the NVDA screen reader in Chrome on Windows, and with VoiceOver on a Mac</t>
         </is>
       </c>
       <c r="D439" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep the names NVDA, Chrome, Windows, VoiceOver and Mac as they are.</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14115,22 +14115,22 @@
     <row r="440">
       <c r="A440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.fewSeconds</t>
+          <t xml:space="preserve">statement.plans.items.2</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a few seconds</t>
+          <t xml:space="preserve">zooming in to 400%, and a screen 320 pixels wide</t>
         </is>
       </c>
       <c r="D440" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14147,22 +14147,22 @@
     <row r="441">
       <c r="A441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.frameRate</t>
+          <t xml:space="preserve">statement.plans.items.3</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{rate} frames a second</t>
+          <t xml:space="preserve">Windows contrast themes</t>
         </is>
       </c>
       <c r="D441" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it has no full stop. Keep the name Windows as it is.</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14179,22 +14179,22 @@
     <row r="442">
       <c r="A442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.resolution</t>
+          <t xml:space="preserve">statement.plans.items.4</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{width} × {height}</t>
+          <t xml:space="preserve">a second automated tool, such as axe or Lighthouse</t>
         </is>
       </c>
       <c r="D442" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop. Keep axe and Lighthouse as they are: they are the names of tools.</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14211,22 +14211,22 @@
     <row r="443">
       <c r="A443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.mono</t>
+          <t xml:space="preserve">statement.plans.items.5</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "We are thinking of:"</t>
         </is>
       </c>
       <c r="C443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Mono (one channel)</t>
+          <t xml:space="preserve">a session with disabled staff who use the tool</t>
         </is>
       </c>
       <c r="D443" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "We are thinking of:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14243,17 +14243,17 @@
     <row r="444">
       <c r="A444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.stereo</t>
+          <t xml:space="preserve">statement.about.heading</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C444" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Stereo (two channels)</t>
+          <t xml:space="preserve">About this statement</t>
         </is>
       </c>
       <c r="D444" t="inlineStr" s="2">
@@ -14275,22 +14275,22 @@
     <row r="445">
       <c r="A445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround51</t>
+          <t xml:space="preserve">statement.about.dates</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5.1 surround</t>
+          <t xml:space="preserve">This statement was written on {date}. Joe Bell reviewed it. We will review it again by {reviewDate}.</t>
         </is>
       </c>
       <c r="D445" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep the name Joe Bell as it is. Keep {date}, {reviewDate} as written: {date} is a date the app writes in your language, like "18 October 2026"; {reviewDate} is the date of the next review, written by the app, like "18 November 2026".</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14307,22 +14307,22 @@
     <row r="446">
       <c r="A446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">format.channels.surround71</t>
+          <t xml:space="preserve">footer.contact.intro</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: the line over the two team links</t>
         </is>
       </c>
       <c r="C446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7.1 surround</t>
+          <t xml:space="preserve">For help with this tool:</t>
         </is>
       </c>
       <c r="D446" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the two links that follow, one under the other. Each link makes sense on its own.</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14339,30 +14339,670 @@
     <row r="447">
       <c r="A447" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">footer.contact.creators</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the creators team</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Email the creators team</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The creators team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.learningContent.</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">footer.contact.learningContent</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The foot of the page, under the Send feedback button: a link that opens an email to the learning content team</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Email the learning content team</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The words of a link on a line of its own, so they must say alone that it opens an email. "The learning content team" is the name of a University team: translate it plainly, and use the same word for "team" as in footer.contact.creators.</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.pickerDescription</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The save dialog, naming the kind of file</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">MP4 video (.mp4)</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.stem</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">video</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Used as the file name when the original has none.</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.branded</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">branded</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name, like "Lecture 3 (branded).mp4".</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.levelled</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">levelled</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.marks.converted</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">converted</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Goes in brackets in the saved file's name.</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.fileName</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The name suggested for the saved file</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{stem} ({mark}).mp4</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep the brackets and .mp4. Keep {stem}, {mark} as written: {stem} is the user's own file name, without its ending; {mark} is a word from save.marks.</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.downloadIos</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 6: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Saving to the Files app, under Downloads</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.downloadOther</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 6: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Saving to your downloads folder</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">save.download</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Step 6: saving the finished video</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{where} — the browser may still be finishing it. Once it is there, upload it where it is going, or choose another video in step 1. The video stays here until you start another one.</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {where} as written: {where} is save.downloadIos or save.downloadOther.</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.unknown</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Shown alone in place of a fact the app could not read.</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.lessThanASecond</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">less than a second</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.fewSeconds</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">a few seconds</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.frameRate</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{rate} frames a second</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {rate} as written: {rate} is a frame rate, like "25 frames a second".</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.resolution</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">{width} × {height}</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Keep {width}, {height} as written: {width} is a number of pixels; {height} is a number of pixels.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.mono</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Mono (one channel)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.stereo</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Stereo (two channels)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround51</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">5.1 surround</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">format.channels.surround71</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7.1 surround</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">format.channels.several</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr" s="2">
+      <c r="B467" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Wherever a length, size or picture fact is shown, mostly Step 1, Video properties</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr" s="2">
+      <c r="C467" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">{count} channels</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr" s="2">
+      <c r="D467" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr" s="2">
+      <c r="E467" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/reviews/2026-10-18/VH-105-strings.xlsx
+++ b/reviews/2026-10-18/VH-105-strings.xlsx
@@ -10019,7 +10019,7 @@
     <row r="312">
       <c r="A312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.heading</t>
+          <t xml:space="preserve">warnings.decodeDamage.heading.one</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound may be distorted in places</t>
+          <t xml:space="preserve">A damaged moment has been silenced</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1.</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10051,7 +10051,7 @@
     <row r="313">
       <c r="A313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.clipping.detail</t>
+          <t xml:space="preserve">warnings.decodeDamage.heading.other</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
+          <t xml:space="preserve">Damaged moments have been silenced</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form.</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10083,7 +10083,7 @@
     <row r="314">
       <c r="A314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.heading</t>
+          <t xml:space="preserve">warnings.decodeDamage.detail.one</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This recording is very quiet</t>
+          <t xml:space="preserve">At {times}, the file holds a burst of noise louder than any recording can be. It comes from damage to the file, not from your recording. That fraction of a second will be silent instead, so no one hears it and the levelling still works as it should.</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {times} as written: {times} is a list of times in the video, like "1:22 and 3:05", perhaps ending "2 other moments" (warnings.decodeDamage.more).</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10115,7 +10115,7 @@
     <row r="315">
       <c r="A315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.veryQuiet.detail</t>
+          <t xml:space="preserve">warnings.decodeDamage.detail.other</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
+          <t xml:space="preserve">At {times}, the file holds bursts of noise louder than any recording can be. They come from damage to the file, not from your recording. Each fraction of a second will be silent instead, so no one hears them and the levelling still works as it should.</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {times} as written: {times} is a list of times in the video, like "1:22 and 3:05", perhaps ending "2 other moments" (warnings.decodeDamage.more).</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10147,7 +10147,7 @@
     <row r="316">
       <c r="A316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.heading</t>
+          <t xml:space="preserve">warnings.decodeDamage.more.one</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The volume varies a lot</t>
+          <t xml:space="preserve">{count} other moment</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10179,7 +10179,7 @@
     <row r="317">
       <c r="A317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.highlyVariable.detail</t>
+          <t xml:space="preserve">warnings.decodeDamage.more.other</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
+          <t xml:space="preserve">{count} other moments</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10211,7 +10211,7 @@
     <row r="318">
       <c r="A318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.heading</t>
+          <t xml:space="preserve">warnings.clipping.heading</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There may be background noise</t>
+          <t xml:space="preserve">The sound may be distorted in places</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="2">
@@ -10243,7 +10243,7 @@
     <row r="319">
       <c r="A319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.noisy.detail</t>
+          <t xml:space="preserve">warnings.clipping.detail</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
+          <t xml:space="preserve">The recording often reaches its maximum level, so some of it may be clipped. That usually means the microphone was set too high. Levelling still runs, but distortion already in the recording cannot be removed.</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="2">
@@ -10275,7 +10275,7 @@
     <row r="320">
       <c r="A320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.heading</t>
+          <t xml:space="preserve">warnings.veryQuiet.heading</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="C320" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">There is a long silent stretch</t>
+          <t xml:space="preserve">This recording is very quiet</t>
         </is>
       </c>
       <c r="D320" t="inlineStr" s="2">
@@ -10307,7 +10307,7 @@
     <row r="321">
       <c r="A321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.extendedSilence.detail</t>
+          <t xml:space="preserve">warnings.veryQuiet.detail</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
+          <t xml:space="preserve">It is well below a comfortable listening level. Levelling will bring it up — but turning up quiet speech turns up whatever else was in the room too.</t>
         </is>
       </c>
       <c r="D321" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10339,7 +10339,7 @@
     <row r="322">
       <c r="A322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.heading</t>
+          <t xml:space="preserve">warnings.highlyVariable.heading</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="C322" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
+          <t xml:space="preserve">The volume varies a lot</t>
         </is>
       </c>
       <c r="D322" t="inlineStr" s="2">
@@ -10371,7 +10371,7 @@
     <row r="323">
       <c r="A323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.targetMissed.detail</t>
+          <t xml:space="preserve">warnings.highlyVariable.detail</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C323" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
+          <t xml:space="preserve">The loudest and quietest parts are far apart. Levelling corrects slow drifts gradually, too slowly to hear, but sudden differences between sentences will remain.</t>
         </is>
       </c>
       <c r="D323" t="inlineStr" s="2">
@@ -10403,7 +10403,7 @@
     <row r="324">
       <c r="A324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.heading</t>
+          <t xml:space="preserve">warnings.noisy.heading</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C324" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The file’s title and date could not be copied across</t>
+          <t xml:space="preserve">There may be background noise</t>
         </is>
       </c>
       <c r="D324" t="inlineStr" s="2">
@@ -10435,7 +10435,7 @@
     <row r="325">
       <c r="A325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">warnings.metadataLost.detail</t>
+          <t xml:space="preserve">warnings.noisy.detail</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="C325" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
+          <t xml:space="preserve">Even the quietest moments carry some sound — a fan, air conditioning, or a noisy room. This tool does not remove noise, and making the speech louder will make the background louder with it.</t>
         </is>
       </c>
       <c r="D325" t="inlineStr" s="2">
@@ -10467,22 +10467,22 @@
     <row r="326">
       <c r="A326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.1</t>
+          <t xml:space="preserve">warnings.extendedSilence.heading</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
+          <t xml:space="preserve">There is a long silent stretch</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10499,22 +10499,22 @@
     <row r="327">
       <c r="A327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.2</t>
+          <t xml:space="preserve">warnings.extendedSilence.detail</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
+          <t xml:space="preserve">About {duration} of near-silence in one continuous run. If that is deliberate, nothing is wrong. If not, it is worth checking the recording before you publish it.</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 2, said in words.</t>
+          <t xml:space="preserve">Keep {duration} as written: {duration} is a length of time in words, like "4 minutes 12 seconds".</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10531,22 +10531,22 @@
     <row r="328">
       <c r="A328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.3</t>
+          <t xml:space="preserve">warnings.targetMissed.heading</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The finished sound is not quite at the usual level</t>
         </is>
       </c>
       <c r="D328" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 3, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10563,22 +10563,22 @@
     <row r="329">
       <c r="A329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.4</t>
+          <t xml:space="preserve">warnings.targetMissed.detail</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The video is fine to use; it may just sound slightly quieter or louder than other videos levelled with this tool.</t>
         </is>
       </c>
       <c r="D329" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 4, said in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10595,22 +10595,22 @@
     <row r="330">
       <c r="A330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossesCount.other</t>
+          <t xml:space="preserve">warnings.metadataLost.heading</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
+          <t xml:space="preserve">The file’s title and date could not be copied across</t>
         </is>
       </c>
       <c r="D330" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10627,22 +10627,22 @@
     <row r="331">
       <c r="A331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">announce.lossSaid</t>
+          <t xml:space="preserve">warnings.metadataLost.detail</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not shown: read out by screen readers</t>
+          <t xml:space="preserve">Step 6: warnings about the sound or the finished video</t>
         </is>
       </c>
       <c r="C331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{title}. {detail}</t>
+          <t xml:space="preserve">The picture and sound are unaffected. If your original carried a title, author or date, the new file will not have them — you can still add them wherever you upload it.</t>
         </is>
       </c>
       <c r="D331" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10659,22 +10659,22 @@
     <row r="332">
       <c r="A332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.originalUnchanged</t>
+          <t xml:space="preserve">announce.lossesCount.1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your original file has not been changed.</t>
+          <t xml:space="preserve">One thing to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D332" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 1, said in words.</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -10691,22 +10691,22 @@
     <row r="333">
       <c r="A333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.what</t>
+          <t xml:space="preserve">announce.lossesCount.2</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video.</t>
+          <t xml:space="preserve">Two things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D333" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 2, said in words.</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -10723,22 +10723,22 @@
     <row r="334">
       <c r="A334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.notAVideo</t>
+          <t xml:space="preserve">announce.lossesCount.3</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
+          <t xml:space="preserve">Three things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D334" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 3, said in words.</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -10755,22 +10755,22 @@
     <row r="335">
       <c r="A335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.soundOnly</t>
+          <t xml:space="preserve">announce.lossesCount.4</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
+          <t xml:space="preserve">Four things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D335" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used when the count is 4, said in words.</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -10787,22 +10787,22 @@
     <row r="336">
       <c r="A336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.noTracks</t>
+          <t xml:space="preserve">announce.lossesCount.other</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
+          <t xml:space="preserve">{count} things to know about what goes into the new file.</t>
         </is>
       </c>
       <c r="D336" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Used for any count above 4, in digits. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -10819,22 +10819,22 @@
     <row r="337">
       <c r="A337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.readError</t>
+          <t xml:space="preserve">announce.lossSaid</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An error box, in the step it affects</t>
+          <t xml:space="preserve">Not shown: read out by screen readers</t>
         </is>
       </c>
       <c r="C337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
+          <t xml:space="preserve">{title}. {detail}</t>
         </is>
       </c>
       <c r="D337" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {title}, {detail} as written: {title} is a heading from this sheet; {detail} is a sentence from this sheet.</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -10851,7 +10851,7 @@
     <row r="338">
       <c r="A338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
+          <t xml:space="preserve">failure.originalUnchanged</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
+          <t xml:space="preserve">Your original file has not been changed.</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="2">
@@ -10883,7 +10883,7 @@
     <row r="339">
       <c r="A339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unreadable.next</t>
+          <t xml:space="preserve">failure.unreadable.what</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
+          <t xml:space="preserve">This file could not be read as a video.</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="2">
@@ -10915,7 +10915,7 @@
     <row r="340">
       <c r="A340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.what</t>
+          <t xml:space="preserve">failure.unreadable.notAVideo</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="C340" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The start and end times could not be used.</t>
+          <t xml:space="preserve">This file could not be read as a video. It needs to be a video file — one whose name ends .mp4, .mov, .mkv or .webm — and it may be damaged.</t>
         </is>
       </c>
       <c r="D340" t="inlineStr" s="2">
@@ -10947,7 +10947,7 @@
     <row r="341">
       <c r="A341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.badTrim.next</t>
+          <t xml:space="preserve">failure.unreadable.soundOnly</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="C341" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
+          <t xml:space="preserve">This file has sound but no video. This tool adds branding to a video, so it needs a file with a picture.</t>
         </is>
       </c>
       <c r="D341" t="inlineStr" s="2">
@@ -10979,7 +10979,7 @@
     <row r="342">
       <c r="A342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.what</t>
+          <t xml:space="preserve">failure.unreadable.noTracks</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="C342" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
+          <t xml:space="preserve">No video or sound was found in this file. It may be incomplete, or it may have been saved incorrectly.</t>
         </is>
       </c>
       <c r="D342" t="inlineStr" s="2">
@@ -11011,7 +11011,7 @@
     <row r="343">
       <c r="A343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unlevellable.next</t>
+          <t xml:space="preserve">failure.unreadable.readError</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">Something went wrong reading this file. It may be damaged, or in a format this tool cannot read.</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="2">
@@ -11043,7 +11043,7 @@
     <row r="344">
       <c r="A344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputLoudness.what</t>
+          <t xml:space="preserve">failure.unreadable.tookTooLong</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
+          <t xml:space="preserve">Reading this file took longer than expected, or the tool ran into a problem.</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="2">
@@ -11075,7 +11075,7 @@
     <row r="345">
       <c r="A345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputPeak.what</t>
+          <t xml:space="preserve">failure.unreadable.next</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C345" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
+          <t xml:space="preserve">Choose a different file, or save this one again from the app that made it, as a file whose name ends .mp4.</t>
         </is>
       </c>
       <c r="D345" t="inlineStr" s="2">
@@ -11107,7 +11107,7 @@
     <row r="346">
       <c r="A346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outputUnreadable.what</t>
+          <t xml:space="preserve">failure.badTrim.what</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="C346" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
+          <t xml:space="preserve">The start and end times could not be used.</t>
         </is>
       </c>
       <c r="D346" t="inlineStr" s="2">
@@ -11139,7 +11139,7 @@
     <row r="347">
       <c r="A347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.what</t>
+          <t xml:space="preserve">failure.badTrim.next</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="C347" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This device ran out of working space part-way through.</t>
+          <t xml:space="preserve">Put the start and end times right in step 2 and try again.</t>
         </is>
       </c>
       <c r="D347" t="inlineStr" s="2">
@@ -11171,7 +11171,7 @@
     <row r="348">
       <c r="A348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.outOfSpace.next</t>
+          <t xml:space="preserve">failure.unlevellable.what</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11181,12 +11181,12 @@
       </c>
       <c r="C348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
+          <t xml:space="preserve">The sound of this recording cannot be brought to the usual level, so the video was not made.</t>
         </is>
       </c>
       <c r="D348" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11203,7 +11203,7 @@
     <row r="349">
       <c r="A349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.what</t>
+          <t xml:space="preserve">failure.unlevellable.next</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="C349" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
+          <t xml:space="preserve">Report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D349" t="inlineStr" s="2">
@@ -11235,7 +11235,7 @@
     <row r="350">
       <c r="A350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.encoderRefused.next</t>
+          <t xml:space="preserve">failure.outputLoudness.what</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="C350" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The finished sound did not come out at the usual level, so the video was not kept.</t>
         </is>
       </c>
       <c r="D350" t="inlineStr" s="2">
@@ -11267,7 +11267,7 @@
     <row r="351">
       <c r="A351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.what</t>
+          <t xml:space="preserve">failure.outputPeak.what</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="C351" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The device check did not finish.</t>
+          <t xml:space="preserve">The finished sound came out louder at its peaks than allowed, so the video was not kept.</t>
         </is>
       </c>
       <c r="D351" t="inlineStr" s="2">
@@ -11299,7 +11299,7 @@
     <row r="352">
       <c r="A352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.checkFailed.next</t>
+          <t xml:space="preserve">failure.outputUnreadable.what</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C352" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">The finished video could not be read back, so it was not kept.</t>
         </is>
       </c>
       <c r="D352" t="inlineStr" s="2">
@@ -11331,7 +11331,7 @@
     <row r="353">
       <c r="A353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.timedOut.what</t>
+          <t xml:space="preserve">failure.outOfSpace.what</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
+          <t xml:space="preserve">This device ran out of working space part-way through.</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="2">
@@ -11363,7 +11363,7 @@
     <row r="354">
       <c r="A354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.what</t>
+          <t xml:space="preserve">failure.outOfSpace.next</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
+          <t xml:space="preserve">Free some space, or choose {smaller}, and try again.</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {smaller} as written: {smaller} is the name of the smaller output, from preset.labels.smaller.</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11395,7 +11395,7 @@
     <row r="355">
       <c r="A355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.titleCardRefused.next</t>
+          <t xml:space="preserve">failure.encoderRefused.what</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
+          <t xml:space="preserve">This browser stopped encoding the video part-way through.</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11427,7 +11427,7 @@
     <row r="356">
       <c r="A356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.unknown.what</t>
+          <t xml:space="preserve">failure.encoderRefused.next</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something went wrong while creating the video.</t>
+          <t xml:space="preserve">Try the other output under File size / quality. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="2">
@@ -11459,7 +11459,7 @@
     <row r="357">
       <c r="A357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.tryAgain</t>
+          <t xml:space="preserve">failure.checkFailed.what</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C357" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
+          <t xml:space="preserve">The device check did not finish.</t>
         </is>
       </c>
       <c r="D357" t="inlineStr" s="2">
@@ -11491,17 +11491,17 @@
     <row r="358">
       <c r="A358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.insecure</t>
+          <t xml:space="preserve">failure.checkFailed.next</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C358" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
+          <t xml:space="preserve">Press Check again to run it once more. If it fails again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D358" t="inlineStr" s="2">
@@ -11523,22 +11523,22 @@
     <row r="359">
       <c r="A359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWebCodecs</t>
+          <t xml:space="preserve">failure.timedOut.what</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">The job stopped reporting progress, so it was stopped.</t>
         </is>
       </c>
       <c r="D359" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11555,22 +11555,22 @@
     <row r="360">
       <c r="A360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noH264</t>
+          <t xml:space="preserve">failure.titleCardRefused.what</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
+          <t xml:space="preserve">The title card’s words did not fit on the video, so it was not made.</t>
         </is>
       </c>
       <c r="D360" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11587,22 +11587,22 @@
     <row r="361">
       <c r="A361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.noWorkingStore</t>
+          <t xml:space="preserve">failure.titleCardRefused.next</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
+          <t xml:space="preserve">Shorten the title card’s fields in step 3 and try again.</t>
         </is>
       </c>
       <c r="D361" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
+          <t xml:space="preserve">Use the same words for "title card" as steps.titleCard.</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11619,17 +11619,17 @@
     <row r="362">
       <c r="A362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.startup.workerNotStarted</t>
+          <t xml:space="preserve">failure.unknown.what</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C362" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
+          <t xml:space="preserve">Something went wrong while creating the video.</t>
         </is>
       </c>
       <c r="D362" t="inlineStr" s="2">
@@ -11651,17 +11651,17 @@
     <row r="363">
       <c r="A363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">failure.captured</t>
+          <t xml:space="preserve">failure.tryAgain</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
+          <t xml:space="preserve">An error box, in the step it affects</t>
         </is>
       </c>
       <c r="C363" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
+          <t xml:space="preserve">Try again. If it happens again, report it with the Send feedback button — the details it adds will help.</t>
         </is>
       </c>
       <c r="D363" t="inlineStr" s="2">
@@ -11683,22 +11683,22 @@
     <row r="364">
       <c r="A364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.summary</t>
+          <t xml:space="preserve">failure.startup.insecure</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">System check — {result}</t>
+          <t xml:space="preserve">This page needs a secure connection before it can work with your video. Open it at an address that starts https://.</t>
         </is>
       </c>
       <c r="D364" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -11715,22 +11715,22 @@
     <row r="365">
       <c r="A365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.one</t>
+          <t xml:space="preserve">failure.startup.noWebCodecs</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problem</t>
+          <t xml:space="preserve">This browser cannot process video, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -11747,22 +11747,22 @@
     <row r="366">
       <c r="A366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.problems.other</t>
+          <t xml:space="preserve">failure.startup.noH264</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} problems</t>
+          <t xml:space="preserve">This browser cannot create the video format this tool needs, so the tool cannot run here. {remedy}</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -11779,22 +11779,22 @@
     <row r="367">
       <c r="A367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.one</t>
+          <t xml:space="preserve">failure.startup.noWorkingStore</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warning</t>
+          <t xml:space="preserve">This browser gives the tool no working space to build a video in. If you are browsing privately, an ordinary window usually works. {remedy}</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve">Keep {remedy} as written: {remedy} is another sentence from this sheet, saying what to do.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -11811,22 +11811,22 @@
     <row r="368">
       <c r="A368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.warnings.other</t>
+          <t xml:space="preserve">failure.startup.workerNotStarted</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">Step 1: the error box when this browser cannot run the tool at all</t>
         </is>
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">{count} warnings</t>
+          <t xml:space="preserve">The part of the tool that does the work did not start. Reload the page. If it happens again, report it with the Send feedback button.</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -11843,17 +11843,17 @@
     <row r="369">
       <c r="A369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.checking</t>
+          <t xml:space="preserve">failure.captured</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The System check at the foot of the page</t>
+          <t xml:space="preserve">The Errors captured panel, when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C369" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">checking</t>
+          <t xml:space="preserve">Something in the tool went wrong. A video being made may not finish; your original file is not affected. Report it with the Send feedback button, which adds these details.</t>
         </is>
       </c>
       <c r="D369" t="inlineStr" s="2">
@@ -11875,7 +11875,7 @@
     <row r="370">
       <c r="A370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.results.allPassed</t>
+          <t xml:space="preserve">systemCheck.summary</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">all passed</t>
+          <t xml:space="preserve">System check — {result}</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {result} as written: {result} is a count from systemCheck.results.</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -11907,7 +11907,7 @@
     <row r="371">
       <c r="A371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pass</t>
+          <t xml:space="preserve">systemCheck.results.problems.one</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OK</t>
+          <t xml:space="preserve">{count} problem</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -11939,7 +11939,7 @@
     <row r="372">
       <c r="A372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.fail</t>
+          <t xml:space="preserve">systemCheck.results.problems.other</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">{count} problems</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -11971,7 +11971,7 @@
     <row r="373">
       <c r="A373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.warn</t>
+          <t xml:space="preserve">systemCheck.results.warnings.one</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -11981,12 +11981,12 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">!</t>
+          <t xml:space="preserve">{count} warning</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
+          <t xml:space="preserve">Used when the count is 1. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12003,7 +12003,7 @@
     <row r="374">
       <c r="A374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.marks.pending</t>
+          <t xml:space="preserve">systemCheck.results.warnings.other</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">…</t>
+          <t xml:space="preserve">{count} warnings</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
+          <t xml:space="preserve">Used for any count other than 1. Fill it even if your language has one form. Keep {count} as written: {count} is a number.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12035,7 +12035,7 @@
     <row r="375">
       <c r="A375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.secure</t>
+          <t xml:space="preserve">systemCheck.results.checking</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secure connection (needed for storage access)</t>
+          <t xml:space="preserve">checking</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="2">
@@ -12067,7 +12067,7 @@
     <row r="376">
       <c r="A376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
+          <t xml:space="preserve">systemCheck.results.allPassed</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="C376" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
+          <t xml:space="preserve">all passed</t>
         </is>
       </c>
       <c r="D376" t="inlineStr" s="2">
@@ -12099,7 +12099,7 @@
     <row r="377">
       <c r="A377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.h264</t>
+          <t xml:space="preserve">systemCheck.marks.pass</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Video format the tool makes (H.264)</t>
+          <t xml:space="preserve">OK</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that passed.</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12131,7 +12131,7 @@
     <row r="378">
       <c r="A378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.aac</t>
+          <t xml:space="preserve">systemCheck.marks.fail</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
+          <t xml:space="preserve">No</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A one-word mark beside a check that failed.</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12163,7 +12163,7 @@
     <row r="379">
       <c r="A379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.opfs</t>
+          <t xml:space="preserve">systemCheck.marks.warn</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="C379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Private working storage</t>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
       <c r="D379" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is unless your language uses another.</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12195,7 +12195,7 @@
     <row r="380">
       <c r="A380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.rows.worker</t>
+          <t xml:space="preserve">systemCheck.marks.pending</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="C380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Background processing</t>
+          <t xml:space="preserve">…</t>
         </is>
       </c>
       <c r="D380" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A mark, not a word: keep it as it is.</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12227,7 +12227,7 @@
     <row r="381">
       <c r="A381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.checking</t>
+          <t xml:space="preserve">systemCheck.rows.secure</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="C381" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Checking</t>
+          <t xml:space="preserve">Secure connection (needed for storage access)</t>
         </is>
       </c>
       <c r="D381" t="inlineStr" s="2">
@@ -12259,7 +12259,7 @@
     <row r="382">
       <c r="A382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.available</t>
+          <t xml:space="preserve">systemCheck.rows.webcodecs</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="C382" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Available</t>
+          <t xml:space="preserve">Video processing in the browser (WebCodecs)</t>
         </is>
       </c>
       <c r="D382" t="inlineStr" s="2">
@@ -12291,7 +12291,7 @@
     <row r="383">
       <c r="A383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notAvailable</t>
+          <t xml:space="preserve">systemCheck.rows.h264</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="C383" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not available</t>
+          <t xml:space="preserve">Video format the tool makes (H.264)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr" s="2">
@@ -12323,7 +12323,7 @@
     <row r="384">
       <c r="A384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.supported</t>
+          <t xml:space="preserve">systemCheck.rows.aac</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="C384" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supported</t>
+          <t xml:space="preserve">Sound format the tool makes (AAC)</t>
         </is>
       </c>
       <c r="D384" t="inlineStr" s="2">
@@ -12355,7 +12355,7 @@
     <row r="385">
       <c r="A385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.notSupported</t>
+          <t xml:space="preserve">systemCheck.rows.opfs</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported</t>
+          <t xml:space="preserve">Private working storage</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="2">
@@ -12387,7 +12387,7 @@
     <row r="386">
       <c r="A386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
+          <t xml:space="preserve">systemCheck.rows.worker</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
+          <t xml:space="preserve">Background processing</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="2">
@@ -12419,7 +12419,7 @@
     <row r="387">
       <c r="A387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.failedToStart</t>
+          <t xml:space="preserve">systemCheck.values.checking</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Failed to start</t>
+          <t xml:space="preserve">Checking</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="2">
@@ -12451,7 +12451,7 @@
     <row r="388">
       <c r="A388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.readyIn</t>
+          <t xml:space="preserve">systemCheck.values.available</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ready in {time}</t>
+          <t xml:space="preserve">Available</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12483,7 +12483,7 @@
     <row r="389">
       <c r="A389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">systemCheck.values.noResponse</t>
+          <t xml:space="preserve">systemCheck.values.notAvailable</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="C389" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No response</t>
+          <t xml:space="preserve">Not available</t>
         </is>
       </c>
       <c r="D389" t="inlineStr" s="2">
@@ -12515,17 +12515,17 @@
     <row r="390">
       <c r="A390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.heading</t>
+          <t xml:space="preserve">systemCheck.values.supported</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C390" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Errors captured</t>
+          <t xml:space="preserve">Supported</t>
         </is>
       </c>
       <c r="D390" t="inlineStr" s="2">
@@ -12547,17 +12547,17 @@
     <row r="391">
       <c r="A391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.technicalDetails</t>
+          <t xml:space="preserve">systemCheck.values.notSupported</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C391" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Technical details</t>
+          <t xml:space="preserve">Not supported</t>
         </is>
       </c>
       <c r="D391" t="inlineStr" s="2">
@@ -12579,17 +12579,17 @@
     <row r="392">
       <c r="A392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">errors.report</t>
+          <t xml:space="preserve">systemCheck.values.aacNotSupported</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C392" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Report this problem</t>
+          <t xml:space="preserve">Not supported — a video with sound cannot be made here</t>
         </is>
       </c>
       <c r="D392" t="inlineStr" s="2">
@@ -12611,17 +12611,17 @@
     <row r="393">
       <c r="A393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.open</t>
+          <t xml:space="preserve">systemCheck.values.failedToStart</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C393" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Failed to start</t>
         </is>
       </c>
       <c r="D393" t="inlineStr" s="2">
@@ -12643,22 +12643,22 @@
     <row r="394">
       <c r="A394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.heading</t>
+          <t xml:space="preserve">systemCheck.values.readyIn</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Send feedback</t>
+          <t xml:space="preserve">Ready in {time}</t>
         </is>
       </c>
       <c r="D394" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {time} as written: {time} is a length of time in words.</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -12675,22 +12675,22 @@
     <row r="395">
       <c r="A395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.intro</t>
+          <t xml:space="preserve">systemCheck.values.noResponse</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The System check at the foot of the page</t>
         </is>
       </c>
       <c r="C395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
+          <t xml:space="preserve">No response</t>
         </is>
       </c>
       <c r="D395" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -12707,17 +12707,17 @@
     <row r="396">
       <c r="A396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.messageLabel</t>
+          <t xml:space="preserve">errors.heading</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C396" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message</t>
+          <t xml:space="preserve">Errors captured</t>
         </is>
       </c>
       <c r="D396" t="inlineStr" s="2">
@@ -12739,17 +12739,17 @@
     <row r="397">
       <c r="A397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.writeFirst</t>
+          <t xml:space="preserve">errors.technicalDetails</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C397" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Write a message first.</t>
+          <t xml:space="preserve">Technical details</t>
         </is>
       </c>
       <c r="D397" t="inlineStr" s="2">
@@ -12771,17 +12771,17 @@
     <row r="398">
       <c r="A398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSent</t>
+          <t xml:space="preserve">errors.report</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Send feedback dialog</t>
+          <t xml:space="preserve">The Errors captured panel, only shown when something in the tool goes wrong</t>
         </is>
       </c>
       <c r="C398" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">What will be sent with it</t>
+          <t xml:space="preserve">Report this problem</t>
         </is>
       </c>
       <c r="D398" t="inlineStr" s="2">
@@ -12803,7 +12803,7 @@
     <row r="399">
       <c r="A399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.whatSentDetail</t>
+          <t xml:space="preserve">feedback.open</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="C399" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D399" t="inlineStr" s="2">
@@ -12835,7 +12835,7 @@
     <row r="400">
       <c r="A400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.openEmail</t>
+          <t xml:space="preserve">feedback.heading</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="C400" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open email app</t>
+          <t xml:space="preserve">Send feedback</t>
         </is>
       </c>
       <c r="D400" t="inlineStr" s="2">
@@ -12867,7 +12867,7 @@
     <row r="401">
       <c r="A401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copy</t>
+          <t xml:space="preserve">feedback.intro</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copy message and details</t>
+          <t xml:space="preserve">Your message goes to {address} from your own email app. You will see the email before it is sent.</t>
         </is>
       </c>
       <c r="D401" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -12899,7 +12899,7 @@
     <row r="402">
       <c r="A402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.close</t>
+          <t xml:space="preserve">feedback.messageLabel</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C402" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Close</t>
+          <t xml:space="preserve">Your message</t>
         </is>
       </c>
       <c r="D402" t="inlineStr" s="2">
@@ -12931,7 +12931,7 @@
     <row r="403">
       <c r="A403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.tooLong</t>
+          <t xml:space="preserve">feedback.writeFirst</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -12941,12 +12941,12 @@
       </c>
       <c r="C403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">Write a message first.</t>
         </is>
       </c>
       <c r="D403" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -12963,7 +12963,7 @@
     <row r="404">
       <c r="A404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.opened</t>
+          <t xml:space="preserve">feedback.whatSent</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="C404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
+          <t xml:space="preserve">What will be sent with it</t>
         </is>
       </c>
       <c r="D404" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -12995,7 +12995,7 @@
     <row r="405">
       <c r="A405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.someOmitted</t>
+          <t xml:space="preserve">feedback.whatSentDetail</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="C405" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
+          <t xml:space="preserve">Details that help find a problem: the app's version, your browser, how far you got, and your video's length, picture size and format. These details never include the video, its name, or anything in it.</t>
         </is>
       </c>
       <c r="D405" t="inlineStr" s="2">
@@ -13027,7 +13027,7 @@
     <row r="406">
       <c r="A406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.copied</t>
+          <t xml:space="preserve">feedback.openEmail</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13037,12 +13037,12 @@
       </c>
       <c r="C406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
+          <t xml:space="preserve">Open email app</t>
         </is>
       </c>
       <c r="D406" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13059,7 +13059,7 @@
     <row r="407">
       <c r="A407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.couldNotCopy</t>
+          <t xml:space="preserve">feedback.copy</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
+          <t xml:space="preserve">Copy message and details</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="2">
@@ -13091,7 +13091,7 @@
     <row r="408">
       <c r="A408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feedback.onlyInCopy</t>
+          <t xml:space="preserve">feedback.close</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
+          <t xml:space="preserve">Close</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="2">
@@ -13123,22 +13123,22 @@
     <row r="409">
       <c r="A409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.heading</t>
+          <t xml:space="preserve">feedback.tooLong</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Accessibility statement</t>
+          <t xml:space="preserve">Your message is too long to hand to your email app in one go. Choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13155,22 +13155,22 @@
     <row r="410">
       <c r="A410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.covers</t>
+          <t xml:space="preserve">feedback.opened</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
+          <t xml:space="preserve">Your email app should have opened with your message ready to send. If it did not, choose "Copy message and details" and paste them into an email to {address}.</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13187,22 +13187,22 @@
     <row r="411">
       <c r="A411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.aim</t>
+          <t xml:space="preserve">feedback.someOmitted</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
+          <t xml:space="preserve">Some details did not fit in the email; the copy has them all.</t>
         </is>
       </c>
       <c r="D411" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13219,22 +13219,22 @@
     <row r="412">
       <c r="A412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.0</t>
+          <t xml:space="preserve">feedback.copied</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a keyboard alone</t>
+          <t xml:space="preserve">Copied. Paste it into an email to {address}.</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">Keep {address} as written: {address} is an email address.</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13251,22 +13251,22 @@
     <row r="413">
       <c r="A413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.1</t>
+          <t xml:space="preserve">feedback.couldNotCopy</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
+          <t xml:space="preserve">Could not copy. Open "What will be sent with it", select the details, and copy them with your message.</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13283,22 +13283,22 @@
     <row r="414">
       <c r="A414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.2</t>
+          <t xml:space="preserve">feedback.onlyInCopy</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Send feedback dialog</t>
         </is>
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
+          <t xml:space="preserve">Too long for the email, so only in "Copy message and details":</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13315,22 +13315,22 @@
     <row r="415">
       <c r="A415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.3</t>
+          <t xml:space="preserve">statement.heading</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page: the heading of the panel</t>
         </is>
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
+          <t xml:space="preserve">Accessibility statement</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">The heading of the panel, so no full stop. A formal statement, as on any official website.</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13347,22 +13347,22 @@
     <row r="416">
       <c r="A416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.abilities.4</t>
+          <t xml:space="preserve">statement.covers</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
+          <t xml:space="preserve">This statement covers UoN Video Helper, the page you are on. Joe Bell runs it at the University of Nottingham.</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
+          <t xml:space="preserve">UoN Video Helper is the product name: use the same name as app.title. Keep the name Joe Bell as it is. A formal statement: use a formal register throughout.</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13379,7 +13379,7 @@
     <row r="417">
       <c r="A417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.plain</t>
+          <t xml:space="preserve">statement.aim</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
+          <t xml:space="preserve">We want as many people as possible to be able to use this tool. You should be able to:</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow, which complete its last sentence.</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13411,22 +13411,22 @@
     <row r="418">
       <c r="A418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.heading</t>
+          <t xml:space="preserve">statement.abilities.0</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">How accessible this tool is</t>
+          <t xml:space="preserve">use it with a keyboard alone</t>
         </is>
       </c>
       <c r="D418" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13443,22 +13443,22 @@
     <row r="419">
       <c r="A419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.intro</t>
+          <t xml:space="preserve">statement.abilities.1</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">We know some parts are not fully accessible:</t>
+          <t xml:space="preserve">use it with a screen reader, which reads out each stage and result</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Introduces the five lines that follow.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13475,22 +13475,22 @@
     <row r="420">
       <c r="A420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.0</t>
+          <t xml:space="preserve">statement.abilities.2</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
+          <t xml:space="preserve">zoom in to 200% without the text going off the screen</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13507,22 +13507,22 @@
     <row r="421">
       <c r="A421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.1</t>
+          <t xml:space="preserve">statement.abilities.3</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
+          <t xml:space="preserve">use your own colours, and your computer's high contrast mode</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13539,22 +13539,22 @@
     <row r="422">
       <c r="A422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.2</t>
+          <t xml:space="preserve">statement.abilities.4</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, completing "You should be able to:"</t>
         </is>
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
+          <t xml:space="preserve">turn off movement on the page in your computer's settings</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Completes "You should be able to:", so it starts in lower case, as the English does, and has no full stop.</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13571,17 +13571,17 @@
     <row r="423">
       <c r="A423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.3</t>
+          <t xml:space="preserve">statement.plain</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The preview plays your own video. Its captions, and whether it flashes, depend on your recording.</t>
+          <t xml:space="preserve">The words are plain, and the text has strong contrast with its background.</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="2">
@@ -13603,22 +13603,22 @@
     <row r="424">
       <c r="A424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.limits.items.4</t>
+          <t xml:space="preserve">statement.limits.heading</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
+          <t xml:space="preserve">The Accessibility statement: a subheading</t>
         </is>
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Some short forms are not spelled out: file sizes, such as MB and GB, and video format names, such as H.264 and AAC.</t>
+          <t xml:space="preserve">How accessible this tool is</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep MB, GB, H.264 and AAC as they are: these short forms are what the sentence is about.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -13635,22 +13635,22 @@
     <row r="425">
       <c r="A425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.heading</t>
+          <t xml:space="preserve">statement.limits.intro</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
         </is>
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Feedback and contact</t>
+          <t xml:space="preserve">We know some parts are not fully accessible:</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Introduces the five lines that follow.</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -13667,22 +13667,22 @@
     <row r="426">
       <c r="A426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.contact.text</t>
+          <t xml:space="preserve">statement.limits.items.0</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">If you find a problem with this tool, or need its information in another way, email Joe Bell at {address}.</t>
+          <t xml:space="preserve">It is built for Google Chrome on a computer. In other browsers, it may not work.</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Keep the name Joe Bell as it is. The email address is shown as a link. Keep {address} as written: {address} is an email address.</t>
+          <t xml:space="preserve">Keep the name Google Chrome as it is.</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -13699,22 +13699,22 @@
     <row r="427">
       <c r="A427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.heading</t>
+          <t xml:space="preserve">statement.limits.items.1</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement: a subheading</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enforcement procedure</t>
+          <t xml:space="preserve">The Chinese and Malay pages were translated by a computer. Colleagues who speak each language are checking them on the live page.</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">"Malay" is the language this page calls Bahasa Malaysia.</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -13731,22 +13731,22 @@
     <row r="428">
       <c r="A428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.text</t>
+          <t xml:space="preserve">statement.limits.items.2</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible this tool is"</t>
         </is>
       </c>
       <c r="C428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission enforces the accessibility regulations. If you are not happy with how we answer your complaint, you can get in touch with the {service}.</t>
+          <t xml:space="preserve">Chinese text uses your computer's own Chinese font, so it may look different from one computer to another.</t>
         </is>
       </c>
       <c r="D428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Equality and Human Rights Commission is an official UK body: give its English name with a translation in brackets, or name it as your language normally would. Keep {service} as written: {service} is the advice service's name, from statement.enforcement.service, as a link to its website.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -13763,22 +13763,22 @@
     <row r="429">
       <c r="A429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">statement.enforcement.service</t>
+          <t xml:space="preserve">statement.limits.items.3</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Accessibility statement at the foot of the page, a panel that opens: its running text</t>
+          <t xml:space="preserve">The Accessibility statement: a list item, under "How accessible